--- a/.design/DB/DB設計.xlsx
+++ b/.design/DB/DB設計.xlsx
@@ -8,17 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevelopmentProjects\vtuber-meikan\.design\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453B5CC9-91B3-4C79-8A3D-D625C43563D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6BC254-4A34-47BF-B8CE-3378846D6A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="-120" windowWidth="57840" windowHeight="31920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テーブル一覧" sheetId="1" r:id="rId1"/>
     <sheet name="テーブル定義_一覧" sheetId="2" r:id="rId2"/>
     <sheet name="型とバイト数" sheetId="3" r:id="rId3"/>
+    <sheet name="|→マスターデータ" sheetId="4" r:id="rId4"/>
+    <sheet name="各テーブル" sheetId="7" r:id="rId5"/>
+    <sheet name="監査列" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">テーブル一覧!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">テーブル一覧!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">テーブル定義_一覧!$A$1:$U$280</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">型とバイト数!$A$2:$G$2</definedName>
   </definedNames>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2177" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="588">
   <si>
     <t>設計完了</t>
   </si>
@@ -1789,10 +1792,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>screen_element.screen_element_uuid</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>screen_element.screen_element_uuidかそれ以外のテーブルのものかを管理する</t>
     <rPh sb="37" eb="39">
       <t>イガイ</t>
@@ -1837,12 +1836,541 @@
     <t>論理名はscreen_wordテーブルで管理する</t>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>テーブル</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>badge</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>timestamptz</t>
+  </si>
+  <si>
+    <t>型</t>
+    <rPh sb="0" eb="1">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>カラム名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>物理名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>カラム名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>論理名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>#1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>#2</t>
+  </si>
+  <si>
+    <t>#3</t>
+  </si>
+  <si>
+    <t>#4</t>
+  </si>
+  <si>
+    <t>#5</t>
+  </si>
+  <si>
+    <t>#6</t>
+  </si>
+  <si>
+    <t>#7</t>
+  </si>
+  <si>
+    <t>#8</t>
+  </si>
+  <si>
+    <t>#9</t>
+  </si>
+  <si>
+    <t>#10</t>
+  </si>
+  <si>
+    <t>#11</t>
+  </si>
+  <si>
+    <t>#12</t>
+  </si>
+  <si>
+    <t>#13</t>
+  </si>
+  <si>
+    <t>#14</t>
+  </si>
+  <si>
+    <t>#15</t>
+  </si>
+  <si>
+    <t>#16</t>
+  </si>
+  <si>
+    <t>#17</t>
+  </si>
+  <si>
+    <t>#18</t>
+  </si>
+  <si>
+    <t>#19</t>
+  </si>
+  <si>
+    <t>#20</t>
+  </si>
+  <si>
+    <t>参考情報</t>
+    <rPh sb="0" eb="2">
+      <t>サンコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>レコード</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>recently_update</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>newcomer</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>most_watch</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>dev_user</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>screen_word</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>各テーブル共通</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウツウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※各テーブル、カラムで共通の値を使用する</t>
+    <rPh sb="1" eb="2">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>自動生成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <rPh sb="1" eb="5">
+      <t>ジドウセイセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>{badge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>テーブルの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>most_watchのUUID}</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>{badge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>テーブルの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>newcomer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UUID}</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>{badge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>テーブルの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>recently_update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UUID}</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>よく見られているVtuber</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>新人Vtuber</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>最近更新されたVtuber</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>other_tables</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>language</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>FK参照先</t>
+    <rPh sb="2" eb="4">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>FK</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>PK</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ワードの検索キー。screen_element.screen_element_uuidかそれ以外のテーブルの対象UUIDが入る</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>dev</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>japan</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>NULL</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>{language</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>テーブルの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dev</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UUID}</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>{language</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>テーブルの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>japan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UUID}</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1885,8 +2413,76 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1923,8 +2519,20 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2001,11 +2609,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2069,7 +2703,61 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2677,7 +3365,7 @@
     <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C14,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v/>
+        <v>〇</v>
       </c>
       <c r="B14" s="2">
         <f t="shared" si="0"/>
@@ -3139,7 +3827,7 @@
       <c r="H29" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H29" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -3288,7 +3976,7 @@
       <c r="K2" s="11"/>
       <c r="L2" s="9"/>
       <c r="M2" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K2="","",IF(L2="","参照先未定義",_xlfn.XLOOKUP(L2,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ref="M2:M65" si="1">_xlfn.SINGLE(IF(K2="","",IF(L2="","参照先未定義",_xlfn.XLOOKUP(L2,B:B,C:C,"エラー"))))</f>
         <v/>
       </c>
       <c r="N2" s="11" t="s">
@@ -3311,7 +3999,7 @@
         <v>46</v>
       </c>
       <c r="B3" s="9" t="str">
-        <f t="shared" ref="B3:B62" ca="1" si="1">D3&amp;"."&amp;F3</f>
+        <f t="shared" ref="B3:B62" ca="1" si="2">D3&amp;"."&amp;F3</f>
         <v>vtuber_profiles.vtuber_profiles_id</v>
       </c>
       <c r="C3" s="10">
@@ -3355,7 +4043,7 @@
       <c r="K3" s="11"/>
       <c r="L3" s="9"/>
       <c r="M3" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K3="","",IF(L3="","参照先未定義",_xlfn.XLOOKUP(L3,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N3" s="11" t="s">
@@ -3378,7 +4066,7 @@
         <v>46</v>
       </c>
       <c r="B4" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>vtuber_profiles.user_id</v>
       </c>
       <c r="C4" s="10">
@@ -3426,7 +4114,7 @@
         <v>506</v>
       </c>
       <c r="M4" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K4="","",IF(L4="","参照先未定義",_xlfn.XLOOKUP(L4,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>149</v>
       </c>
       <c r="N4" s="11"/>
@@ -3445,7 +4133,7 @@
         <v>46</v>
       </c>
       <c r="B5" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>vtuber_profiles.join_group</v>
       </c>
       <c r="C5" s="10">
@@ -3493,7 +4181,7 @@
         <v>507</v>
       </c>
       <c r="M5" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K5="","",IF(L5="","参照先未定義",_xlfn.XLOOKUP(L5,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>12</v>
       </c>
       <c r="N5" s="11"/>
@@ -3512,7 +4200,7 @@
         <v>46</v>
       </c>
       <c r="B6" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>vtuber_profiles.debut_date</v>
       </c>
       <c r="C6" s="10">
@@ -3556,7 +4244,7 @@
       <c r="K6" s="11"/>
       <c r="L6" s="9"/>
       <c r="M6" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K6="","",IF(L6="","参照先未定義",_xlfn.XLOOKUP(L6,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N6" s="11"/>
@@ -3575,7 +4263,7 @@
         <v>46</v>
       </c>
       <c r="B7" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>vtuber_profiles.activity_status</v>
       </c>
       <c r="C7" s="10">
@@ -3623,7 +4311,7 @@
         <v>508</v>
       </c>
       <c r="M7" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K7="","",IF(L7="","参照先未定義",_xlfn.XLOOKUP(L7,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
       <c r="N7" s="11" t="s">
@@ -3642,7 +4330,7 @@
         <v>46</v>
       </c>
       <c r="B8" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>vtuber_profiles.create_datetime</v>
       </c>
       <c r="C8" s="10">
@@ -3686,7 +4374,7 @@
       <c r="K8" s="11"/>
       <c r="L8" s="9"/>
       <c r="M8" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K8="","",IF(L8="","参照先未定義",_xlfn.XLOOKUP(L8,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N8" s="11" t="s">
@@ -3707,7 +4395,7 @@
         <v>46</v>
       </c>
       <c r="B9" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>vtuber_profiles.create_user</v>
       </c>
       <c r="C9" s="10">
@@ -3751,7 +4439,7 @@
       <c r="K9" s="11"/>
       <c r="L9" s="9"/>
       <c r="M9" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K9="","",IF(L9="","参照先未定義",_xlfn.XLOOKUP(L9,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N9" s="11" t="s">
@@ -3774,7 +4462,7 @@
         <v>46</v>
       </c>
       <c r="B10" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>vtuber_profiles.update_datetime</v>
       </c>
       <c r="C10" s="10">
@@ -3796,7 +4484,7 @@
         <v>118</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I10" s="11">
         <f>_xlfn.LET(
@@ -3818,7 +4506,7 @@
       <c r="K10" s="11"/>
       <c r="L10" s="9"/>
       <c r="M10" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K10="","",IF(L10="","参照先未定義",_xlfn.XLOOKUP(L10,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N10" s="11" t="s">
@@ -3839,7 +4527,7 @@
         <v>46</v>
       </c>
       <c r="B11" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>vtuber_profiles.update_user</v>
       </c>
       <c r="C11" s="10">
@@ -3883,7 +4571,7 @@
       <c r="K11" s="11"/>
       <c r="L11" s="9"/>
       <c r="M11" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K11="","",IF(L11="","参照先未定義",_xlfn.XLOOKUP(L11,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N11" s="11" t="s">
@@ -3906,7 +4594,7 @@
         <v>46</v>
       </c>
       <c r="B12" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>vtuber_profiles.soft_delete_flag</v>
       </c>
       <c r="C12" s="10">
@@ -3950,7 +4638,7 @@
       <c r="K12" s="11"/>
       <c r="L12" s="9"/>
       <c r="M12" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K12="","",IF(L12="","参照先未定義",_xlfn.XLOOKUP(L12,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N12" s="11" t="s">
@@ -3971,7 +4659,7 @@
         <v>46</v>
       </c>
       <c r="B13" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>join_group.join_group_uuid</v>
       </c>
       <c r="C13" s="10">
@@ -4016,7 +4704,7 @@
       <c r="K13" s="11"/>
       <c r="L13" s="9"/>
       <c r="M13" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K13="","",IF(L13="","参照先未定義",_xlfn.XLOOKUP(L13,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N13" s="11" t="s">
@@ -4039,7 +4727,7 @@
         <v>46</v>
       </c>
       <c r="B14" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>join_group.group_name</v>
       </c>
       <c r="C14" s="10">
@@ -4083,7 +4771,7 @@
       <c r="K14" s="11"/>
       <c r="L14" s="9"/>
       <c r="M14" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K14="","",IF(L14="","参照先未定義",_xlfn.XLOOKUP(L14,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N14" s="11" t="s">
@@ -4106,7 +4794,7 @@
         <v>46</v>
       </c>
       <c r="B15" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>join_group.operation_status</v>
       </c>
       <c r="C15" s="10">
@@ -4154,7 +4842,7 @@
         <v>508</v>
       </c>
       <c r="M15" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K15="","",IF(L15="","参照先未定義",_xlfn.XLOOKUP(L15,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>35</v>
       </c>
       <c r="N15" s="11"/>
@@ -4171,7 +4859,7 @@
         <v>46</v>
       </c>
       <c r="B16" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>join_group.group_detail</v>
       </c>
       <c r="C16" s="10">
@@ -4215,7 +4903,7 @@
       <c r="K16" s="11"/>
       <c r="L16" s="9"/>
       <c r="M16" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K16="","",IF(L16="","参照先未定義",_xlfn.XLOOKUP(L16,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N16" s="11"/>
@@ -4232,7 +4920,7 @@
         <v>46</v>
       </c>
       <c r="B17" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>join_group.create_datetime</v>
       </c>
       <c r="C17" s="10">
@@ -4276,7 +4964,7 @@
       <c r="K17" s="11"/>
       <c r="L17" s="9"/>
       <c r="M17" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K17="","",IF(L17="","参照先未定義",_xlfn.XLOOKUP(L17,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N17" s="11" t="s">
@@ -4297,7 +4985,7 @@
         <v>46</v>
       </c>
       <c r="B18" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>join_group.create_user</v>
       </c>
       <c r="C18" s="10">
@@ -4341,7 +5029,7 @@
       <c r="K18" s="11"/>
       <c r="L18" s="9"/>
       <c r="M18" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K18="","",IF(L18="","参照先未定義",_xlfn.XLOOKUP(L18,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N18" s="11" t="s">
@@ -4364,7 +5052,7 @@
         <v>46</v>
       </c>
       <c r="B19" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>join_group.update_datetime</v>
       </c>
       <c r="C19" s="10">
@@ -4408,7 +5096,7 @@
       <c r="K19" s="11"/>
       <c r="L19" s="9"/>
       <c r="M19" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K19="","",IF(L19="","参照先未定義",_xlfn.XLOOKUP(L19,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N19" s="11" t="s">
@@ -4429,7 +5117,7 @@
         <v>46</v>
       </c>
       <c r="B20" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>join_group.update_user</v>
       </c>
       <c r="C20" s="10">
@@ -4473,7 +5161,7 @@
       <c r="K20" s="11"/>
       <c r="L20" s="9"/>
       <c r="M20" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K20="","",IF(L20="","参照先未定義",_xlfn.XLOOKUP(L20,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N20" s="11" t="s">
@@ -4496,7 +5184,7 @@
         <v>46</v>
       </c>
       <c r="B21" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>join_group.soft_delete_flag</v>
       </c>
       <c r="C21" s="10">
@@ -4540,7 +5228,7 @@
       <c r="K21" s="11"/>
       <c r="L21" s="9"/>
       <c r="M21" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K21="","",IF(L21="","参照先未定義",_xlfn.XLOOKUP(L21,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N21" s="11" t="s">
@@ -4561,7 +5249,7 @@
         <v>46</v>
       </c>
       <c r="B22" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>tag.tag_uuid</v>
       </c>
       <c r="C22" s="10">
@@ -4606,7 +5294,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="9"/>
       <c r="M22" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K22="","",IF(L22="","参照先未定義",_xlfn.XLOOKUP(L22,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N22" s="11" t="s">
@@ -4629,7 +5317,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>tag.tag</v>
       </c>
       <c r="C23" s="10">
@@ -4673,7 +5361,7 @@
       <c r="K23" s="11"/>
       <c r="L23" s="9"/>
       <c r="M23" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K23="","",IF(L23="","参照先未定義",_xlfn.XLOOKUP(L23,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N23" s="11" t="s">
@@ -4696,7 +5384,7 @@
         <v>46</v>
       </c>
       <c r="B24" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>tag.create_datetime</v>
       </c>
       <c r="C24" s="10">
@@ -4740,7 +5428,7 @@
       <c r="K24" s="11"/>
       <c r="L24" s="9"/>
       <c r="M24" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K24="","",IF(L24="","参照先未定義",_xlfn.XLOOKUP(L24,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N24" s="11" t="s">
@@ -4761,7 +5449,7 @@
         <v>46</v>
       </c>
       <c r="B25" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>tag.create_user</v>
       </c>
       <c r="C25" s="10">
@@ -4805,7 +5493,7 @@
       <c r="K25" s="11"/>
       <c r="L25" s="9"/>
       <c r="M25" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K25="","",IF(L25="","参照先未定義",_xlfn.XLOOKUP(L25,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N25" s="11" t="s">
@@ -4828,7 +5516,7 @@
         <v>46</v>
       </c>
       <c r="B26" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>tag.update_datetime</v>
       </c>
       <c r="C26" s="10">
@@ -4872,7 +5560,7 @@
       <c r="K26" s="11"/>
       <c r="L26" s="9"/>
       <c r="M26" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K26="","",IF(L26="","参照先未定義",_xlfn.XLOOKUP(L26,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N26" s="11" t="s">
@@ -4893,7 +5581,7 @@
         <v>46</v>
       </c>
       <c r="B27" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>tag.update_user</v>
       </c>
       <c r="C27" s="10">
@@ -4937,7 +5625,7 @@
       <c r="K27" s="11"/>
       <c r="L27" s="9"/>
       <c r="M27" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K27="","",IF(L27="","参照先未定義",_xlfn.XLOOKUP(L27,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N27" s="11" t="s">
@@ -4960,7 +5648,7 @@
         <v>46</v>
       </c>
       <c r="B28" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>tag.soft_delete_flag</v>
       </c>
       <c r="C28" s="10">
@@ -5004,7 +5692,7 @@
       <c r="K28" s="11"/>
       <c r="L28" s="9"/>
       <c r="M28" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K28="","",IF(L28="","参照先未定義",_xlfn.XLOOKUP(L28,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N28" s="11" t="s">
@@ -5025,7 +5713,7 @@
         <v>46</v>
       </c>
       <c r="B29" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>badge.badge_uuid</v>
       </c>
       <c r="C29" s="10">
@@ -5070,7 +5758,7 @@
       <c r="K29" s="11"/>
       <c r="L29" s="9"/>
       <c r="M29" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K29="","",IF(L29="","参照先未定義",_xlfn.XLOOKUP(L29,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N29" s="11" t="s">
@@ -5093,7 +5781,7 @@
         <v>46</v>
       </c>
       <c r="B30" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>badge.badge_physical_name</v>
       </c>
       <c r="C30" s="10">
@@ -5137,7 +5825,7 @@
       <c r="K30" s="11"/>
       <c r="L30" s="9"/>
       <c r="M30" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K30="","",IF(L30="","参照先未定義",_xlfn.XLOOKUP(L30,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N30" s="11" t="s">
@@ -5154,7 +5842,7 @@
         <v>51</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5162,7 +5850,7 @@
         <v>46</v>
       </c>
       <c r="B31" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>badge.create_datetime</v>
       </c>
       <c r="C31" s="10">
@@ -5206,7 +5894,7 @@
       <c r="K31" s="11"/>
       <c r="L31" s="9"/>
       <c r="M31" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K31="","",IF(L31="","参照先未定義",_xlfn.XLOOKUP(L31,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N31" s="11" t="s">
@@ -5227,7 +5915,7 @@
         <v>46</v>
       </c>
       <c r="B32" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>badge.create_user</v>
       </c>
       <c r="C32" s="10">
@@ -5271,7 +5959,7 @@
       <c r="K32" s="11"/>
       <c r="L32" s="9"/>
       <c r="M32" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K32="","",IF(L32="","参照先未定義",_xlfn.XLOOKUP(L32,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N32" s="11" t="s">
@@ -5294,7 +5982,7 @@
         <v>46</v>
       </c>
       <c r="B33" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>badge.update_datetime</v>
       </c>
       <c r="C33" s="10">
@@ -5338,7 +6026,7 @@
       <c r="K33" s="11"/>
       <c r="L33" s="9"/>
       <c r="M33" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K33="","",IF(L33="","参照先未定義",_xlfn.XLOOKUP(L33,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N33" s="11" t="s">
@@ -5359,7 +6047,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>badge.update_user</v>
       </c>
       <c r="C34" s="10">
@@ -5403,7 +6091,7 @@
       <c r="K34" s="11"/>
       <c r="L34" s="9"/>
       <c r="M34" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K34="","",IF(L34="","参照先未定義",_xlfn.XLOOKUP(L34,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N34" s="11" t="s">
@@ -5426,7 +6114,7 @@
         <v>46</v>
       </c>
       <c r="B35" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>badge.soft_delete_flag</v>
       </c>
       <c r="C35" s="10">
@@ -5470,7 +6158,7 @@
       <c r="K35" s="11"/>
       <c r="L35" s="9"/>
       <c r="M35" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K35="","",IF(L35="","参照先未定義",_xlfn.XLOOKUP(L35,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N35" s="11" t="s">
@@ -5491,7 +6179,7 @@
         <v>46</v>
       </c>
       <c r="B36" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>activity_status.activity_status_uuid</v>
       </c>
       <c r="C36" s="10">
@@ -5536,7 +6224,7 @@
       <c r="K36" s="11"/>
       <c r="L36" s="9"/>
       <c r="M36" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K36="","",IF(L36="","参照先未定義",_xlfn.XLOOKUP(L36,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N36" s="11" t="s">
@@ -5559,7 +6247,7 @@
         <v>46</v>
       </c>
       <c r="B37" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>activity_status.activity_status_physical_name</v>
       </c>
       <c r="C37" s="10">
@@ -5603,7 +6291,7 @@
       <c r="K37" s="11"/>
       <c r="L37" s="9"/>
       <c r="M37" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K37="","",IF(L37="","参照先未定義",_xlfn.XLOOKUP(L37,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N37" s="11" t="s">
@@ -5618,7 +6306,7 @@
       <c r="S37" s="9"/>
       <c r="T37" s="9"/>
       <c r="U37" s="11" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5626,7 +6314,7 @@
         <v>46</v>
       </c>
       <c r="B38" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>activity_status.create_datetime</v>
       </c>
       <c r="C38" s="10">
@@ -5670,7 +6358,7 @@
       <c r="K38" s="11"/>
       <c r="L38" s="9"/>
       <c r="M38" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K38="","",IF(L38="","参照先未定義",_xlfn.XLOOKUP(L38,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N38" s="11" t="s">
@@ -5691,7 +6379,7 @@
         <v>46</v>
       </c>
       <c r="B39" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>activity_status.create_user</v>
       </c>
       <c r="C39" s="10">
@@ -5735,7 +6423,7 @@
       <c r="K39" s="11"/>
       <c r="L39" s="9"/>
       <c r="M39" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K39="","",IF(L39="","参照先未定義",_xlfn.XLOOKUP(L39,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N39" s="11" t="s">
@@ -5758,7 +6446,7 @@
         <v>46</v>
       </c>
       <c r="B40" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>activity_status.update_datetime</v>
       </c>
       <c r="C40" s="10">
@@ -5802,7 +6490,7 @@
       <c r="K40" s="11"/>
       <c r="L40" s="9"/>
       <c r="M40" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K40="","",IF(L40="","参照先未定義",_xlfn.XLOOKUP(L40,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N40" s="11" t="s">
@@ -5823,7 +6511,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>activity_status.update_user</v>
       </c>
       <c r="C41" s="10">
@@ -5867,7 +6555,7 @@
       <c r="K41" s="11"/>
       <c r="L41" s="9"/>
       <c r="M41" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K41="","",IF(L41="","参照先未定義",_xlfn.XLOOKUP(L41,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N41" s="11" t="s">
@@ -5890,7 +6578,7 @@
         <v>46</v>
       </c>
       <c r="B42" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>activity_status.soft_delete_flag</v>
       </c>
       <c r="C42" s="10">
@@ -5934,7 +6622,7 @@
       <c r="K42" s="11"/>
       <c r="L42" s="9"/>
       <c r="M42" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K42="","",IF(L42="","参照先未定義",_xlfn.XLOOKUP(L42,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N42" s="11" t="s">
@@ -5955,7 +6643,7 @@
         <v>46</v>
       </c>
       <c r="B43" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>sns_link.sns_link_uuid</v>
       </c>
       <c r="C43" s="10">
@@ -6000,7 +6688,7 @@
       <c r="K43" s="11"/>
       <c r="L43" s="9"/>
       <c r="M43" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K43="","",IF(L43="","参照先未定義",_xlfn.XLOOKUP(L43,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N43" s="11" t="s">
@@ -6023,7 +6711,7 @@
         <v>46</v>
       </c>
       <c r="B44" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>sns_link.vtuber_profiles_id</v>
       </c>
       <c r="C44" s="10">
@@ -6071,7 +6759,7 @@
         <v>509</v>
       </c>
       <c r="M44" s="11">
-        <f>_xlfn.SINGLE(IF(K44="","",IF(L44="","参照先未定義",_xlfn.XLOOKUP(L44,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N44" s="11" t="s">
@@ -6090,7 +6778,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>sns_link.sns_icon</v>
       </c>
       <c r="C45" s="10">
@@ -6138,7 +6826,7 @@
         <v>510</v>
       </c>
       <c r="M45" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K45="","",IF(L45="","参照先未定義",_xlfn.XLOOKUP(L45,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>121</v>
       </c>
       <c r="N45" s="11"/>
@@ -6157,7 +6845,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>sns_link.sns_link_label</v>
       </c>
       <c r="C46" s="10">
@@ -6201,7 +6889,7 @@
       <c r="K46" s="11"/>
       <c r="L46" s="9"/>
       <c r="M46" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K46="","",IF(L46="","参照先未定義",_xlfn.XLOOKUP(L46,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N46" s="11"/>
@@ -6220,7 +6908,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>sns_link.sns_url</v>
       </c>
       <c r="C47" s="10">
@@ -6264,7 +6952,7 @@
       <c r="K47" s="11"/>
       <c r="L47" s="9"/>
       <c r="M47" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K47="","",IF(L47="","参照先未定義",_xlfn.XLOOKUP(L47,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N47" s="11" t="s">
@@ -6283,7 +6971,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>sns_link.create_datetime</v>
       </c>
       <c r="C48" s="10">
@@ -6327,7 +7015,7 @@
       <c r="K48" s="11"/>
       <c r="L48" s="9"/>
       <c r="M48" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K48="","",IF(L48="","参照先未定義",_xlfn.XLOOKUP(L48,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N48" s="11" t="s">
@@ -6348,7 +7036,7 @@
         <v>46</v>
       </c>
       <c r="B49" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>sns_link.create_user</v>
       </c>
       <c r="C49" s="10">
@@ -6392,7 +7080,7 @@
       <c r="K49" s="11"/>
       <c r="L49" s="9"/>
       <c r="M49" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K49="","",IF(L49="","参照先未定義",_xlfn.XLOOKUP(L49,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N49" s="11" t="s">
@@ -6415,7 +7103,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>sns_link.update_datetime</v>
       </c>
       <c r="C50" s="10">
@@ -6459,7 +7147,7 @@
       <c r="K50" s="11"/>
       <c r="L50" s="9"/>
       <c r="M50" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K50="","",IF(L50="","参照先未定義",_xlfn.XLOOKUP(L50,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N50" s="11" t="s">
@@ -6480,7 +7168,7 @@
         <v>46</v>
       </c>
       <c r="B51" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>sns_link.update_user</v>
       </c>
       <c r="C51" s="10">
@@ -6524,7 +7212,7 @@
       <c r="K51" s="11"/>
       <c r="L51" s="9"/>
       <c r="M51" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K51="","",IF(L51="","参照先未定義",_xlfn.XLOOKUP(L51,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N51" s="11" t="s">
@@ -6547,7 +7235,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>sns_link.soft_delete_flag</v>
       </c>
       <c r="C52" s="10">
@@ -6591,7 +7279,7 @@
       <c r="K52" s="11"/>
       <c r="L52" s="9"/>
       <c r="M52" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K52="","",IF(L52="","参照先未定義",_xlfn.XLOOKUP(L52,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N52" s="11" t="s">
@@ -6612,7 +7300,7 @@
         <v>46</v>
       </c>
       <c r="B53" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>bbs_res.bbs_res_uuid</v>
       </c>
       <c r="C53" s="10">
@@ -6657,7 +7345,7 @@
       <c r="K53" s="11"/>
       <c r="L53" s="9"/>
       <c r="M53" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K53="","",IF(L53="","参照先未定義",_xlfn.XLOOKUP(L53,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N53" s="11" t="s">
@@ -6680,7 +7368,7 @@
         <v>46</v>
       </c>
       <c r="B54" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>bbs_res.vtuber_profiles_id</v>
       </c>
       <c r="C54" s="10">
@@ -6728,7 +7416,7 @@
         <v>509</v>
       </c>
       <c r="M54" s="11">
-        <f>_xlfn.SINGLE(IF(K54="","",IF(L54="","参照先未定義",_xlfn.XLOOKUP(L54,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N54" s="11" t="s">
@@ -6747,7 +7435,7 @@
         <v>46</v>
       </c>
       <c r="B55" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>bbs_res.user_id</v>
       </c>
       <c r="C55" s="10">
@@ -6795,7 +7483,7 @@
         <v>506</v>
       </c>
       <c r="M55" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K55="","",IF(L55="","参照先未定義",_xlfn.XLOOKUP(L55,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>149</v>
       </c>
       <c r="N55" s="11" t="s">
@@ -6814,7 +7502,7 @@
         <v>46</v>
       </c>
       <c r="B56" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>bbs_res.res_text</v>
       </c>
       <c r="C56" s="10">
@@ -6858,7 +7546,7 @@
       <c r="K56" s="11"/>
       <c r="L56" s="9"/>
       <c r="M56" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K56="","",IF(L56="","参照先未定義",_xlfn.XLOOKUP(L56,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N56" s="11" t="s">
@@ -6877,7 +7565,7 @@
         <v>46</v>
       </c>
       <c r="B57" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>bbs_res.res_datetime</v>
       </c>
       <c r="C57" s="10">
@@ -6921,7 +7609,7 @@
       <c r="K57" s="11"/>
       <c r="L57" s="9"/>
       <c r="M57" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K57="","",IF(L57="","参照先未定義",_xlfn.XLOOKUP(L57,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N57" s="11" t="s">
@@ -6940,7 +7628,7 @@
         <v>46</v>
       </c>
       <c r="B58" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>bbs_res.create_datetime</v>
       </c>
       <c r="C58" s="10">
@@ -6984,7 +7672,7 @@
       <c r="K58" s="11"/>
       <c r="L58" s="9"/>
       <c r="M58" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K58="","",IF(L58="","参照先未定義",_xlfn.XLOOKUP(L58,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N58" s="11" t="s">
@@ -7005,7 +7693,7 @@
         <v>46</v>
       </c>
       <c r="B59" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>bbs_res.create_user</v>
       </c>
       <c r="C59" s="10">
@@ -7049,7 +7737,7 @@
       <c r="K59" s="11"/>
       <c r="L59" s="9"/>
       <c r="M59" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K59="","",IF(L59="","参照先未定義",_xlfn.XLOOKUP(L59,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N59" s="11" t="s">
@@ -7072,7 +7760,7 @@
         <v>46</v>
       </c>
       <c r="B60" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>bbs_res.update_datetime</v>
       </c>
       <c r="C60" s="10">
@@ -7116,7 +7804,7 @@
       <c r="K60" s="11"/>
       <c r="L60" s="9"/>
       <c r="M60" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K60="","",IF(L60="","参照先未定義",_xlfn.XLOOKUP(L60,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N60" s="11" t="s">
@@ -7137,7 +7825,7 @@
         <v>46</v>
       </c>
       <c r="B61" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>bbs_res.update_user</v>
       </c>
       <c r="C61" s="10">
@@ -7181,7 +7869,7 @@
       <c r="K61" s="11"/>
       <c r="L61" s="9"/>
       <c r="M61" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K61="","",IF(L61="","参照先未定義",_xlfn.XLOOKUP(L61,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N61" s="11" t="s">
@@ -7204,7 +7892,7 @@
         <v>46</v>
       </c>
       <c r="B62" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>bbs_res.soft_delete_flag</v>
       </c>
       <c r="C62" s="10">
@@ -7248,7 +7936,7 @@
       <c r="K62" s="11"/>
       <c r="L62" s="9"/>
       <c r="M62" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K62="","",IF(L62="","参照先未定義",_xlfn.XLOOKUP(L62,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N62" s="11" t="s">
@@ -7269,7 +7957,7 @@
         <v>46</v>
       </c>
       <c r="B63" s="9" t="str">
-        <f t="shared" ref="B63:B125" si="2">D63&amp;"."&amp;F63</f>
+        <f t="shared" ref="B63:B125" si="3">D63&amp;"."&amp;F63</f>
         <v>page_author.page_author_uuid</v>
       </c>
       <c r="C63" s="10">
@@ -7314,7 +8002,7 @@
       <c r="K63" s="11"/>
       <c r="L63" s="9"/>
       <c r="M63" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K63="","",IF(L63="","参照先未定義",_xlfn.XLOOKUP(L63,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N63" s="11" t="s">
@@ -7337,7 +8025,7 @@
         <v>46</v>
       </c>
       <c r="B64" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>page_author.user_id</v>
       </c>
       <c r="C64" s="10">
@@ -7385,7 +8073,7 @@
         <v>506</v>
       </c>
       <c r="M64" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K64="","",IF(L64="","参照先未定義",_xlfn.XLOOKUP(L64,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="1"/>
         <v>149</v>
       </c>
       <c r="N64" s="11" t="s">
@@ -7404,7 +8092,7 @@
         <v>46</v>
       </c>
       <c r="B65" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>page_author.vtuber_profiles_id</v>
       </c>
       <c r="C65" s="10">
@@ -7452,7 +8140,7 @@
         <v>509</v>
       </c>
       <c r="M65" s="11">
-        <f>_xlfn.SINGLE(IF(K65="","",IF(L65="","参照先未定義",_xlfn.XLOOKUP(L65,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N65" s="11" t="s">
@@ -7471,7 +8159,7 @@
         <v>46</v>
       </c>
       <c r="B66" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>page_author.fix_item</v>
       </c>
       <c r="C66" s="10">
@@ -7519,7 +8207,7 @@
         <v>511</v>
       </c>
       <c r="M66" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K66="","",IF(L66="","参照先未定義",_xlfn.XLOOKUP(L66,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ref="M66:M129" ca="1" si="4">_xlfn.SINGLE(IF(K66="","",IF(L66="","参照先未定義",_xlfn.XLOOKUP(L66,B:B,C:C,"エラー"))))</f>
         <v>111</v>
       </c>
       <c r="N66" s="11" t="s">
@@ -7538,7 +8226,7 @@
         <v>46</v>
       </c>
       <c r="B67" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>page_author.fix_before</v>
       </c>
       <c r="C67" s="10">
@@ -7582,7 +8270,7 @@
       <c r="K67" s="11"/>
       <c r="L67" s="9"/>
       <c r="M67" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K67="","",IF(L67="","参照先未定義",_xlfn.XLOOKUP(L67,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N67" s="11" t="s">
@@ -7601,7 +8289,7 @@
         <v>46</v>
       </c>
       <c r="B68" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>page_author.fix_after</v>
       </c>
       <c r="C68" s="10">
@@ -7645,7 +8333,7 @@
       <c r="K68" s="11"/>
       <c r="L68" s="9"/>
       <c r="M68" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K68="","",IF(L68="","参照先未定義",_xlfn.XLOOKUP(L68,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N68" s="11" t="s">
@@ -7664,7 +8352,7 @@
         <v>46</v>
       </c>
       <c r="B69" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>page_author.fix_datetime</v>
       </c>
       <c r="C69" s="10">
@@ -7708,7 +8396,7 @@
       <c r="K69" s="11"/>
       <c r="L69" s="9"/>
       <c r="M69" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K69="","",IF(L69="","参照先未定義",_xlfn.XLOOKUP(L69,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N69" s="11" t="s">
@@ -7729,7 +8417,7 @@
         <v>46</v>
       </c>
       <c r="B70" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>page_author.report_count</v>
       </c>
       <c r="C70" s="10">
@@ -7773,7 +8461,7 @@
       <c r="K70" s="11"/>
       <c r="L70" s="9"/>
       <c r="M70" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K70="","",IF(L70="","参照先未定義",_xlfn.XLOOKUP(L70,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N70" s="11" t="s">
@@ -7794,7 +8482,7 @@
         <v>46</v>
       </c>
       <c r="B71" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>page_author.create_datetime</v>
       </c>
       <c r="C71" s="10">
@@ -7838,7 +8526,7 @@
       <c r="K71" s="11"/>
       <c r="L71" s="9"/>
       <c r="M71" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K71="","",IF(L71="","参照先未定義",_xlfn.XLOOKUP(L71,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N71" s="11" t="s">
@@ -7859,7 +8547,7 @@
         <v>46</v>
       </c>
       <c r="B72" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>page_author.create_user</v>
       </c>
       <c r="C72" s="10">
@@ -7903,7 +8591,7 @@
       <c r="K72" s="11"/>
       <c r="L72" s="9"/>
       <c r="M72" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K72="","",IF(L72="","参照先未定義",_xlfn.XLOOKUP(L72,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N72" s="11" t="s">
@@ -7926,7 +8614,7 @@
         <v>46</v>
       </c>
       <c r="B73" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>page_author.update_datetime</v>
       </c>
       <c r="C73" s="10">
@@ -7970,7 +8658,7 @@
       <c r="K73" s="11"/>
       <c r="L73" s="9"/>
       <c r="M73" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K73="","",IF(L73="","参照先未定義",_xlfn.XLOOKUP(L73,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N73" s="11" t="s">
@@ -7991,7 +8679,7 @@
         <v>46</v>
       </c>
       <c r="B74" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>page_author.update_user</v>
       </c>
       <c r="C74" s="10">
@@ -8035,7 +8723,7 @@
       <c r="K74" s="11"/>
       <c r="L74" s="9"/>
       <c r="M74" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K74="","",IF(L74="","参照先未定義",_xlfn.XLOOKUP(L74,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N74" s="11" t="s">
@@ -8058,7 +8746,7 @@
         <v>46</v>
       </c>
       <c r="B75" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>page_author.soft_delete_flag</v>
       </c>
       <c r="C75" s="10">
@@ -8102,7 +8790,7 @@
       <c r="K75" s="11"/>
       <c r="L75" s="9"/>
       <c r="M75" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K75="","",IF(L75="","参照先未定義",_xlfn.XLOOKUP(L75,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N75" s="11" t="s">
@@ -8123,7 +8811,7 @@
         <v>46</v>
       </c>
       <c r="B76" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>contact.contact_uuid</v>
       </c>
       <c r="C76" s="10">
@@ -8168,7 +8856,7 @@
       <c r="K76" s="11"/>
       <c r="L76" s="9"/>
       <c r="M76" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K76="","",IF(L76="","参照先未定義",_xlfn.XLOOKUP(L76,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N76" s="11" t="s">
@@ -8191,7 +8879,7 @@
         <v>46</v>
       </c>
       <c r="B77" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>contact.mail_address</v>
       </c>
       <c r="C77" s="10">
@@ -8235,7 +8923,7 @@
       <c r="K77" s="11"/>
       <c r="L77" s="9"/>
       <c r="M77" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K77="","",IF(L77="","参照先未定義",_xlfn.XLOOKUP(L77,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N77" s="11" t="s">
@@ -8256,7 +8944,7 @@
         <v>46</v>
       </c>
       <c r="B78" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>contact.subject</v>
       </c>
       <c r="C78" s="10">
@@ -8300,7 +8988,7 @@
       <c r="K78" s="11"/>
       <c r="L78" s="9"/>
       <c r="M78" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K78="","",IF(L78="","参照先未定義",_xlfn.XLOOKUP(L78,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N78" s="11" t="s">
@@ -8321,7 +9009,7 @@
         <v>46</v>
       </c>
       <c r="B79" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>contact.contact_detail</v>
       </c>
       <c r="C79" s="10">
@@ -8365,7 +9053,7 @@
       <c r="K79" s="11"/>
       <c r="L79" s="9"/>
       <c r="M79" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K79="","",IF(L79="","参照先未定義",_xlfn.XLOOKUP(L79,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N79" s="11" t="s">
@@ -8386,7 +9074,7 @@
         <v>46</v>
       </c>
       <c r="B80" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>contact.priority_physical_name</v>
       </c>
       <c r="C80" s="10">
@@ -8401,7 +9089,7 @@
         <f t="array" aca="1" ref="E80" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>問い合わせ</v>
       </c>
-      <c r="F80" s="21" t="s">
+      <c r="F80" s="11" t="s">
         <v>173</v>
       </c>
       <c r="G80" s="11" t="s">
@@ -8434,7 +9122,7 @@
         <v>513</v>
       </c>
       <c r="M80" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K80="","",IF(L80="","参照先未定義",_xlfn.XLOOKUP(L80,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="4"/>
         <v>86</v>
       </c>
       <c r="N80" s="11"/>
@@ -8451,7 +9139,7 @@
         <v>46</v>
       </c>
       <c r="B81" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>contact.response_status_physical_name</v>
       </c>
       <c r="C81" s="10">
@@ -8466,7 +9154,7 @@
         <f t="array" aca="1" ref="E81" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>問い合わせ</v>
       </c>
-      <c r="F81" s="21" t="s">
+      <c r="F81" s="11" t="s">
         <v>175</v>
       </c>
       <c r="G81" s="11" t="s">
@@ -8499,7 +9187,7 @@
         <v>512</v>
       </c>
       <c r="M81" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K81="","",IF(L81="","参照先未定義",_xlfn.XLOOKUP(L81,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="4"/>
         <v>94</v>
       </c>
       <c r="N81" s="11"/>
@@ -8516,7 +9204,7 @@
         <v>46</v>
       </c>
       <c r="B82" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>contact.create_datetime</v>
       </c>
       <c r="C82" s="10">
@@ -8560,7 +9248,7 @@
       <c r="K82" s="11"/>
       <c r="L82" s="9"/>
       <c r="M82" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K82="","",IF(L82="","参照先未定義",_xlfn.XLOOKUP(L82,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N82" s="11" t="s">
@@ -8581,7 +9269,7 @@
         <v>46</v>
       </c>
       <c r="B83" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>contact.create_user</v>
       </c>
       <c r="C83" s="10">
@@ -8625,7 +9313,7 @@
       <c r="K83" s="11"/>
       <c r="L83" s="9"/>
       <c r="M83" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K83="","",IF(L83="","参照先未定義",_xlfn.XLOOKUP(L83,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N83" s="11" t="s">
@@ -8648,7 +9336,7 @@
         <v>46</v>
       </c>
       <c r="B84" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>contact.update_datetime</v>
       </c>
       <c r="C84" s="10">
@@ -8692,7 +9380,7 @@
       <c r="K84" s="11"/>
       <c r="L84" s="9"/>
       <c r="M84" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K84="","",IF(L84="","参照先未定義",_xlfn.XLOOKUP(L84,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N84" s="11" t="s">
@@ -8713,7 +9401,7 @@
         <v>46</v>
       </c>
       <c r="B85" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>contact.update_user</v>
       </c>
       <c r="C85" s="10">
@@ -8757,7 +9445,7 @@
       <c r="K85" s="11"/>
       <c r="L85" s="9"/>
       <c r="M85" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K85="","",IF(L85="","参照先未定義",_xlfn.XLOOKUP(L85,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N85" s="11" t="s">
@@ -8780,7 +9468,7 @@
         <v>46</v>
       </c>
       <c r="B86" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>contact.soft_delete_flag</v>
       </c>
       <c r="C86" s="10">
@@ -8824,7 +9512,7 @@
       <c r="K86" s="11"/>
       <c r="L86" s="9"/>
       <c r="M86" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K86="","",IF(L86="","参照先未定義",_xlfn.XLOOKUP(L86,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N86" s="11" t="s">
@@ -8845,7 +9533,7 @@
         <v>46</v>
       </c>
       <c r="B87" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>priority.priority_uuid</v>
       </c>
       <c r="C87" s="10">
@@ -8890,7 +9578,7 @@
       <c r="K87" s="11"/>
       <c r="L87" s="9"/>
       <c r="M87" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K87="","",IF(L87="","参照先未定義",_xlfn.XLOOKUP(L87,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N87" s="11" t="s">
@@ -8913,7 +9601,7 @@
         <v>46</v>
       </c>
       <c r="B88" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>priority.priority_physical_name</v>
       </c>
       <c r="C88" s="10">
@@ -8957,7 +9645,7 @@
       <c r="K88" s="11"/>
       <c r="L88" s="9"/>
       <c r="M88" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K88="","",IF(L88="","参照先未定義",_xlfn.XLOOKUP(L88,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N88" s="11" t="s">
@@ -8978,7 +9666,7 @@
         <v>46</v>
       </c>
       <c r="B89" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>priority.priority_logical_name</v>
       </c>
       <c r="C89" s="10">
@@ -9022,7 +9710,7 @@
       <c r="K89" s="11"/>
       <c r="L89" s="9"/>
       <c r="M89" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K89="","",IF(L89="","参照先未定義",_xlfn.XLOOKUP(L89,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N89" s="11"/>
@@ -9041,7 +9729,7 @@
         <v>46</v>
       </c>
       <c r="B90" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>priority.create_datetime</v>
       </c>
       <c r="C90" s="10">
@@ -9085,7 +9773,7 @@
       <c r="K90" s="11"/>
       <c r="L90" s="9"/>
       <c r="M90" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K90="","",IF(L90="","参照先未定義",_xlfn.XLOOKUP(L90,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N90" s="11" t="s">
@@ -9106,7 +9794,7 @@
         <v>46</v>
       </c>
       <c r="B91" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>priority.create_user</v>
       </c>
       <c r="C91" s="10">
@@ -9150,7 +9838,7 @@
       <c r="K91" s="11"/>
       <c r="L91" s="9"/>
       <c r="M91" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K91="","",IF(L91="","参照先未定義",_xlfn.XLOOKUP(L91,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N91" s="11" t="s">
@@ -9173,7 +9861,7 @@
         <v>46</v>
       </c>
       <c r="B92" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>priority.update_datetime</v>
       </c>
       <c r="C92" s="10">
@@ -9217,7 +9905,7 @@
       <c r="K92" s="11"/>
       <c r="L92" s="9"/>
       <c r="M92" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K92="","",IF(L92="","参照先未定義",_xlfn.XLOOKUP(L92,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N92" s="11" t="s">
@@ -9238,7 +9926,7 @@
         <v>46</v>
       </c>
       <c r="B93" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>priority.update_user</v>
       </c>
       <c r="C93" s="10">
@@ -9282,7 +9970,7 @@
       <c r="K93" s="11"/>
       <c r="L93" s="9"/>
       <c r="M93" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K93="","",IF(L93="","参照先未定義",_xlfn.XLOOKUP(L93,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N93" s="11" t="s">
@@ -9305,7 +9993,7 @@
         <v>46</v>
       </c>
       <c r="B94" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>priority.soft_delete_flag</v>
       </c>
       <c r="C94" s="10">
@@ -9349,7 +10037,7 @@
       <c r="K94" s="11"/>
       <c r="L94" s="9"/>
       <c r="M94" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K94="","",IF(L94="","参照先未定義",_xlfn.XLOOKUP(L94,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N94" s="11" t="s">
@@ -9370,7 +10058,7 @@
         <v>46</v>
       </c>
       <c r="B95" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>response_status.response_status_uuid</v>
       </c>
       <c r="C95" s="10">
@@ -9415,7 +10103,7 @@
       <c r="K95" s="11"/>
       <c r="L95" s="9"/>
       <c r="M95" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K95="","",IF(L95="","参照先未定義",_xlfn.XLOOKUP(L95,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N95" s="11" t="s">
@@ -9438,7 +10126,7 @@
         <v>46</v>
       </c>
       <c r="B96" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>response_status.response_status_physical_name</v>
       </c>
       <c r="C96" s="10">
@@ -9482,7 +10170,7 @@
       <c r="K96" s="11"/>
       <c r="L96" s="9"/>
       <c r="M96" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K96="","",IF(L96="","参照先未定義",_xlfn.XLOOKUP(L96,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N96" s="11" t="s">
@@ -9503,7 +10191,7 @@
         <v>46</v>
       </c>
       <c r="B97" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>response_status.response_status_logical_name</v>
       </c>
       <c r="C97" s="10">
@@ -9547,7 +10235,7 @@
       <c r="K97" s="11"/>
       <c r="L97" s="9"/>
       <c r="M97" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K97="","",IF(L97="","参照先未定義",_xlfn.XLOOKUP(L97,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N97" s="11"/>
@@ -9566,7 +10254,7 @@
         <v>46</v>
       </c>
       <c r="B98" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>response_status.create_datetime</v>
       </c>
       <c r="C98" s="10">
@@ -9610,7 +10298,7 @@
       <c r="K98" s="11"/>
       <c r="L98" s="9"/>
       <c r="M98" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K98="","",IF(L98="","参照先未定義",_xlfn.XLOOKUP(L98,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N98" s="11" t="s">
@@ -9631,7 +10319,7 @@
         <v>46</v>
       </c>
       <c r="B99" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>response_status.create_user</v>
       </c>
       <c r="C99" s="10">
@@ -9675,7 +10363,7 @@
       <c r="K99" s="11"/>
       <c r="L99" s="9"/>
       <c r="M99" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K99="","",IF(L99="","参照先未定義",_xlfn.XLOOKUP(L99,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N99" s="11" t="s">
@@ -9698,7 +10386,7 @@
         <v>46</v>
       </c>
       <c r="B100" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>response_status.update_datetime</v>
       </c>
       <c r="C100" s="10">
@@ -9742,7 +10430,7 @@
       <c r="K100" s="11"/>
       <c r="L100" s="9"/>
       <c r="M100" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K100="","",IF(L100="","参照先未定義",_xlfn.XLOOKUP(L100,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N100" s="11" t="s">
@@ -9763,7 +10451,7 @@
         <v>46</v>
       </c>
       <c r="B101" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>response_status.update_user</v>
       </c>
       <c r="C101" s="10">
@@ -9807,7 +10495,7 @@
       <c r="K101" s="11"/>
       <c r="L101" s="9"/>
       <c r="M101" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K101="","",IF(L101="","参照先未定義",_xlfn.XLOOKUP(L101,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N101" s="11" t="s">
@@ -9830,7 +10518,7 @@
         <v>46</v>
       </c>
       <c r="B102" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>response_status.soft_delete_flag</v>
       </c>
       <c r="C102" s="10">
@@ -9874,7 +10562,7 @@
       <c r="K102" s="11"/>
       <c r="L102" s="9"/>
       <c r="M102" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K102="","",IF(L102="","参照先未定義",_xlfn.XLOOKUP(L102,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N102" s="11" t="s">
@@ -9895,7 +10583,7 @@
         <v>46</v>
       </c>
       <c r="B103" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>language.language_uuid</v>
       </c>
       <c r="C103" s="10">
@@ -9940,7 +10628,7 @@
       <c r="K103" s="11"/>
       <c r="L103" s="9"/>
       <c r="M103" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K103="","",IF(L103="","参照先未定義",_xlfn.XLOOKUP(L103,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N103" s="11" t="s">
@@ -9963,7 +10651,7 @@
         <v>46</v>
       </c>
       <c r="B104" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>language.language_physical_name</v>
       </c>
       <c r="C104" s="10">
@@ -10007,7 +10695,7 @@
       <c r="K104" s="11"/>
       <c r="L104" s="9"/>
       <c r="M104" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K104="","",IF(L104="","参照先未定義",_xlfn.XLOOKUP(L104,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N104" s="11" t="s">
@@ -10022,7 +10710,7 @@
       <c r="S104" s="9"/>
       <c r="T104" s="9"/>
       <c r="U104" s="11" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10030,7 +10718,7 @@
         <v>46</v>
       </c>
       <c r="B105" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>language.language_image</v>
       </c>
       <c r="C105" s="10">
@@ -10074,7 +10762,7 @@
       <c r="K105" s="11"/>
       <c r="L105" s="9"/>
       <c r="M105" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K105="","",IF(L105="","参照先未定義",_xlfn.XLOOKUP(L105,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N105" s="11"/>
@@ -10093,7 +10781,7 @@
         <v>46</v>
       </c>
       <c r="B106" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>language.enable</v>
       </c>
       <c r="C106" s="10">
@@ -10137,7 +10825,7 @@
       <c r="K106" s="11"/>
       <c r="L106" s="9"/>
       <c r="M106" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K106="","",IF(L106="","参照先未定義",_xlfn.XLOOKUP(L106,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N106" s="11" t="s">
@@ -10158,7 +10846,7 @@
         <v>46</v>
       </c>
       <c r="B107" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>language.create_datetime</v>
       </c>
       <c r="C107" s="10">
@@ -10202,7 +10890,7 @@
       <c r="K107" s="11"/>
       <c r="L107" s="9"/>
       <c r="M107" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K107="","",IF(L107="","参照先未定義",_xlfn.XLOOKUP(L107,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N107" s="11" t="s">
@@ -10223,7 +10911,7 @@
         <v>46</v>
       </c>
       <c r="B108" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>language.create_user</v>
       </c>
       <c r="C108" s="10">
@@ -10267,7 +10955,7 @@
       <c r="K108" s="11"/>
       <c r="L108" s="9"/>
       <c r="M108" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K108="","",IF(L108="","参照先未定義",_xlfn.XLOOKUP(L108,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N108" s="11" t="s">
@@ -10290,7 +10978,7 @@
         <v>46</v>
       </c>
       <c r="B109" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>language.update_datetime</v>
       </c>
       <c r="C109" s="10">
@@ -10334,7 +11022,7 @@
       <c r="K109" s="11"/>
       <c r="L109" s="9"/>
       <c r="M109" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K109="","",IF(L109="","参照先未定義",_xlfn.XLOOKUP(L109,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N109" s="11" t="s">
@@ -10355,7 +11043,7 @@
         <v>46</v>
       </c>
       <c r="B110" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>language.update_user</v>
       </c>
       <c r="C110" s="10">
@@ -10399,7 +11087,7 @@
       <c r="K110" s="11"/>
       <c r="L110" s="9"/>
       <c r="M110" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K110="","",IF(L110="","参照先未定義",_xlfn.XLOOKUP(L110,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N110" s="11" t="s">
@@ -10422,7 +11110,7 @@
         <v>46</v>
       </c>
       <c r="B111" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>language.soft_delete_flag</v>
       </c>
       <c r="C111" s="10">
@@ -10466,7 +11154,7 @@
       <c r="K111" s="11"/>
       <c r="L111" s="9"/>
       <c r="M111" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K111="","",IF(L111="","参照先未定義",_xlfn.XLOOKUP(L111,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N111" s="11" t="s">
@@ -10487,7 +11175,7 @@
         <v>46</v>
       </c>
       <c r="B112" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>screen_word.screen_word_uuid</v>
       </c>
       <c r="C112" s="10">
@@ -10532,7 +11220,7 @@
       <c r="K112" s="11"/>
       <c r="L112" s="9"/>
       <c r="M112" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K112="","",IF(L112="","参照先未定義",_xlfn.XLOOKUP(L112,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N112" s="11" t="s">
@@ -10555,7 +11243,7 @@
         <v>46</v>
       </c>
       <c r="B113" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>screen_word.language_physical_name</v>
       </c>
       <c r="C113" s="10">
@@ -10570,7 +11258,7 @@
         <f t="array" aca="1" ref="E113" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>画面文言</v>
       </c>
-      <c r="F113" s="21" t="s">
+      <c r="F113" s="11" t="s">
         <v>187</v>
       </c>
       <c r="G113" s="11" t="s">
@@ -10603,7 +11291,7 @@
         <v>514</v>
       </c>
       <c r="M113" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K113="","",IF(L113="","参照先未定義",_xlfn.XLOOKUP(L113,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="4"/>
         <v>102</v>
       </c>
       <c r="N113" s="11"/>
@@ -10620,7 +11308,7 @@
         <v>46</v>
       </c>
       <c r="B114" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>screen_word.message_id</v>
       </c>
       <c r="C114" s="10">
@@ -10661,21 +11349,17 @@
         <v>128</v>
       </c>
       <c r="J114" s="11"/>
-      <c r="K114" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="L114" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="M114" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K114="","",IF(L114="","参照先未定義",_xlfn.XLOOKUP(L114,B:B,C:C,"エラー"))))</f>
-        <v>208</v>
+      <c r="K114" s="11"/>
+      <c r="L114" s="9"/>
+      <c r="M114" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N114" s="11"/>
       <c r="O114" s="11"/>
       <c r="P114" s="11"/>
       <c r="Q114" s="11" t="s">
-        <v>198</v>
+        <v>582</v>
       </c>
       <c r="R114" s="9"/>
       <c r="S114" s="9"/>
@@ -10687,7 +11371,7 @@
         <v>46</v>
       </c>
       <c r="B115" s="9" t="str">
-        <f t="shared" ref="B115" ca="1" si="3">D115&amp;"."&amp;F115</f>
+        <f t="shared" ref="B115" ca="1" si="5">D115&amp;"."&amp;F115</f>
         <v>screen_word.display_message</v>
       </c>
       <c r="C115" s="10">
@@ -10731,7 +11415,7 @@
       <c r="K115" s="11"/>
       <c r="L115" s="9"/>
       <c r="M115" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K115="","",IF(L115="","参照先未定義",_xlfn.XLOOKUP(L115,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N115" s="11"/>
@@ -10746,9 +11430,11 @@
       <c r="U115" s="11"/>
     </row>
     <row r="116" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="9"/>
+      <c r="A116" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="B116" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>screen_word.message_type</v>
       </c>
       <c r="C116" s="10">
@@ -10770,7 +11456,7 @@
         <v>523</v>
       </c>
       <c r="H116" s="11" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I116" s="11" t="str">
         <f>_xlfn.LET(
@@ -10792,20 +11478,20 @@
       <c r="K116" s="11"/>
       <c r="L116" s="9"/>
       <c r="M116" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K116="","",IF(L116="","参照先未定義",_xlfn.XLOOKUP(L116,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N116" s="11"/>
       <c r="O116" s="11"/>
       <c r="P116" s="11"/>
       <c r="Q116" s="11" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="R116" s="9"/>
       <c r="S116" s="9"/>
       <c r="T116" s="9"/>
       <c r="U116" s="11" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="117" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10813,7 +11499,7 @@
         <v>46</v>
       </c>
       <c r="B117" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>screen_word.create_datetime</v>
       </c>
       <c r="C117" s="10">
@@ -10857,7 +11543,7 @@
       <c r="K117" s="11"/>
       <c r="L117" s="9"/>
       <c r="M117" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K117="","",IF(L117="","参照先未定義",_xlfn.XLOOKUP(L117,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N117" s="11" t="s">
@@ -10878,7 +11564,7 @@
         <v>46</v>
       </c>
       <c r="B118" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>screen_word.create_user</v>
       </c>
       <c r="C118" s="10">
@@ -10922,7 +11608,7 @@
       <c r="K118" s="11"/>
       <c r="L118" s="9"/>
       <c r="M118" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K118="","",IF(L118="","参照先未定義",_xlfn.XLOOKUP(L118,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N118" s="11" t="s">
@@ -10945,7 +11631,7 @@
         <v>46</v>
       </c>
       <c r="B119" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>screen_word.update_datetime</v>
       </c>
       <c r="C119" s="10">
@@ -10989,7 +11675,7 @@
       <c r="K119" s="11"/>
       <c r="L119" s="9"/>
       <c r="M119" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K119="","",IF(L119="","参照先未定義",_xlfn.XLOOKUP(L119,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N119" s="11" t="s">
@@ -11010,7 +11696,7 @@
         <v>46</v>
       </c>
       <c r="B120" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>screen_word.update_user</v>
       </c>
       <c r="C120" s="10">
@@ -11054,7 +11740,7 @@
       <c r="K120" s="11"/>
       <c r="L120" s="9"/>
       <c r="M120" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K120="","",IF(L120="","参照先未定義",_xlfn.XLOOKUP(L120,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N120" s="11" t="s">
@@ -11077,7 +11763,7 @@
         <v>46</v>
       </c>
       <c r="B121" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>screen_word.soft_delete_flag</v>
       </c>
       <c r="C121" s="10">
@@ -11121,7 +11807,7 @@
       <c r="K121" s="11"/>
       <c r="L121" s="9"/>
       <c r="M121" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K121="","",IF(L121="","参照先未定義",_xlfn.XLOOKUP(L121,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N121" s="11" t="s">
@@ -11142,7 +11828,7 @@
         <v>46</v>
       </c>
       <c r="B122" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>sns_support.sns_support_uuid</v>
       </c>
       <c r="C122" s="10">
@@ -11187,7 +11873,7 @@
       <c r="K122" s="11"/>
       <c r="L122" s="9"/>
       <c r="M122" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K122="","",IF(L122="","参照先未定義",_xlfn.XLOOKUP(L122,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N122" s="11" t="s">
@@ -11210,7 +11896,7 @@
         <v>46</v>
       </c>
       <c r="B123" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>sns_support.sns_name_physical_name</v>
       </c>
       <c r="C123" s="10">
@@ -11225,7 +11911,7 @@
         <f t="array" aca="1" ref="E123" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>サポートするSNS</v>
       </c>
-      <c r="F123" s="21" t="s">
+      <c r="F123" s="11" t="s">
         <v>203</v>
       </c>
       <c r="G123" s="11" t="s">
@@ -11258,7 +11944,7 @@
         <v>522</v>
       </c>
       <c r="M123" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K123="","",IF(L123="","参照先未定義",_xlfn.XLOOKUP(L123,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="4"/>
         <v>102</v>
       </c>
       <c r="N123" s="11" t="s">
@@ -11279,7 +11965,7 @@
         <v>46</v>
       </c>
       <c r="B124" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>sns_support.image_id</v>
       </c>
       <c r="C124" s="10">
@@ -11327,7 +12013,7 @@
         <v>515</v>
       </c>
       <c r="M124" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K124="","",IF(L124="","参照先未定義",_xlfn.XLOOKUP(L124,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="4"/>
         <v>193</v>
       </c>
       <c r="N124" s="11" t="s">
@@ -11350,7 +12036,7 @@
         <v>46</v>
       </c>
       <c r="B125" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="3"/>
         <v>sns_support.use_login_service</v>
       </c>
       <c r="C125" s="10">
@@ -11394,7 +12080,7 @@
       <c r="K125" s="11"/>
       <c r="L125" s="9"/>
       <c r="M125" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K125="","",IF(L125="","参照先未定義",_xlfn.XLOOKUP(L125,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N125" s="11" t="s">
@@ -11415,7 +12101,7 @@
         <v>46</v>
       </c>
       <c r="B126" s="9" t="str">
-        <f t="shared" ref="B126:B182" ca="1" si="4">D126&amp;"."&amp;F126</f>
+        <f t="shared" ref="B126:B182" ca="1" si="6">D126&amp;"."&amp;F126</f>
         <v>sns_support.use_sns_link</v>
       </c>
       <c r="C126" s="10">
@@ -11459,7 +12145,7 @@
       <c r="K126" s="11"/>
       <c r="L126" s="9"/>
       <c r="M126" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K126="","",IF(L126="","参照先未定義",_xlfn.XLOOKUP(L126,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N126" s="11" t="s">
@@ -11480,7 +12166,7 @@
         <v>46</v>
       </c>
       <c r="B127" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>sns_support.create_datetime</v>
       </c>
       <c r="C127" s="10">
@@ -11524,7 +12210,7 @@
       <c r="K127" s="11"/>
       <c r="L127" s="9"/>
       <c r="M127" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K127="","",IF(L127="","参照先未定義",_xlfn.XLOOKUP(L127,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N127" s="11" t="s">
@@ -11545,7 +12231,7 @@
         <v>46</v>
       </c>
       <c r="B128" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>sns_support.create_user</v>
       </c>
       <c r="C128" s="10">
@@ -11589,7 +12275,7 @@
       <c r="K128" s="11"/>
       <c r="L128" s="9"/>
       <c r="M128" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K128="","",IF(L128="","参照先未定義",_xlfn.XLOOKUP(L128,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N128" s="11" t="s">
@@ -11612,7 +12298,7 @@
         <v>46</v>
       </c>
       <c r="B129" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>sns_support.update_datetime</v>
       </c>
       <c r="C129" s="10">
@@ -11656,7 +12342,7 @@
       <c r="K129" s="11"/>
       <c r="L129" s="9"/>
       <c r="M129" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K129="","",IF(L129="","参照先未定義",_xlfn.XLOOKUP(L129,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N129" s="11" t="s">
@@ -11677,7 +12363,7 @@
         <v>46</v>
       </c>
       <c r="B130" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>sns_support.update_user</v>
       </c>
       <c r="C130" s="10">
@@ -11721,7 +12407,7 @@
       <c r="K130" s="11"/>
       <c r="L130" s="9"/>
       <c r="M130" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K130="","",IF(L130="","参照先未定義",_xlfn.XLOOKUP(L130,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ref="M130:M193" si="7">_xlfn.SINGLE(IF(K130="","",IF(L130="","参照先未定義",_xlfn.XLOOKUP(L130,B:B,C:C,"エラー"))))</f>
         <v/>
       </c>
       <c r="N130" s="11" t="s">
@@ -11744,7 +12430,7 @@
         <v>46</v>
       </c>
       <c r="B131" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>sns_support.soft_delete_flag</v>
       </c>
       <c r="C131" s="10">
@@ -11788,7 +12474,7 @@
       <c r="K131" s="11"/>
       <c r="L131" s="9"/>
       <c r="M131" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K131="","",IF(L131="","参照先未定義",_xlfn.XLOOKUP(L131,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N131" s="11" t="s">
@@ -11809,7 +12495,7 @@
         <v>46</v>
       </c>
       <c r="B132" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>profile_report.profile_report_uuid</v>
       </c>
       <c r="C132" s="10">
@@ -11854,7 +12540,7 @@
       <c r="K132" s="11"/>
       <c r="L132" s="9"/>
       <c r="M132" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K132="","",IF(L132="","参照先未定義",_xlfn.XLOOKUP(L132,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N132" s="11" t="s">
@@ -11877,7 +12563,7 @@
         <v>46</v>
       </c>
       <c r="B133" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>profile_report.user_id</v>
       </c>
       <c r="C133" s="10">
@@ -11925,7 +12611,7 @@
         <v>506</v>
       </c>
       <c r="M133" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K133="","",IF(L133="","参照先未定義",_xlfn.XLOOKUP(L133,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="7"/>
         <v>149</v>
       </c>
       <c r="N133" s="11"/>
@@ -11942,7 +12628,7 @@
         <v>46</v>
       </c>
       <c r="B134" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>profile_report.vtuber_profiles_id</v>
       </c>
       <c r="C134" s="10">
@@ -11990,7 +12676,7 @@
         <v>509</v>
       </c>
       <c r="M134" s="11">
-        <f>_xlfn.SINGLE(IF(K134="","",IF(L134="","参照先未定義",_xlfn.XLOOKUP(L134,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N134" s="11" t="s">
@@ -12009,7 +12695,7 @@
         <v>46</v>
       </c>
       <c r="B135" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>profile_report.report_reason_physical_name</v>
       </c>
       <c r="C135" s="10">
@@ -12024,7 +12710,7 @@
         <f t="array" aca="1" ref="E135" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>プロフィール通報</v>
       </c>
-      <c r="F135" s="21" t="s">
+      <c r="F135" s="11" t="s">
         <v>214</v>
       </c>
       <c r="G135" s="11" t="s">
@@ -12057,7 +12743,7 @@
         <v>516</v>
       </c>
       <c r="M135" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K135="","",IF(L135="","参照先未定義",_xlfn.XLOOKUP(L135,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="7"/>
         <v>142</v>
       </c>
       <c r="N135" s="11" t="s">
@@ -12078,7 +12764,7 @@
         <v>46</v>
       </c>
       <c r="B136" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>profile_report.report_detail</v>
       </c>
       <c r="C136" s="10">
@@ -12122,7 +12808,7 @@
       <c r="K136" s="11"/>
       <c r="L136" s="9"/>
       <c r="M136" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K136="","",IF(L136="","参照先未定義",_xlfn.XLOOKUP(L136,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N136" s="11" t="s">
@@ -12143,7 +12829,7 @@
         <v>46</v>
       </c>
       <c r="B137" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>profile_report.report_datetime</v>
       </c>
       <c r="C137" s="10">
@@ -12187,7 +12873,7 @@
       <c r="K137" s="11"/>
       <c r="L137" s="9"/>
       <c r="M137" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K137="","",IF(L137="","参照先未定義",_xlfn.XLOOKUP(L137,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N137" s="11" t="s">
@@ -12208,7 +12894,7 @@
         <v>46</v>
       </c>
       <c r="B138" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>profile_report.create_datetime</v>
       </c>
       <c r="C138" s="10">
@@ -12252,7 +12938,7 @@
       <c r="K138" s="11"/>
       <c r="L138" s="9"/>
       <c r="M138" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K138="","",IF(L138="","参照先未定義",_xlfn.XLOOKUP(L138,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N138" s="11" t="s">
@@ -12273,7 +12959,7 @@
         <v>46</v>
       </c>
       <c r="B139" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>profile_report.create_user</v>
       </c>
       <c r="C139" s="10">
@@ -12317,7 +13003,7 @@
       <c r="K139" s="11"/>
       <c r="L139" s="9"/>
       <c r="M139" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K139="","",IF(L139="","参照先未定義",_xlfn.XLOOKUP(L139,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N139" s="11" t="s">
@@ -12340,7 +13026,7 @@
         <v>46</v>
       </c>
       <c r="B140" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>profile_report.update_datetime</v>
       </c>
       <c r="C140" s="10">
@@ -12384,7 +13070,7 @@
       <c r="K140" s="11"/>
       <c r="L140" s="9"/>
       <c r="M140" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K140="","",IF(L140="","参照先未定義",_xlfn.XLOOKUP(L140,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N140" s="11" t="s">
@@ -12405,7 +13091,7 @@
         <v>46</v>
       </c>
       <c r="B141" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>profile_report.update_user</v>
       </c>
       <c r="C141" s="10">
@@ -12449,7 +13135,7 @@
       <c r="K141" s="11"/>
       <c r="L141" s="9"/>
       <c r="M141" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K141="","",IF(L141="","参照先未定義",_xlfn.XLOOKUP(L141,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N141" s="11" t="s">
@@ -12472,7 +13158,7 @@
         <v>46</v>
       </c>
       <c r="B142" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>profile_report.soft_delete_flag</v>
       </c>
       <c r="C142" s="10">
@@ -12516,7 +13202,7 @@
       <c r="K142" s="11"/>
       <c r="L142" s="9"/>
       <c r="M142" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K142="","",IF(L142="","参照先未定義",_xlfn.XLOOKUP(L142,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N142" s="11" t="s">
@@ -12537,7 +13223,7 @@
         <v>46</v>
       </c>
       <c r="B143" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>report_reason.report_reason_uuid</v>
       </c>
       <c r="C143" s="10">
@@ -12582,7 +13268,7 @@
       <c r="K143" s="11"/>
       <c r="L143" s="9"/>
       <c r="M143" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K143="","",IF(L143="","参照先未定義",_xlfn.XLOOKUP(L143,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N143" s="11" t="s">
@@ -12605,7 +13291,7 @@
         <v>46</v>
       </c>
       <c r="B144" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>report_reason.report_reason_physical_name</v>
       </c>
       <c r="C144" s="10">
@@ -12620,7 +13306,7 @@
         <f t="array" aca="1" ref="E144" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>通報理由</v>
       </c>
-      <c r="F144" s="21" t="s">
+      <c r="F144" s="11" t="s">
         <v>214</v>
       </c>
       <c r="G144" s="11" t="s">
@@ -12649,7 +13335,7 @@
       <c r="K144" s="11"/>
       <c r="L144" s="9"/>
       <c r="M144" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K144="","",IF(L144="","参照先未定義",_xlfn.XLOOKUP(L144,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N144" s="11" t="s">
@@ -12664,7 +13350,7 @@
       <c r="S144" s="9"/>
       <c r="T144" s="9"/>
       <c r="U144" s="11" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="145" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12672,7 +13358,7 @@
         <v>46</v>
       </c>
       <c r="B145" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>report_reason.create_datetime</v>
       </c>
       <c r="C145" s="10">
@@ -12716,7 +13402,7 @@
       <c r="K145" s="11"/>
       <c r="L145" s="9"/>
       <c r="M145" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K145="","",IF(L145="","参照先未定義",_xlfn.XLOOKUP(L145,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N145" s="11" t="s">
@@ -12737,7 +13423,7 @@
         <v>46</v>
       </c>
       <c r="B146" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>report_reason.create_user</v>
       </c>
       <c r="C146" s="10">
@@ -12781,7 +13467,7 @@
       <c r="K146" s="11"/>
       <c r="L146" s="9"/>
       <c r="M146" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K146="","",IF(L146="","参照先未定義",_xlfn.XLOOKUP(L146,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N146" s="11" t="s">
@@ -12804,7 +13490,7 @@
         <v>46</v>
       </c>
       <c r="B147" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>report_reason.update_datetime</v>
       </c>
       <c r="C147" s="10">
@@ -12848,7 +13534,7 @@
       <c r="K147" s="11"/>
       <c r="L147" s="9"/>
       <c r="M147" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K147="","",IF(L147="","参照先未定義",_xlfn.XLOOKUP(L147,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N147" s="11" t="s">
@@ -12869,7 +13555,7 @@
         <v>46</v>
       </c>
       <c r="B148" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>report_reason.update_user</v>
       </c>
       <c r="C148" s="10">
@@ -12913,7 +13599,7 @@
       <c r="K148" s="11"/>
       <c r="L148" s="9"/>
       <c r="M148" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K148="","",IF(L148="","参照先未定義",_xlfn.XLOOKUP(L148,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N148" s="11" t="s">
@@ -12936,7 +13622,7 @@
         <v>46</v>
       </c>
       <c r="B149" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>report_reason.soft_delete_flag</v>
       </c>
       <c r="C149" s="10">
@@ -12980,7 +13666,7 @@
       <c r="K149" s="11"/>
       <c r="L149" s="9"/>
       <c r="M149" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K149="","",IF(L149="","参照先未定義",_xlfn.XLOOKUP(L149,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N149" s="11" t="s">
@@ -13001,7 +13687,7 @@
         <v>46</v>
       </c>
       <c r="B150" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>users.users_uuid</v>
       </c>
       <c r="C150" s="10">
@@ -13046,7 +13732,7 @@
       <c r="K150" s="11"/>
       <c r="L150" s="9"/>
       <c r="M150" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K150="","",IF(L150="","参照先未定義",_xlfn.XLOOKUP(L150,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N150" s="11" t="s">
@@ -13069,7 +13755,7 @@
         <v>46</v>
       </c>
       <c r="B151" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.user_id</v>
       </c>
       <c r="C151" s="10">
@@ -13113,7 +13799,7 @@
       <c r="K151" s="11"/>
       <c r="L151" s="9"/>
       <c r="M151" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K151="","",IF(L151="","参照先未定義",_xlfn.XLOOKUP(L151,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N151" s="11" t="s">
@@ -13136,7 +13822,7 @@
         <v>46</v>
       </c>
       <c r="B152" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.user_name</v>
       </c>
       <c r="C152" s="10">
@@ -13180,7 +13866,7 @@
       <c r="K152" s="11"/>
       <c r="L152" s="9"/>
       <c r="M152" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K152="","",IF(L152="","参照先未定義",_xlfn.XLOOKUP(L152,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N152" s="11"/>
@@ -13197,7 +13883,7 @@
         <v>46</v>
       </c>
       <c r="B153" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.user_role_physical_name</v>
       </c>
       <c r="C153" s="10">
@@ -13212,7 +13898,7 @@
         <f t="array" aca="1" ref="E153" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>ユーザー</v>
       </c>
-      <c r="F153" s="21" t="s">
+      <c r="F153" s="11" t="s">
         <v>223</v>
       </c>
       <c r="G153" s="11" t="s">
@@ -13245,7 +13931,7 @@
         <v>517</v>
       </c>
       <c r="M153" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K153="","",IF(L153="","参照先未定義",_xlfn.XLOOKUP(L153,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="7"/>
         <v>170</v>
       </c>
       <c r="N153" s="11"/>
@@ -13262,7 +13948,7 @@
         <v>46</v>
       </c>
       <c r="B154" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.user_name_hidden_flag</v>
       </c>
       <c r="C154" s="10">
@@ -13306,7 +13992,7 @@
       <c r="K154" s="11"/>
       <c r="L154" s="9"/>
       <c r="M154" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K154="","",IF(L154="","参照先未定義",_xlfn.XLOOKUP(L154,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N154" s="11" t="s">
@@ -13329,7 +14015,7 @@
         <v>46</v>
       </c>
       <c r="B155" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.login_service</v>
       </c>
       <c r="C155" s="10">
@@ -13377,7 +14063,7 @@
         <v>510</v>
       </c>
       <c r="M155" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K155="","",IF(L155="","参照先未定義",_xlfn.XLOOKUP(L155,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="7"/>
         <v>121</v>
       </c>
       <c r="N155" s="11"/>
@@ -13394,7 +14080,7 @@
         <v>46</v>
       </c>
       <c r="B156" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.register_date</v>
       </c>
       <c r="C156" s="10">
@@ -13438,7 +14124,7 @@
       <c r="K156" s="11"/>
       <c r="L156" s="9"/>
       <c r="M156" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K156="","",IF(L156="","参照先未定義",_xlfn.XLOOKUP(L156,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N156" s="11" t="s">
@@ -13459,7 +14145,7 @@
         <v>46</v>
       </c>
       <c r="B157" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.disp_theme</v>
       </c>
       <c r="C157" s="10">
@@ -13507,7 +14193,7 @@
         <v>518</v>
       </c>
       <c r="M157" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K157="","",IF(L157="","参照先未定義",_xlfn.XLOOKUP(L157,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="7"/>
         <v>163</v>
       </c>
       <c r="N157" s="11" t="s">
@@ -13528,7 +14214,7 @@
         <v>46</v>
       </c>
       <c r="B158" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.language</v>
       </c>
       <c r="C158" s="10">
@@ -13576,7 +14262,7 @@
         <v>514</v>
       </c>
       <c r="M158" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K158="","",IF(L158="","参照先未定義",_xlfn.XLOOKUP(L158,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="7"/>
         <v>102</v>
       </c>
       <c r="N158" s="11" t="s">
@@ -13597,7 +14283,7 @@
         <v>46</v>
       </c>
       <c r="B159" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.create_datetime</v>
       </c>
       <c r="C159" s="10">
@@ -13641,7 +14327,7 @@
       <c r="K159" s="11"/>
       <c r="L159" s="9"/>
       <c r="M159" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K159="","",IF(L159="","参照先未定義",_xlfn.XLOOKUP(L159,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N159" s="11" t="s">
@@ -13662,7 +14348,7 @@
         <v>46</v>
       </c>
       <c r="B160" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.create_user</v>
       </c>
       <c r="C160" s="10">
@@ -13706,7 +14392,7 @@
       <c r="K160" s="11"/>
       <c r="L160" s="9"/>
       <c r="M160" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K160="","",IF(L160="","参照先未定義",_xlfn.XLOOKUP(L160,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N160" s="11" t="s">
@@ -13729,7 +14415,7 @@
         <v>46</v>
       </c>
       <c r="B161" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.update_datetime</v>
       </c>
       <c r="C161" s="10">
@@ -13773,7 +14459,7 @@
       <c r="K161" s="11"/>
       <c r="L161" s="9"/>
       <c r="M161" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K161="","",IF(L161="","参照先未定義",_xlfn.XLOOKUP(L161,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N161" s="11" t="s">
@@ -13794,7 +14480,7 @@
         <v>46</v>
       </c>
       <c r="B162" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.update_user</v>
       </c>
       <c r="C162" s="10">
@@ -13838,7 +14524,7 @@
       <c r="K162" s="11"/>
       <c r="L162" s="9"/>
       <c r="M162" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K162="","",IF(L162="","参照先未定義",_xlfn.XLOOKUP(L162,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N162" s="11" t="s">
@@ -13861,7 +14547,7 @@
         <v>46</v>
       </c>
       <c r="B163" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>users.soft_delete_flag</v>
       </c>
       <c r="C163" s="10">
@@ -13905,7 +14591,7 @@
       <c r="K163" s="11"/>
       <c r="L163" s="9"/>
       <c r="M163" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K163="","",IF(L163="","参照先未定義",_xlfn.XLOOKUP(L163,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N163" s="11" t="s">
@@ -13926,7 +14612,7 @@
         <v>46</v>
       </c>
       <c r="B164" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>theme.theme_uuid</v>
       </c>
       <c r="C164" s="10">
@@ -13971,7 +14657,7 @@
       <c r="K164" s="11"/>
       <c r="L164" s="9"/>
       <c r="M164" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K164="","",IF(L164="","参照先未定義",_xlfn.XLOOKUP(L164,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N164" s="11" t="s">
@@ -13994,7 +14680,7 @@
         <v>46</v>
       </c>
       <c r="B165" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>theme.theme_physical_name</v>
       </c>
       <c r="C165" s="10">
@@ -14038,7 +14724,7 @@
       <c r="K165" s="11"/>
       <c r="L165" s="9"/>
       <c r="M165" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K165="","",IF(L165="","参照先未定義",_xlfn.XLOOKUP(L165,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N165" s="11" t="s">
@@ -14053,7 +14739,7 @@
       <c r="S165" s="9"/>
       <c r="T165" s="9"/>
       <c r="U165" s="11" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="166" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14061,7 +14747,7 @@
         <v>46</v>
       </c>
       <c r="B166" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>theme.create_datetime</v>
       </c>
       <c r="C166" s="10">
@@ -14105,7 +14791,7 @@
       <c r="K166" s="11"/>
       <c r="L166" s="9"/>
       <c r="M166" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K166="","",IF(L166="","参照先未定義",_xlfn.XLOOKUP(L166,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N166" s="11" t="s">
@@ -14126,7 +14812,7 @@
         <v>46</v>
       </c>
       <c r="B167" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>theme.create_user</v>
       </c>
       <c r="C167" s="10">
@@ -14170,7 +14856,7 @@
       <c r="K167" s="11"/>
       <c r="L167" s="9"/>
       <c r="M167" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K167="","",IF(L167="","参照先未定義",_xlfn.XLOOKUP(L167,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N167" s="11" t="s">
@@ -14193,7 +14879,7 @@
         <v>46</v>
       </c>
       <c r="B168" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>theme.update_datetime</v>
       </c>
       <c r="C168" s="10">
@@ -14237,7 +14923,7 @@
       <c r="K168" s="11"/>
       <c r="L168" s="9"/>
       <c r="M168" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K168="","",IF(L168="","参照先未定義",_xlfn.XLOOKUP(L168,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N168" s="11" t="s">
@@ -14258,7 +14944,7 @@
         <v>46</v>
       </c>
       <c r="B169" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>theme.update_user</v>
       </c>
       <c r="C169" s="10">
@@ -14302,7 +14988,7 @@
       <c r="K169" s="11"/>
       <c r="L169" s="9"/>
       <c r="M169" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K169="","",IF(L169="","参照先未定義",_xlfn.XLOOKUP(L169,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N169" s="11" t="s">
@@ -14325,7 +15011,7 @@
         <v>46</v>
       </c>
       <c r="B170" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>theme.soft_delete_flag</v>
       </c>
       <c r="C170" s="10">
@@ -14369,7 +15055,7 @@
       <c r="K170" s="11"/>
       <c r="L170" s="9"/>
       <c r="M170" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K170="","",IF(L170="","参照先未定義",_xlfn.XLOOKUP(L170,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N170" s="11" t="s">
@@ -14390,7 +15076,7 @@
         <v>46</v>
       </c>
       <c r="B171" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>user_role.user_role_uuid</v>
       </c>
       <c r="C171" s="10">
@@ -14435,7 +15121,7 @@
       <c r="K171" s="11"/>
       <c r="L171" s="9"/>
       <c r="M171" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K171="","",IF(L171="","参照先未定義",_xlfn.XLOOKUP(L171,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N171" s="11" t="s">
@@ -14458,7 +15144,7 @@
         <v>46</v>
       </c>
       <c r="B172" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>user_role.user_role_physical_name</v>
       </c>
       <c r="C172" s="10">
@@ -14502,7 +15188,7 @@
       <c r="K172" s="11"/>
       <c r="L172" s="9"/>
       <c r="M172" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K172="","",IF(L172="","参照先未定義",_xlfn.XLOOKUP(L172,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N172" s="11" t="s">
@@ -14517,7 +15203,7 @@
       <c r="S172" s="9"/>
       <c r="T172" s="9"/>
       <c r="U172" s="11" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="173" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14525,7 +15211,7 @@
         <v>46</v>
       </c>
       <c r="B173" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>user_role.create_datetime</v>
       </c>
       <c r="C173" s="10">
@@ -14569,7 +15255,7 @@
       <c r="K173" s="11"/>
       <c r="L173" s="9"/>
       <c r="M173" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K173="","",IF(L173="","参照先未定義",_xlfn.XLOOKUP(L173,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N173" s="11" t="s">
@@ -14590,7 +15276,7 @@
         <v>46</v>
       </c>
       <c r="B174" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>user_role.create_user</v>
       </c>
       <c r="C174" s="10">
@@ -14634,7 +15320,7 @@
       <c r="K174" s="11"/>
       <c r="L174" s="9"/>
       <c r="M174" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K174="","",IF(L174="","参照先未定義",_xlfn.XLOOKUP(L174,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N174" s="11" t="s">
@@ -14657,7 +15343,7 @@
         <v>46</v>
       </c>
       <c r="B175" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>user_role.update_datetime</v>
       </c>
       <c r="C175" s="10">
@@ -14701,7 +15387,7 @@
       <c r="K175" s="11"/>
       <c r="L175" s="9"/>
       <c r="M175" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K175="","",IF(L175="","参照先未定義",_xlfn.XLOOKUP(L175,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N175" s="11" t="s">
@@ -14722,7 +15408,7 @@
         <v>46</v>
       </c>
       <c r="B176" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>user_role.update_user</v>
       </c>
       <c r="C176" s="10">
@@ -14766,7 +15452,7 @@
       <c r="K176" s="11"/>
       <c r="L176" s="9"/>
       <c r="M176" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K176="","",IF(L176="","参照先未定義",_xlfn.XLOOKUP(L176,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N176" s="11" t="s">
@@ -14789,7 +15475,7 @@
         <v>46</v>
       </c>
       <c r="B177" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>user_role.soft_delete_flag</v>
       </c>
       <c r="C177" s="10">
@@ -14833,7 +15519,7 @@
       <c r="K177" s="11"/>
       <c r="L177" s="9"/>
       <c r="M177" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K177="","",IF(L177="","参照先未定義",_xlfn.XLOOKUP(L177,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N177" s="11" t="s">
@@ -14854,7 +15540,7 @@
         <v>46</v>
       </c>
       <c r="B178" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>images_contents.images_contents_uuid</v>
       </c>
       <c r="C178" s="10">
@@ -14899,7 +15585,7 @@
       <c r="K178" s="11"/>
       <c r="L178" s="9"/>
       <c r="M178" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K178="","",IF(L178="","参照先未定義",_xlfn.XLOOKUP(L178,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N178" s="11" t="s">
@@ -14922,7 +15608,7 @@
         <v>46</v>
       </c>
       <c r="B179" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>images_contents.image_id</v>
       </c>
       <c r="C179" s="10">
@@ -14966,7 +15652,7 @@
       <c r="K179" s="11"/>
       <c r="L179" s="9"/>
       <c r="M179" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K179="","",IF(L179="","参照先未定義",_xlfn.XLOOKUP(L179,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N179" s="11" t="s">
@@ -14987,7 +15673,7 @@
         <v>46</v>
       </c>
       <c r="B180" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>images_contents.user_id</v>
       </c>
       <c r="C180" s="10">
@@ -15035,7 +15721,7 @@
         <v>506</v>
       </c>
       <c r="M180" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K180="","",IF(L180="","参照先未定義",_xlfn.XLOOKUP(L180,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="7"/>
         <v>149</v>
       </c>
       <c r="N180" s="11" t="s">
@@ -15054,7 +15740,7 @@
         <v>46</v>
       </c>
       <c r="B181" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>images_contents.gcs_bucket</v>
       </c>
       <c r="C181" s="10">
@@ -15098,7 +15784,7 @@
       <c r="K181" s="11"/>
       <c r="L181" s="9"/>
       <c r="M181" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K181="","",IF(L181="","参照先未定義",_xlfn.XLOOKUP(L181,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N181" s="11" t="s">
@@ -15117,7 +15803,7 @@
         <v>46</v>
       </c>
       <c r="B182" s="9" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="6"/>
         <v>images_contents.gcs_object_name</v>
       </c>
       <c r="C182" s="10">
@@ -15161,7 +15847,7 @@
       <c r="K182" s="11"/>
       <c r="L182" s="9"/>
       <c r="M182" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K182="","",IF(L182="","参照先未定義",_xlfn.XLOOKUP(L182,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N182" s="11" t="s">
@@ -15182,7 +15868,7 @@
         <v>46</v>
       </c>
       <c r="B183" s="9" t="str">
-        <f t="shared" ref="B183:B246" ca="1" si="5">D183&amp;"."&amp;F183</f>
+        <f t="shared" ref="B183:B246" ca="1" si="8">D183&amp;"."&amp;F183</f>
         <v>images_contents.cdn_url</v>
       </c>
       <c r="C183" s="10">
@@ -15226,7 +15912,7 @@
       <c r="K183" s="11"/>
       <c r="L183" s="9"/>
       <c r="M183" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K183="","",IF(L183="","参照先未定義",_xlfn.XLOOKUP(L183,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N183" s="11"/>
@@ -15245,7 +15931,7 @@
         <v>46</v>
       </c>
       <c r="B184" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_contents.content_type</v>
       </c>
       <c r="C184" s="10">
@@ -15289,7 +15975,7 @@
       <c r="K184" s="11"/>
       <c r="L184" s="9"/>
       <c r="M184" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K184="","",IF(L184="","参照先未定義",_xlfn.XLOOKUP(L184,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N184" s="11"/>
@@ -15308,7 +15994,7 @@
         <v>46</v>
       </c>
       <c r="B185" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_contents.width</v>
       </c>
       <c r="C185" s="10">
@@ -15352,7 +16038,7 @@
       <c r="K185" s="11"/>
       <c r="L185" s="9"/>
       <c r="M185" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K185="","",IF(L185="","参照先未定義",_xlfn.XLOOKUP(L185,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N185" s="11"/>
@@ -15369,7 +16055,7 @@
         <v>46</v>
       </c>
       <c r="B186" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_contents.height</v>
       </c>
       <c r="C186" s="10">
@@ -15413,7 +16099,7 @@
       <c r="K186" s="11"/>
       <c r="L186" s="9"/>
       <c r="M186" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K186="","",IF(L186="","参照先未定義",_xlfn.XLOOKUP(L186,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N186" s="11"/>
@@ -15430,7 +16116,7 @@
         <v>46</v>
       </c>
       <c r="B187" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_contents.file_size</v>
       </c>
       <c r="C187" s="10">
@@ -15474,7 +16160,7 @@
       <c r="K187" s="11"/>
       <c r="L187" s="9"/>
       <c r="M187" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K187="","",IF(L187="","参照先未定義",_xlfn.XLOOKUP(L187,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N187" s="11"/>
@@ -15491,7 +16177,7 @@
         <v>46</v>
       </c>
       <c r="B188" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_contents.alt_text</v>
       </c>
       <c r="C188" s="10">
@@ -15535,7 +16221,7 @@
       <c r="K188" s="11"/>
       <c r="L188" s="9"/>
       <c r="M188" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K188="","",IF(L188="","参照先未定義",_xlfn.XLOOKUP(L188,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N188" s="11"/>
@@ -15552,7 +16238,7 @@
         <v>46</v>
       </c>
       <c r="B189" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_contents.create_datetime</v>
       </c>
       <c r="C189" s="10">
@@ -15596,7 +16282,7 @@
       <c r="K189" s="11"/>
       <c r="L189" s="9"/>
       <c r="M189" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K189="","",IF(L189="","参照先未定義",_xlfn.XLOOKUP(L189,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N189" s="11" t="s">
@@ -15617,7 +16303,7 @@
         <v>46</v>
       </c>
       <c r="B190" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_contents.create_user</v>
       </c>
       <c r="C190" s="10">
@@ -15661,7 +16347,7 @@
       <c r="K190" s="11"/>
       <c r="L190" s="9"/>
       <c r="M190" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K190="","",IF(L190="","参照先未定義",_xlfn.XLOOKUP(L190,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N190" s="11" t="s">
@@ -15684,7 +16370,7 @@
         <v>46</v>
       </c>
       <c r="B191" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_contents.update_datetime</v>
       </c>
       <c r="C191" s="10">
@@ -15728,7 +16414,7 @@
       <c r="K191" s="11"/>
       <c r="L191" s="9"/>
       <c r="M191" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K191="","",IF(L191="","参照先未定義",_xlfn.XLOOKUP(L191,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N191" s="11" t="s">
@@ -15749,7 +16435,7 @@
         <v>46</v>
       </c>
       <c r="B192" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_contents.update_user</v>
       </c>
       <c r="C192" s="10">
@@ -15793,7 +16479,7 @@
       <c r="K192" s="11"/>
       <c r="L192" s="9"/>
       <c r="M192" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K192="","",IF(L192="","参照先未定義",_xlfn.XLOOKUP(L192,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N192" s="11" t="s">
@@ -15816,7 +16502,7 @@
         <v>46</v>
       </c>
       <c r="B193" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_contents.soft_delete_flag</v>
       </c>
       <c r="C193" s="10">
@@ -15860,7 +16546,7 @@
       <c r="K193" s="11"/>
       <c r="L193" s="9"/>
       <c r="M193" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K193="","",IF(L193="","参照先未定義",_xlfn.XLOOKUP(L193,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N193" s="11" t="s">
@@ -15881,7 +16567,7 @@
         <v>46</v>
       </c>
       <c r="B194" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>images_system.images_system_uuid</v>
       </c>
       <c r="C194" s="10">
@@ -15926,7 +16612,7 @@
       <c r="K194" s="11"/>
       <c r="L194" s="9"/>
       <c r="M194" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K194="","",IF(L194="","参照先未定義",_xlfn.XLOOKUP(L194,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ref="M194:M257" si="9">_xlfn.SINGLE(IF(K194="","",IF(L194="","参照先未定義",_xlfn.XLOOKUP(L194,B:B,C:C,"エラー"))))</f>
         <v/>
       </c>
       <c r="N194" s="11" t="s">
@@ -15949,7 +16635,7 @@
         <v>46</v>
       </c>
       <c r="B195" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.image_id</v>
       </c>
       <c r="C195" s="10">
@@ -15993,7 +16679,7 @@
       <c r="K195" s="11"/>
       <c r="L195" s="9"/>
       <c r="M195" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K195="","",IF(L195="","参照先未定義",_xlfn.XLOOKUP(L195,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N195" s="11" t="s">
@@ -16014,7 +16700,7 @@
         <v>46</v>
       </c>
       <c r="B196" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.gcs_bucket</v>
       </c>
       <c r="C196" s="10">
@@ -16058,7 +16744,7 @@
       <c r="K196" s="11"/>
       <c r="L196" s="9"/>
       <c r="M196" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K196="","",IF(L196="","参照先未定義",_xlfn.XLOOKUP(L196,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N196" s="11" t="s">
@@ -16077,7 +16763,7 @@
         <v>46</v>
       </c>
       <c r="B197" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.gcs_object_name</v>
       </c>
       <c r="C197" s="10">
@@ -16121,7 +16807,7 @@
       <c r="K197" s="11"/>
       <c r="L197" s="9"/>
       <c r="M197" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K197="","",IF(L197="","参照先未定義",_xlfn.XLOOKUP(L197,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N197" s="11" t="s">
@@ -16142,7 +16828,7 @@
         <v>46</v>
       </c>
       <c r="B198" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.cdn_url</v>
       </c>
       <c r="C198" s="10">
@@ -16186,7 +16872,7 @@
       <c r="K198" s="11"/>
       <c r="L198" s="9"/>
       <c r="M198" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K198="","",IF(L198="","参照先未定義",_xlfn.XLOOKUP(L198,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N198" s="11"/>
@@ -16205,11 +16891,11 @@
         <v>46</v>
       </c>
       <c r="B199" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.content_type</v>
       </c>
       <c r="C199" s="10">
-        <f t="shared" ref="C199:C254" si="6">ROW()-1</f>
+        <f t="shared" ref="C199:C254" si="10">ROW()-1</f>
         <v>198</v>
       </c>
       <c r="D199" s="11" t="str" cm="1">
@@ -16249,7 +16935,7 @@
       <c r="K199" s="11"/>
       <c r="L199" s="9"/>
       <c r="M199" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K199="","",IF(L199="","参照先未定義",_xlfn.XLOOKUP(L199,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N199" s="11"/>
@@ -16268,11 +16954,11 @@
         <v>46</v>
       </c>
       <c r="B200" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.width</v>
       </c>
       <c r="C200" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>199</v>
       </c>
       <c r="D200" s="11" t="str" cm="1">
@@ -16312,7 +16998,7 @@
       <c r="K200" s="11"/>
       <c r="L200" s="9"/>
       <c r="M200" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K200="","",IF(L200="","参照先未定義",_xlfn.XLOOKUP(L200,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N200" s="11"/>
@@ -16329,11 +17015,11 @@
         <v>46</v>
       </c>
       <c r="B201" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.height</v>
       </c>
       <c r="C201" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>200</v>
       </c>
       <c r="D201" s="11" t="str" cm="1">
@@ -16373,7 +17059,7 @@
       <c r="K201" s="11"/>
       <c r="L201" s="9"/>
       <c r="M201" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K201="","",IF(L201="","参照先未定義",_xlfn.XLOOKUP(L201,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N201" s="11"/>
@@ -16390,11 +17076,11 @@
         <v>46</v>
       </c>
       <c r="B202" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.file_size</v>
       </c>
       <c r="C202" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>201</v>
       </c>
       <c r="D202" s="11" t="str" cm="1">
@@ -16434,7 +17120,7 @@
       <c r="K202" s="11"/>
       <c r="L202" s="9"/>
       <c r="M202" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K202="","",IF(L202="","参照先未定義",_xlfn.XLOOKUP(L202,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N202" s="11"/>
@@ -16451,11 +17137,11 @@
         <v>46</v>
       </c>
       <c r="B203" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.alt_text</v>
       </c>
       <c r="C203" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>202</v>
       </c>
       <c r="D203" s="11" t="str" cm="1">
@@ -16495,7 +17181,7 @@
       <c r="K203" s="11"/>
       <c r="L203" s="9"/>
       <c r="M203" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K203="","",IF(L203="","参照先未定義",_xlfn.XLOOKUP(L203,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N203" s="11"/>
@@ -16512,11 +17198,11 @@
         <v>46</v>
       </c>
       <c r="B204" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.create_datetime</v>
       </c>
       <c r="C204" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>203</v>
       </c>
       <c r="D204" s="11" t="str" cm="1">
@@ -16556,7 +17242,7 @@
       <c r="K204" s="11"/>
       <c r="L204" s="9"/>
       <c r="M204" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K204="","",IF(L204="","参照先未定義",_xlfn.XLOOKUP(L204,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N204" s="11" t="s">
@@ -16577,11 +17263,11 @@
         <v>46</v>
       </c>
       <c r="B205" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.create_user</v>
       </c>
       <c r="C205" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>204</v>
       </c>
       <c r="D205" s="11" t="str" cm="1">
@@ -16621,7 +17307,7 @@
       <c r="K205" s="11"/>
       <c r="L205" s="9"/>
       <c r="M205" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K205="","",IF(L205="","参照先未定義",_xlfn.XLOOKUP(L205,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N205" s="11" t="s">
@@ -16644,11 +17330,11 @@
         <v>46</v>
       </c>
       <c r="B206" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.update_datetime</v>
       </c>
       <c r="C206" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>205</v>
       </c>
       <c r="D206" s="11" t="str" cm="1">
@@ -16688,7 +17374,7 @@
       <c r="K206" s="11"/>
       <c r="L206" s="9"/>
       <c r="M206" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K206="","",IF(L206="","参照先未定義",_xlfn.XLOOKUP(L206,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N206" s="11" t="s">
@@ -16709,11 +17395,11 @@
         <v>46</v>
       </c>
       <c r="B207" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.update_user</v>
       </c>
       <c r="C207" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>206</v>
       </c>
       <c r="D207" s="11" t="str" cm="1">
@@ -16753,7 +17439,7 @@
       <c r="K207" s="11"/>
       <c r="L207" s="9"/>
       <c r="M207" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K207="","",IF(L207="","参照先未定義",_xlfn.XLOOKUP(L207,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N207" s="11" t="s">
@@ -16776,11 +17462,11 @@
         <v>46</v>
       </c>
       <c r="B208" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>images_system.soft_delete_flag</v>
       </c>
       <c r="C208" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>207</v>
       </c>
       <c r="D208" s="11" t="str" cm="1">
@@ -16820,7 +17506,7 @@
       <c r="K208" s="11"/>
       <c r="L208" s="9"/>
       <c r="M208" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K208="","",IF(L208="","参照先未定義",_xlfn.XLOOKUP(L208,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N208" s="11" t="s">
@@ -16841,11 +17527,11 @@
         <v>46</v>
       </c>
       <c r="B209" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>screen_element.screen_element_uuid</v>
       </c>
       <c r="C209" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>208</v>
       </c>
       <c r="D209" s="11" t="s">
@@ -16886,7 +17572,7 @@
       <c r="K209" s="11"/>
       <c r="L209" s="9"/>
       <c r="M209" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K209="","",IF(L209="","参照先未定義",_xlfn.XLOOKUP(L209,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N209" s="11" t="s">
@@ -16909,11 +17595,11 @@
         <v>46</v>
       </c>
       <c r="B210" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>screen_element.message_id</v>
       </c>
       <c r="C210" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>209</v>
       </c>
       <c r="D210" s="11" t="str" cm="1">
@@ -16953,7 +17639,7 @@
       <c r="K210" s="11"/>
       <c r="L210" s="9"/>
       <c r="M210" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K210="","",IF(L210="","参照先未定義",_xlfn.XLOOKUP(L210,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N210" s="11" t="s">
@@ -16976,11 +17662,11 @@
         <v>46</v>
       </c>
       <c r="B211" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>screen_element.create_datetime</v>
       </c>
       <c r="C211" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>210</v>
       </c>
       <c r="D211" s="11" t="str" cm="1">
@@ -17020,7 +17706,7 @@
       <c r="K211" s="11"/>
       <c r="L211" s="9"/>
       <c r="M211" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K211="","",IF(L211="","参照先未定義",_xlfn.XLOOKUP(L211,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N211" s="11" t="s">
@@ -17041,11 +17727,11 @@
         <v>46</v>
       </c>
       <c r="B212" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>screen_element.create_user</v>
       </c>
       <c r="C212" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>211</v>
       </c>
       <c r="D212" s="11" t="str" cm="1">
@@ -17085,7 +17771,7 @@
       <c r="K212" s="11"/>
       <c r="L212" s="9"/>
       <c r="M212" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K212="","",IF(L212="","参照先未定義",_xlfn.XLOOKUP(L212,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N212" s="11" t="s">
@@ -17108,11 +17794,11 @@
         <v>46</v>
       </c>
       <c r="B213" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>screen_element.update_datetime</v>
       </c>
       <c r="C213" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>212</v>
       </c>
       <c r="D213" s="11" t="str" cm="1">
@@ -17152,7 +17838,7 @@
       <c r="K213" s="11"/>
       <c r="L213" s="9"/>
       <c r="M213" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K213="","",IF(L213="","参照先未定義",_xlfn.XLOOKUP(L213,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N213" s="11" t="s">
@@ -17173,11 +17859,11 @@
         <v>46</v>
       </c>
       <c r="B214" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>screen_element.update_user</v>
       </c>
       <c r="C214" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>213</v>
       </c>
       <c r="D214" s="11" t="str" cm="1">
@@ -17217,7 +17903,7 @@
       <c r="K214" s="11"/>
       <c r="L214" s="9"/>
       <c r="M214" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K214="","",IF(L214="","参照先未定義",_xlfn.XLOOKUP(L214,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N214" s="11" t="s">
@@ -17240,11 +17926,11 @@
         <v>46</v>
       </c>
       <c r="B215" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>screen_element.soft_delete_flag</v>
       </c>
       <c r="C215" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>214</v>
       </c>
       <c r="D215" s="11" t="str" cm="1">
@@ -17284,7 +17970,7 @@
       <c r="K215" s="11"/>
       <c r="L215" s="9"/>
       <c r="M215" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K215="","",IF(L215="","参照先未定義",_xlfn.XLOOKUP(L215,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N215" s="11" t="s">
@@ -17305,11 +17991,11 @@
         <v>46</v>
       </c>
       <c r="B216" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>likes.likes_uuid</v>
       </c>
       <c r="C216" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>215</v>
       </c>
       <c r="D216" s="11" t="s">
@@ -17350,7 +18036,7 @@
       <c r="K216" s="11"/>
       <c r="L216" s="9"/>
       <c r="M216" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K216="","",IF(L216="","参照先未定義",_xlfn.XLOOKUP(L216,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N216" s="11" t="s">
@@ -17373,11 +18059,11 @@
         <v>46</v>
       </c>
       <c r="B217" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>likes.likes_do_user</v>
       </c>
       <c r="C217" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>216</v>
       </c>
       <c r="D217" s="11" t="s">
@@ -17420,7 +18106,7 @@
         <v>506</v>
       </c>
       <c r="M217" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K217="","",IF(L217="","参照先未定義",_xlfn.XLOOKUP(L217,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="9"/>
         <v>149</v>
       </c>
       <c r="N217" s="11" t="s">
@@ -17443,11 +18129,11 @@
         <v>46</v>
       </c>
       <c r="B218" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>likes.likes_target_user</v>
       </c>
       <c r="C218" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>217</v>
       </c>
       <c r="D218" s="11" t="str" cm="1">
@@ -17491,7 +18177,7 @@
         <v>506</v>
       </c>
       <c r="M218" s="11">
-        <f ca="1">_xlfn.SINGLE(IF(K218="","",IF(L218="","参照先未定義",_xlfn.XLOOKUP(L218,B:B,C:C,"エラー"))))</f>
+        <f t="shared" ca="1" si="9"/>
         <v>149</v>
       </c>
       <c r="N218" s="11" t="s">
@@ -17514,11 +18200,11 @@
         <v>46</v>
       </c>
       <c r="B219" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>likes.likes_type</v>
       </c>
       <c r="C219" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>218</v>
       </c>
       <c r="D219" s="11" t="str" cm="1">
@@ -17558,7 +18244,7 @@
       <c r="K219" s="11"/>
       <c r="L219" s="9"/>
       <c r="M219" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K219="","",IF(L219="","参照先未定義",_xlfn.XLOOKUP(L219,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N219" s="11" t="s">
@@ -17581,11 +18267,11 @@
         <v>46</v>
       </c>
       <c r="B220" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>likes.likes_datetime</v>
       </c>
       <c r="C220" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>219</v>
       </c>
       <c r="D220" s="11" t="str" cm="1">
@@ -17625,7 +18311,7 @@
       <c r="K220" s="11"/>
       <c r="L220" s="9"/>
       <c r="M220" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K220="","",IF(L220="","参照先未定義",_xlfn.XLOOKUP(L220,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N220" s="11" t="s">
@@ -17644,11 +18330,11 @@
         <v>46</v>
       </c>
       <c r="B221" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>likes.create_datetime</v>
       </c>
       <c r="C221" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>220</v>
       </c>
       <c r="D221" s="11" t="str" cm="1">
@@ -17688,7 +18374,7 @@
       <c r="K221" s="11"/>
       <c r="L221" s="9"/>
       <c r="M221" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K221="","",IF(L221="","参照先未定義",_xlfn.XLOOKUP(L221,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N221" s="11" t="s">
@@ -17709,11 +18395,11 @@
         <v>46</v>
       </c>
       <c r="B222" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>likes.create_user</v>
       </c>
       <c r="C222" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>221</v>
       </c>
       <c r="D222" s="11" t="str" cm="1">
@@ -17753,7 +18439,7 @@
       <c r="K222" s="11"/>
       <c r="L222" s="9"/>
       <c r="M222" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K222="","",IF(L222="","参照先未定義",_xlfn.XLOOKUP(L222,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N222" s="11" t="s">
@@ -17776,11 +18462,11 @@
         <v>46</v>
       </c>
       <c r="B223" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>likes.update_datetime</v>
       </c>
       <c r="C223" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>222</v>
       </c>
       <c r="D223" s="11" t="str" cm="1">
@@ -17820,7 +18506,7 @@
       <c r="K223" s="11"/>
       <c r="L223" s="9"/>
       <c r="M223" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K223="","",IF(L223="","参照先未定義",_xlfn.XLOOKUP(L223,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N223" s="11" t="s">
@@ -17841,11 +18527,11 @@
         <v>46</v>
       </c>
       <c r="B224" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>likes.update_user</v>
       </c>
       <c r="C224" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>223</v>
       </c>
       <c r="D224" s="11" t="str" cm="1">
@@ -17885,7 +18571,7 @@
       <c r="K224" s="11"/>
       <c r="L224" s="9"/>
       <c r="M224" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K224="","",IF(L224="","参照先未定義",_xlfn.XLOOKUP(L224,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N224" s="11" t="s">
@@ -17908,11 +18594,11 @@
         <v>46</v>
       </c>
       <c r="B225" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>likes.soft_delete_flag</v>
       </c>
       <c r="C225" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>224</v>
       </c>
       <c r="D225" s="11" t="str" cm="1">
@@ -17952,7 +18638,7 @@
       <c r="K225" s="11"/>
       <c r="L225" s="9"/>
       <c r="M225" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K225="","",IF(L225="","参照先未定義",_xlfn.XLOOKUP(L225,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N225" s="11" t="s">
@@ -17973,11 +18659,11 @@
         <v>46</v>
       </c>
       <c r="B226" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>movie_link.movie_link_uuid</v>
       </c>
       <c r="C226" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>225</v>
       </c>
       <c r="D226" s="11" t="s">
@@ -18018,7 +18704,7 @@
       <c r="K226" s="11"/>
       <c r="L226" s="9"/>
       <c r="M226" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K226="","",IF(L226="","参照先未定義",_xlfn.XLOOKUP(L226,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N226" s="11" t="s">
@@ -18041,11 +18727,11 @@
         <v>46</v>
       </c>
       <c r="B227" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>movie_link.movie_id</v>
       </c>
       <c r="C227" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>226</v>
       </c>
       <c r="D227" s="11" t="str" cm="1">
@@ -18085,7 +18771,7 @@
       <c r="K227" s="11"/>
       <c r="L227" s="9"/>
       <c r="M227" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K227="","",IF(L227="","参照先未定義",_xlfn.XLOOKUP(L227,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N227" s="11" t="s">
@@ -18106,11 +18792,11 @@
         <v>46</v>
       </c>
       <c r="B228" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>movie_link.vtuber_profiles_id</v>
       </c>
       <c r="C228" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>227</v>
       </c>
       <c r="D228" s="11" t="str" cm="1">
@@ -18154,7 +18840,7 @@
         <v>509</v>
       </c>
       <c r="M228" s="11">
-        <f>_xlfn.SINGLE(IF(K228="","",IF(L228="","参照先未定義",_xlfn.XLOOKUP(L228,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N228" s="11" t="s">
@@ -18173,11 +18859,11 @@
         <v>46</v>
       </c>
       <c r="B229" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>movie_link.url</v>
       </c>
       <c r="C229" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>228</v>
       </c>
       <c r="D229" s="11" t="str" cm="1">
@@ -18217,7 +18903,7 @@
       <c r="K229" s="11"/>
       <c r="L229" s="9"/>
       <c r="M229" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K229="","",IF(L229="","参照先未定義",_xlfn.XLOOKUP(L229,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N229" s="11" t="s">
@@ -18236,11 +18922,11 @@
         <v>46</v>
       </c>
       <c r="B230" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>movie_link.create_datetime</v>
       </c>
       <c r="C230" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>229</v>
       </c>
       <c r="D230" s="11" t="str" cm="1">
@@ -18280,7 +18966,7 @@
       <c r="K230" s="11"/>
       <c r="L230" s="9"/>
       <c r="M230" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K230="","",IF(L230="","参照先未定義",_xlfn.XLOOKUP(L230,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N230" s="11" t="s">
@@ -18301,11 +18987,11 @@
         <v>46</v>
       </c>
       <c r="B231" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>movie_link.create_user</v>
       </c>
       <c r="C231" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>230</v>
       </c>
       <c r="D231" s="11" t="str" cm="1">
@@ -18345,7 +19031,7 @@
       <c r="K231" s="11"/>
       <c r="L231" s="9"/>
       <c r="M231" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K231="","",IF(L231="","参照先未定義",_xlfn.XLOOKUP(L231,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N231" s="11" t="s">
@@ -18368,11 +19054,11 @@
         <v>46</v>
       </c>
       <c r="B232" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>movie_link.update_datetime</v>
       </c>
       <c r="C232" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>231</v>
       </c>
       <c r="D232" s="11" t="str" cm="1">
@@ -18412,7 +19098,7 @@
       <c r="K232" s="11"/>
       <c r="L232" s="9"/>
       <c r="M232" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K232="","",IF(L232="","参照先未定義",_xlfn.XLOOKUP(L232,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N232" s="11" t="s">
@@ -18433,11 +19119,11 @@
         <v>46</v>
       </c>
       <c r="B233" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>movie_link.update_user</v>
       </c>
       <c r="C233" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>232</v>
       </c>
       <c r="D233" s="11" t="str" cm="1">
@@ -18477,7 +19163,7 @@
       <c r="K233" s="11"/>
       <c r="L233" s="9"/>
       <c r="M233" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K233="","",IF(L233="","参照先未定義",_xlfn.XLOOKUP(L233,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N233" s="11" t="s">
@@ -18500,11 +19186,11 @@
         <v>46</v>
       </c>
       <c r="B234" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>movie_link.soft_delete_flag</v>
       </c>
       <c r="C234" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>233</v>
       </c>
       <c r="D234" s="11" t="str" cm="1">
@@ -18544,7 +19230,7 @@
       <c r="K234" s="11"/>
       <c r="L234" s="9"/>
       <c r="M234" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K234="","",IF(L234="","参照先未定義",_xlfn.XLOOKUP(L234,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N234" s="11" t="s">
@@ -18565,11 +19251,11 @@
         <v>46</v>
       </c>
       <c r="B235" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>relation.relation_uuid</v>
       </c>
       <c r="C235" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>234</v>
       </c>
       <c r="D235" s="11" t="s">
@@ -18610,7 +19296,7 @@
       <c r="K235" s="11"/>
       <c r="L235" s="9"/>
       <c r="M235" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K235="","",IF(L235="","参照先未定義",_xlfn.XLOOKUP(L235,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N235" s="11" t="s">
@@ -18633,11 +19319,11 @@
         <v>46</v>
       </c>
       <c r="B236" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>relation.node_from</v>
       </c>
       <c r="C236" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>235</v>
       </c>
       <c r="D236" s="11" t="str" cm="1">
@@ -18681,7 +19367,7 @@
         <v>509</v>
       </c>
       <c r="M236" s="11">
-        <f>_xlfn.SINGLE(IF(K236="","",IF(L236="","参照先未定義",_xlfn.XLOOKUP(L236,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N236" s="11" t="s">
@@ -18704,11 +19390,11 @@
         <v>46</v>
       </c>
       <c r="B237" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>relation.node_to</v>
       </c>
       <c r="C237" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>236</v>
       </c>
       <c r="D237" s="11" t="str" cm="1">
@@ -18752,7 +19438,7 @@
         <v>509</v>
       </c>
       <c r="M237" s="11">
-        <f>_xlfn.SINGLE(IF(K237="","",IF(L237="","参照先未定義",_xlfn.XLOOKUP(L237,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N237" s="11" t="s">
@@ -18775,11 +19461,11 @@
         <v>46</v>
       </c>
       <c r="B238" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>relation.node_name</v>
       </c>
       <c r="C238" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>237</v>
       </c>
       <c r="D238" s="11" t="str" cm="1">
@@ -18819,7 +19505,7 @@
       <c r="K238" s="11"/>
       <c r="L238" s="9"/>
       <c r="M238" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K238="","",IF(L238="","参照先未定義",_xlfn.XLOOKUP(L238,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N238" s="11" t="s">
@@ -18838,11 +19524,11 @@
         <v>46</v>
       </c>
       <c r="B239" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>relation.create_datetime</v>
       </c>
       <c r="C239" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>238</v>
       </c>
       <c r="D239" s="11" t="str" cm="1">
@@ -18882,7 +19568,7 @@
       <c r="K239" s="11"/>
       <c r="L239" s="9"/>
       <c r="M239" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K239="","",IF(L239="","参照先未定義",_xlfn.XLOOKUP(L239,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N239" s="11" t="s">
@@ -18903,11 +19589,11 @@
         <v>46</v>
       </c>
       <c r="B240" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>relation.create_user</v>
       </c>
       <c r="C240" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>239</v>
       </c>
       <c r="D240" s="11" t="str" cm="1">
@@ -18947,7 +19633,7 @@
       <c r="K240" s="11"/>
       <c r="L240" s="9"/>
       <c r="M240" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K240="","",IF(L240="","参照先未定義",_xlfn.XLOOKUP(L240,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N240" s="11" t="s">
@@ -18970,11 +19656,11 @@
         <v>46</v>
       </c>
       <c r="B241" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>relation.update_datetime</v>
       </c>
       <c r="C241" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>240</v>
       </c>
       <c r="D241" s="11" t="str" cm="1">
@@ -19014,7 +19700,7 @@
       <c r="K241" s="11"/>
       <c r="L241" s="9"/>
       <c r="M241" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K241="","",IF(L241="","参照先未定義",_xlfn.XLOOKUP(L241,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N241" s="11" t="s">
@@ -19035,11 +19721,11 @@
         <v>46</v>
       </c>
       <c r="B242" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>relation.update_user</v>
       </c>
       <c r="C242" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>241</v>
       </c>
       <c r="D242" s="11" t="str" cm="1">
@@ -19079,7 +19765,7 @@
       <c r="K242" s="11"/>
       <c r="L242" s="9"/>
       <c r="M242" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K242="","",IF(L242="","参照先未定義",_xlfn.XLOOKUP(L242,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N242" s="11" t="s">
@@ -19102,11 +19788,11 @@
         <v>46</v>
       </c>
       <c r="B243" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>relation.soft_delete_flag</v>
       </c>
       <c r="C243" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>242</v>
       </c>
       <c r="D243" s="11" t="str" cm="1">
@@ -19146,7 +19832,7 @@
       <c r="K243" s="11"/>
       <c r="L243" s="9"/>
       <c r="M243" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K243="","",IF(L243="","参照先未定義",_xlfn.XLOOKUP(L243,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N243" s="11" t="s">
@@ -19167,11 +19853,11 @@
         <v>46</v>
       </c>
       <c r="B244" s="9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>vtuber_profiles_lang.vtuber_profiles_lang_uuid</v>
       </c>
       <c r="C244" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>243</v>
       </c>
       <c r="D244" s="11" t="s">
@@ -19212,7 +19898,7 @@
       <c r="K244" s="11"/>
       <c r="L244" s="9"/>
       <c r="M244" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K244="","",IF(L244="","参照先未定義",_xlfn.XLOOKUP(L244,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N244" s="11" t="s">
@@ -19235,11 +19921,11 @@
         <v>46</v>
       </c>
       <c r="B245" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>vtuber_profiles_lang.vtuber_profiles_id</v>
       </c>
       <c r="C245" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>244</v>
       </c>
       <c r="D245" s="11" t="str" cm="1">
@@ -19283,7 +19969,7 @@
         <v>509</v>
       </c>
       <c r="M245" s="11">
-        <f>_xlfn.SINGLE(IF(K245="","",IF(L245="","参照先未定義",_xlfn.XLOOKUP(L245,B:B,C:C,"エラー"))))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N245" s="11" t="s">
@@ -19306,11 +19992,11 @@
         <v>46</v>
       </c>
       <c r="B246" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="8"/>
         <v>vtuber_profiles_lang.lang</v>
       </c>
       <c r="C246" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>245</v>
       </c>
       <c r="D246" s="11" t="str" cm="1">
@@ -19354,7 +20040,7 @@
         <v>514</v>
       </c>
       <c r="M246" s="11">
-        <f ca="1">IF(K246="","",IF(L246="","参照先未定義",_xlfn.XLOOKUP(L246,B:B,C:C,"エラー")))</f>
+        <f t="shared" ref="M246:M280" ca="1" si="11">IF(K246="","",IF(L246="","参照先未定義",_xlfn.XLOOKUP(L246,B:B,C:C,"エラー")))</f>
         <v>102</v>
       </c>
       <c r="N246" s="11" t="s">
@@ -19377,11 +20063,11 @@
         <v>46</v>
       </c>
       <c r="B247" s="9" t="str">
-        <f t="shared" ref="B247:B275" ca="1" si="7">D247&amp;"."&amp;F247</f>
+        <f t="shared" ref="B247:B275" ca="1" si="12">D247&amp;"."&amp;F247</f>
         <v>vtuber_profiles_lang.name</v>
       </c>
       <c r="C247" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>246</v>
       </c>
       <c r="D247" s="11" t="str" cm="1">
@@ -19421,7 +20107,7 @@
       <c r="K247" s="11"/>
       <c r="L247" s="9"/>
       <c r="M247" s="11" t="str">
-        <f>IF(K247="","",IF(L247="","参照先未定義",_xlfn.XLOOKUP(L247,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N247" s="11" t="s">
@@ -19444,11 +20130,11 @@
         <v>46</v>
       </c>
       <c r="B248" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.nickname</v>
       </c>
       <c r="C248" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>247</v>
       </c>
       <c r="D248" s="11" t="str" cm="1">
@@ -19488,7 +20174,7 @@
       <c r="K248" s="11"/>
       <c r="L248" s="9"/>
       <c r="M248" s="11" t="str">
-        <f>IF(K248="","",IF(L248="","参照先未定義",_xlfn.XLOOKUP(L248,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N248" s="11"/>
@@ -19507,11 +20193,11 @@
         <v>46</v>
       </c>
       <c r="B249" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.birthday</v>
       </c>
       <c r="C249" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>248</v>
       </c>
       <c r="D249" s="11" t="str" cm="1">
@@ -19551,7 +20237,7 @@
       <c r="K249" s="11"/>
       <c r="L249" s="9"/>
       <c r="M249" s="11" t="str">
-        <f>IF(K249="","",IF(L249="","参照先未定義",_xlfn.XLOOKUP(L249,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N249" s="11"/>
@@ -19570,11 +20256,11 @@
         <v>46</v>
       </c>
       <c r="B250" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.blood_type</v>
       </c>
       <c r="C250" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>249</v>
       </c>
       <c r="D250" s="11" t="str" cm="1">
@@ -19614,7 +20300,7 @@
       <c r="K250" s="11"/>
       <c r="L250" s="9"/>
       <c r="M250" s="11" t="str">
-        <f>IF(K250="","",IF(L250="","参照先未定義",_xlfn.XLOOKUP(L250,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N250" s="11"/>
@@ -19633,11 +20319,11 @@
         <v>46</v>
       </c>
       <c r="B251" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.height</v>
       </c>
       <c r="C251" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>250</v>
       </c>
       <c r="D251" s="11" t="str" cm="1">
@@ -19677,7 +20363,7 @@
       <c r="K251" s="11"/>
       <c r="L251" s="9"/>
       <c r="M251" s="11" t="str">
-        <f>IF(K251="","",IF(L251="","参照先未定義",_xlfn.XLOOKUP(L251,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N251" s="11"/>
@@ -19696,11 +20382,11 @@
         <v>46</v>
       </c>
       <c r="B252" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.mutter</v>
       </c>
       <c r="C252" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>251</v>
       </c>
       <c r="D252" s="11" t="str" cm="1">
@@ -19740,7 +20426,7 @@
       <c r="K252" s="11"/>
       <c r="L252" s="9"/>
       <c r="M252" s="11" t="str">
-        <f>IF(K252="","",IF(L252="","参照先未定義",_xlfn.XLOOKUP(L252,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N252" s="11"/>
@@ -19759,11 +20445,11 @@
         <v>46</v>
       </c>
       <c r="B253" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.catchphrase</v>
       </c>
       <c r="C253" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>252</v>
       </c>
       <c r="D253" s="11" t="str" cm="1">
@@ -19803,7 +20489,7 @@
       <c r="K253" s="11"/>
       <c r="L253" s="9"/>
       <c r="M253" s="11" t="str">
-        <f>IF(K253="","",IF(L253="","参照先未定義",_xlfn.XLOOKUP(L253,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N253" s="11"/>
@@ -19822,11 +20508,11 @@
         <v>46</v>
       </c>
       <c r="B254" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.favorite</v>
       </c>
       <c r="C254" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>253</v>
       </c>
       <c r="D254" s="11" t="str" cm="1">
@@ -19866,7 +20552,7 @@
       <c r="K254" s="11"/>
       <c r="L254" s="9"/>
       <c r="M254" s="11" t="str">
-        <f>IF(K254="","",IF(L254="","参照先未定義",_xlfn.XLOOKUP(L254,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N254" s="11"/>
@@ -19885,11 +20571,11 @@
         <v>46</v>
       </c>
       <c r="B255" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.dis_favorite</v>
       </c>
       <c r="C255" s="10">
-        <f t="shared" ref="C255:C275" si="8">ROW()-1</f>
+        <f t="shared" ref="C255:C275" si="13">ROW()-1</f>
         <v>254</v>
       </c>
       <c r="D255" s="11" t="str" cm="1">
@@ -19929,7 +20615,7 @@
       <c r="K255" s="11"/>
       <c r="L255" s="9"/>
       <c r="M255" s="11" t="str">
-        <f>IF(K255="","",IF(L255="","参照先未定義",_xlfn.XLOOKUP(L255,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N255" s="11"/>
@@ -19948,11 +20634,11 @@
         <v>46</v>
       </c>
       <c r="B256" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.hobby</v>
       </c>
       <c r="C256" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>255</v>
       </c>
       <c r="D256" s="11" t="str" cm="1">
@@ -19992,7 +20678,7 @@
       <c r="K256" s="11"/>
       <c r="L256" s="9"/>
       <c r="M256" s="11" t="str">
-        <f>IF(K256="","",IF(L256="","参照先未定義",_xlfn.XLOOKUP(L256,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N256" s="11"/>
@@ -20011,11 +20697,11 @@
         <v>46</v>
       </c>
       <c r="B257" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.dream</v>
       </c>
       <c r="C257" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>256</v>
       </c>
       <c r="D257" s="11" t="str" cm="1">
@@ -20055,7 +20741,7 @@
       <c r="K257" s="11"/>
       <c r="L257" s="9"/>
       <c r="M257" s="11" t="str">
-        <f>IF(K257="","",IF(L257="","参照先未定義",_xlfn.XLOOKUP(L257,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N257" s="11"/>
@@ -20074,11 +20760,11 @@
         <v>46</v>
       </c>
       <c r="B258" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.messages</v>
       </c>
       <c r="C258" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>257</v>
       </c>
       <c r="D258" s="11" t="str" cm="1">
@@ -20118,7 +20804,7 @@
       <c r="K258" s="11"/>
       <c r="L258" s="9"/>
       <c r="M258" s="11" t="str">
-        <f>IF(K258="","",IF(L258="","参照先未定義",_xlfn.XLOOKUP(L258,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N258" s="11"/>
@@ -20137,11 +20823,11 @@
         <v>46</v>
       </c>
       <c r="B259" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.profile_detail</v>
       </c>
       <c r="C259" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>258</v>
       </c>
       <c r="D259" s="11" t="str" cm="1">
@@ -20181,7 +20867,7 @@
       <c r="K259" s="11"/>
       <c r="L259" s="9"/>
       <c r="M259" s="11" t="str">
-        <f>IF(K259="","",IF(L259="","参照先未定義",_xlfn.XLOOKUP(L259,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N259" s="11"/>
@@ -20202,11 +20888,11 @@
         <v>46</v>
       </c>
       <c r="B260" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.create_datetime</v>
       </c>
       <c r="C260" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>259</v>
       </c>
       <c r="D260" s="11" t="str" cm="1">
@@ -20246,7 +20932,7 @@
       <c r="K260" s="11"/>
       <c r="L260" s="9"/>
       <c r="M260" s="11" t="str">
-        <f>IF(K260="","",IF(L260="","参照先未定義",_xlfn.XLOOKUP(L260,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N260" s="11" t="s">
@@ -20267,11 +20953,11 @@
         <v>46</v>
       </c>
       <c r="B261" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.create_user</v>
       </c>
       <c r="C261" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>260</v>
       </c>
       <c r="D261" s="11" t="str" cm="1">
@@ -20311,7 +20997,7 @@
       <c r="K261" s="11"/>
       <c r="L261" s="9"/>
       <c r="M261" s="11" t="str">
-        <f>IF(K261="","",IF(L261="","参照先未定義",_xlfn.XLOOKUP(L261,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N261" s="11" t="s">
@@ -20334,11 +21020,11 @@
         <v>46</v>
       </c>
       <c r="B262" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.update_datetime</v>
       </c>
       <c r="C262" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>261</v>
       </c>
       <c r="D262" s="11" t="str" cm="1">
@@ -20378,7 +21064,7 @@
       <c r="K262" s="11"/>
       <c r="L262" s="9"/>
       <c r="M262" s="11" t="str">
-        <f>IF(K262="","",IF(L262="","参照先未定義",_xlfn.XLOOKUP(L262,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N262" s="11" t="s">
@@ -20399,11 +21085,11 @@
         <v>46</v>
       </c>
       <c r="B263" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.update_user</v>
       </c>
       <c r="C263" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>262</v>
       </c>
       <c r="D263" s="11" t="str" cm="1">
@@ -20443,7 +21129,7 @@
       <c r="K263" s="11"/>
       <c r="L263" s="9"/>
       <c r="M263" s="11" t="str">
-        <f>IF(K263="","",IF(L263="","参照先未定義",_xlfn.XLOOKUP(L263,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N263" s="11" t="s">
@@ -20466,11 +21152,11 @@
         <v>46</v>
       </c>
       <c r="B264" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>vtuber_profiles_lang.soft_delete_flag</v>
       </c>
       <c r="C264" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>263</v>
       </c>
       <c r="D264" s="11" t="str" cm="1">
@@ -20510,7 +21196,7 @@
       <c r="K264" s="11"/>
       <c r="L264" s="9"/>
       <c r="M264" s="11" t="str">
-        <f>IF(K264="","",IF(L264="","参照先未定義",_xlfn.XLOOKUP(L264,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N264" s="11" t="s">
@@ -20531,11 +21217,11 @@
         <v>46</v>
       </c>
       <c r="B265" s="9" t="str">
-        <f t="shared" ref="B265:B267" si="9">D265&amp;"."&amp;F265</f>
+        <f t="shared" ref="B265:B267" si="14">D265&amp;"."&amp;F265</f>
         <v>profile_tag.profile_tag_uuid</v>
       </c>
       <c r="C265" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>264</v>
       </c>
       <c r="D265" s="11" t="s">
@@ -20576,7 +21262,7 @@
       <c r="K265" s="11"/>
       <c r="L265" s="9"/>
       <c r="M265" s="11" t="str">
-        <f>IF(K265="","",IF(L265="","参照先未定義",_xlfn.XLOOKUP(L265,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N265" s="11" t="s">
@@ -20599,11 +21285,11 @@
         <v>46</v>
       </c>
       <c r="B266" s="9" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v>profile_tag.vtuber_profiles_id</v>
       </c>
       <c r="C266" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>265</v>
       </c>
       <c r="D266" s="11" t="str" cm="1">
@@ -20647,7 +21333,7 @@
         <v>509</v>
       </c>
       <c r="M266" s="11">
-        <f>IF(K266="","",IF(L266="","参照先未定義",_xlfn.XLOOKUP(L266,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="N266" s="11" t="s">
@@ -20670,11 +21356,11 @@
         <v>46</v>
       </c>
       <c r="B267" s="9" t="str">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" ca="1" si="14"/>
         <v>profile_tag.tag</v>
       </c>
       <c r="C267" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>266</v>
       </c>
       <c r="D267" s="11" t="str" cm="1">
@@ -20718,7 +21404,7 @@
         <v>519</v>
       </c>
       <c r="M267" s="11">
-        <f ca="1">IF(K267="","",IF(L267="","参照先未定義",_xlfn.XLOOKUP(L267,B:B,C:C,"エラー")))</f>
+        <f t="shared" ca="1" si="11"/>
         <v>21</v>
       </c>
       <c r="N267" s="11" t="s">
@@ -20787,7 +21473,7 @@
       <c r="K268" s="11"/>
       <c r="L268" s="9"/>
       <c r="M268" s="11" t="str">
-        <f>IF(K268="","",IF(L268="","参照先未定義",_xlfn.XLOOKUP(L268,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N268" s="11" t="s">
@@ -20852,7 +21538,7 @@
       <c r="K269" s="11"/>
       <c r="L269" s="9"/>
       <c r="M269" s="11" t="str">
-        <f>IF(K269="","",IF(L269="","参照先未定義",_xlfn.XLOOKUP(L269,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N269" s="11" t="s">
@@ -20919,7 +21605,7 @@
       <c r="K270" s="11"/>
       <c r="L270" s="9"/>
       <c r="M270" s="11" t="str">
-        <f>IF(K270="","",IF(L270="","参照先未定義",_xlfn.XLOOKUP(L270,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N270" s="11" t="s">
@@ -20984,7 +21670,7 @@
       <c r="K271" s="11"/>
       <c r="L271" s="9"/>
       <c r="M271" s="11" t="str">
-        <f>IF(K271="","",IF(L271="","参照先未定義",_xlfn.XLOOKUP(L271,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N271" s="11" t="s">
@@ -21051,7 +21737,7 @@
       <c r="K272" s="11"/>
       <c r="L272" s="9"/>
       <c r="M272" s="11" t="str">
-        <f>IF(K272="","",IF(L272="","参照先未定義",_xlfn.XLOOKUP(L272,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N272" s="11" t="s">
@@ -21072,11 +21758,11 @@
         <v>46</v>
       </c>
       <c r="B273" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>profile_activity.profile_activity_uuid</v>
       </c>
       <c r="C273" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>272</v>
       </c>
       <c r="D273" s="11" t="s">
@@ -21117,7 +21803,7 @@
       <c r="K273" s="11"/>
       <c r="L273" s="9"/>
       <c r="M273" s="11" t="str">
-        <f>IF(K273="","",IF(L273="","参照先未定義",_xlfn.XLOOKUP(L273,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N273" s="11" t="s">
@@ -21140,11 +21826,11 @@
         <v>46</v>
       </c>
       <c r="B274" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>profile_activity.vtuber_profiles_id</v>
       </c>
       <c r="C274" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>273</v>
       </c>
       <c r="D274" s="11" t="str" cm="1">
@@ -21188,7 +21874,7 @@
         <v>509</v>
       </c>
       <c r="M274" s="11">
-        <f>IF(K274="","",IF(L274="","参照先未定義",_xlfn.XLOOKUP(L274,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="N274" s="11" t="s">
@@ -21211,11 +21897,11 @@
         <v>46</v>
       </c>
       <c r="B275" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="12"/>
         <v>profile_activity.activity</v>
       </c>
       <c r="C275" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>274</v>
       </c>
       <c r="D275" s="11" t="str" cm="1">
@@ -21255,7 +21941,7 @@
       <c r="K275" s="11"/>
       <c r="L275" s="9"/>
       <c r="M275" s="11" t="str">
-        <f>IF(K275="","",IF(L275="","参照先未定義",_xlfn.XLOOKUP(L275,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N275" s="11" t="s">
@@ -21324,7 +22010,7 @@
       <c r="K276" s="11"/>
       <c r="L276" s="9"/>
       <c r="M276" s="11" t="str">
-        <f>IF(K276="","",IF(L276="","参照先未定義",_xlfn.XLOOKUP(L276,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N276" s="11" t="s">
@@ -21389,7 +22075,7 @@
       <c r="K277" s="11"/>
       <c r="L277" s="9"/>
       <c r="M277" s="11" t="str">
-        <f>IF(K277="","",IF(L277="","参照先未定義",_xlfn.XLOOKUP(L277,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N277" s="11" t="s">
@@ -21456,7 +22142,7 @@
       <c r="K278" s="11"/>
       <c r="L278" s="9"/>
       <c r="M278" s="11" t="str">
-        <f>IF(K278="","",IF(L278="","参照先未定義",_xlfn.XLOOKUP(L278,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N278" s="11" t="s">
@@ -21521,7 +22207,7 @@
       <c r="K279" s="11"/>
       <c r="L279" s="9"/>
       <c r="M279" s="11" t="str">
-        <f>IF(K279="","",IF(L279="","参照先未定義",_xlfn.XLOOKUP(L279,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N279" s="11" t="s">
@@ -21588,7 +22274,7 @@
       <c r="K280" s="11"/>
       <c r="L280" s="9"/>
       <c r="M280" s="11" t="str">
-        <f>IF(K280="","",IF(L280="","参照先未定義",_xlfn.XLOOKUP(L280,B:B,C:C,"エラー")))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N280" s="11" t="s">
@@ -22917,4 +23603,1246 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527F880D-2464-4E30-ABEB-FCC49C30E780}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9015CB-442A-4E29-AB18-BB59E1AE0828}">
+  <dimension ref="A1:M33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="22.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>532</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="38" t="s">
+        <v>565</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>565</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>565</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>565</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>565</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>533</v>
+      </c>
+      <c r="J1" s="38" t="s">
+        <v>578</v>
+      </c>
+      <c r="K1" s="26" t="s">
+        <v>578</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>578</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
+        <v>536</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="23">
+        <f t="shared" ref="C2" si="0">IF(B1=C1,B2+1,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D2" s="23">
+        <f t="shared" ref="D2" si="1">IF(C1=D1,C2+1,1)</f>
+        <v>2</v>
+      </c>
+      <c r="E2" s="23">
+        <f t="shared" ref="E2" si="2">IF(D1=E1,D2+1,1)</f>
+        <v>3</v>
+      </c>
+      <c r="F2" s="23">
+        <f t="shared" ref="F2" si="3">IF(E1=F1,E2+1,1)</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="23">
+        <f t="shared" ref="G2:H2" si="4">IF(F1=G1,F2+1,1)</f>
+        <v>5</v>
+      </c>
+      <c r="H2" s="23">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I2" s="23">
+        <f t="shared" ref="I2:J2" si="5">IF(H1=I1,H2+1,1)</f>
+        <v>2</v>
+      </c>
+      <c r="J2" s="23">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K2" s="23">
+        <f t="shared" ref="K2" si="6">IF(J1=K1,J2+1,1)</f>
+        <v>2</v>
+      </c>
+      <c r="L2" s="23">
+        <f t="shared" ref="L2" si="7">IF(K1=L1,K2+1,1)</f>
+        <v>3</v>
+      </c>
+      <c r="M2" s="23">
+        <f t="shared" ref="M2" si="8">IF(L1=M1,L2+1,1)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>559</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>537</v>
+      </c>
+      <c r="C3" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="C3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>screen_word_uuid</v>
+      </c>
+      <c r="D3" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="D3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=D$1), D$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>language_physical_name</v>
+      </c>
+      <c r="E3" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="E3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=E$1), E$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>message_id</v>
+      </c>
+      <c r="F3" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="F3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=F$1), F$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>display_message</v>
+      </c>
+      <c r="G3" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="G3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=G$1), G$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>message_type</v>
+      </c>
+      <c r="H3" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="H3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=H$1), H$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>badge_uuid</v>
+      </c>
+      <c r="I3" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="I3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=I$1), I$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>badge_physical_name</v>
+      </c>
+      <c r="J3" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="J3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=J$1), J$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>language_uuid</v>
+      </c>
+      <c r="K3" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="K3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=K$1), K$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>language_physical_name</v>
+      </c>
+      <c r="L3" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="L3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=L$1), L$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>language_image</v>
+      </c>
+      <c r="M3" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="M3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>enable</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="27"/>
+      <c r="B4" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="C4" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="C4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>UUID</v>
+      </c>
+      <c r="D4" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="D4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=D$1), D$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>表示言語(物理名)</v>
+      </c>
+      <c r="E4" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="E4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=E$1), E$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>メッセージID</v>
+      </c>
+      <c r="F4" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="F4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=F$1), F$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>文言</v>
+      </c>
+      <c r="G4" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="G4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=G$1), G$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>文言種別</v>
+      </c>
+      <c r="H4" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="H4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=H$1), H$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>UUID</v>
+      </c>
+      <c r="I4" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="I4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=I$1), I$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>バッジ名(物理名)</v>
+      </c>
+      <c r="J4" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="J4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=J$1), J$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>UUID</v>
+      </c>
+      <c r="K4" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="K4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=K$1), K$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>表示言語(物理名)</v>
+      </c>
+      <c r="L4" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="L4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=L$1), L$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>言語画像</v>
+      </c>
+      <c r="M4" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="M4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>有効フラグ</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="27"/>
+      <c r="B5" s="24" t="s">
+        <v>535</v>
+      </c>
+      <c r="C5" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="C5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>uuid</v>
+      </c>
+      <c r="D5" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="D5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=D$1), D$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>uuid</v>
+      </c>
+      <c r="E5" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="E5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=E$1), E$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>uuid</v>
+      </c>
+      <c r="F5" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="F5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=F$1), F$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>text</v>
+      </c>
+      <c r="G5" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="G5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=G$1), G$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>enum</v>
+      </c>
+      <c r="H5" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="H5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=H$1), H$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>uuid</v>
+      </c>
+      <c r="I5" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="I5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=I$1), I$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>varchar(24)</v>
+      </c>
+      <c r="J5" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="J5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=J$1), J$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>uuid</v>
+      </c>
+      <c r="K5" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="K5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=K$1), K$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>varchar(16)</v>
+      </c>
+      <c r="L5" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="L5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=L$1), L$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>bigserial</v>
+      </c>
+      <c r="M5" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="M5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>boolean</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="27"/>
+      <c r="B6" s="24" t="s">
+        <v>581</v>
+      </c>
+      <c r="C6" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="D6" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="D6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=D$1), D$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="E6" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="E6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=E$1), E$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="F6" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="F6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=F$1), F$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="G6" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="G6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=G$1), G$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="H6" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="H6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=H$1), H$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="I6" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="I6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=I$1), I$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="J6" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="J6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=J$1), J$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="K6" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="K6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=K$1), K$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="L6" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="L6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=L$1), L$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="M6" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="M6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="27"/>
+      <c r="B7" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="C7" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="C7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="D7" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="D7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=D$1), D$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="E7" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="E7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=E$1), E$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="F7" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="F7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=F$1), F$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="G7" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="G7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=G$1), G$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="H7" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="H7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=H$1), H$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="I7" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="I7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=I$1), I$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="J7" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="J7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=J$1), J$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="K7" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="K7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=K$1), K$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="L7" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="L7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=L$1), L$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="M7" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="M7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="27"/>
+      <c r="B8" s="24" t="s">
+        <v>579</v>
+      </c>
+      <c r="C8" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="D8" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="D8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=D$1), D$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>language.language_uuid</v>
+      </c>
+      <c r="E8" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="E8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=E$1), E$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="F8" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="F8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=F$1), F$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="G8" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="G8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=G$1), G$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="H8" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="H8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=H$1), H$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="I8" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="I8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=I$1), I$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="J8" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="J8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=J$1), J$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="K8" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="K8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=K$1), K$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="L8" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="L8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=L$1), L$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="M8" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="M8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="27"/>
+      <c r="B9" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="C9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="D9" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="D9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=D$1), D$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="E9" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="E9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=E$1), E$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="F9" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="F9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=F$1), F$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="G9" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="G9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=G$1), G$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="H9" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="H9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=H$1), H$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="I9" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="I9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=I$1), I$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="J9" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="J9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=J$1), J$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="K9" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="K9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=K$1), K$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="L9" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="L9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=L$1), L$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="M9" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="M9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="27"/>
+      <c r="B10" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="D10" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="D10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=D$1), D$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="E10" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="E10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=E$1), E$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="F10" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="F10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=F$1), F$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="G10" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="G10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=G$1), G$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="H10" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="H10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=H$1), H$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="I10" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="I10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=I$1), I$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="J10" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="J10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=J$1), J$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="K10" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="K10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=K$1), K$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="L10" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="L10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=L$1), L$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="M10" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="M10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="27"/>
+      <c r="B11" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="C11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>gen_random_uuid()</v>
+      </c>
+      <c r="D11" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="D11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=D$1), D$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="E11" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="E11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=E$1), E$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="F11" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="F11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=F$1), F$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="G11" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="G11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=G$1), G$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="H11" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="H11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=H$1), H$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>gen_random_uuid()</v>
+      </c>
+      <c r="I11" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="I11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=I$1), I$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="J11" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="J11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=J$1), J$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>gen_random_uuid()</v>
+      </c>
+      <c r="K11" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="K11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=K$1), K$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="L11" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="L11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=L$1), L$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="M11" s="33" t="str" cm="1">
+        <f t="array" aca="1" ref="M11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>560</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>539</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>586</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>571</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>574</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>563</v>
+      </c>
+      <c r="J12" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="K12" s="34" t="s">
+        <v>583</v>
+      </c>
+      <c r="L12" s="34" t="s">
+        <v>585</v>
+      </c>
+      <c r="M12" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="27"/>
+      <c r="B13" s="25" t="s">
+        <v>540</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>586</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>575</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>562</v>
+      </c>
+      <c r="J13" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="K13" s="34" t="s">
+        <v>584</v>
+      </c>
+      <c r="L13" s="34" t="s">
+        <v>585</v>
+      </c>
+      <c r="M13" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="27"/>
+      <c r="B14" s="25" t="s">
+        <v>541</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>586</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>573</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>576</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>561</v>
+      </c>
+      <c r="J14" s="39"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="27"/>
+      <c r="B15" s="25" t="s">
+        <v>542</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>587</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>571</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>574</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="27"/>
+      <c r="B16" s="25" t="s">
+        <v>543</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>587</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>575</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="27"/>
+      <c r="B17" s="25" t="s">
+        <v>544</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>587</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>573</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>576</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="27"/>
+      <c r="B18" s="25" t="s">
+        <v>545</v>
+      </c>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="27"/>
+      <c r="B19" s="25" t="s">
+        <v>546</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="27"/>
+      <c r="B20" s="25" t="s">
+        <v>547</v>
+      </c>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="27"/>
+      <c r="B21" s="25" t="s">
+        <v>548</v>
+      </c>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="27"/>
+      <c r="B22" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="27"/>
+      <c r="B23" s="25" t="s">
+        <v>550</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="27"/>
+      <c r="B24" s="25" t="s">
+        <v>551</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="27"/>
+      <c r="B25" s="25" t="s">
+        <v>552</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="27"/>
+      <c r="B26" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="27"/>
+      <c r="B27" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="27"/>
+      <c r="B28" s="25" t="s">
+        <v>555</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="27"/>
+      <c r="B29" s="25" t="s">
+        <v>556</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="27"/>
+      <c r="B30" s="25" t="s">
+        <v>557</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="27"/>
+      <c r="B31" s="25" t="s">
+        <v>558</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+    </row>
+    <row r="33" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="A12:A31"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A51AEB3-80E9-467E-8003-42277CA783CA}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>532</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="37" t="s">
+        <v>568</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>568</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>568</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>568</v>
+      </c>
+      <c r="G1" s="36" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
+        <v>536</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="23">
+        <f t="shared" ref="C2:G2" si="0">IF(B1=C1,B2+1,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D2" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E2" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F2" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G2" s="23">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>559</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>537</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="27"/>
+      <c r="B4" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="27"/>
+      <c r="B5" s="24" t="s">
+        <v>535</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="27"/>
+      <c r="B6" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="27"/>
+      <c r="B7" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>566</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>566</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>566</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>566</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="27"/>
+      <c r="B8" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="55.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="35" t="s">
+        <v>560</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>539</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>564</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>570</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>564</v>
+      </c>
+      <c r="G9" s="18">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>569</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:A8"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/.design/DB/DB設計.xlsx
+++ b/.design/DB/DB設計.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevelopmentProjects\vtuber-meikan\.design\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6BC254-4A34-47BF-B8CE-3378846D6A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1DF6CD-6C4C-419C-97EA-AC3AE80DED30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テーブル一覧" sheetId="1" r:id="rId1"/>
@@ -4645,7 +4645,7 @@
         <v>51</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11">
+      <c r="P12" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q12" s="11"/>
@@ -5235,7 +5235,7 @@
         <v>51</v>
       </c>
       <c r="O21" s="11"/>
-      <c r="P21" s="11">
+      <c r="P21" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q21" s="11"/>
@@ -5699,7 +5699,7 @@
         <v>51</v>
       </c>
       <c r="O28" s="11"/>
-      <c r="P28" s="11">
+      <c r="P28" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q28" s="11"/>
@@ -6165,7 +6165,7 @@
         <v>51</v>
       </c>
       <c r="O35" s="11"/>
-      <c r="P35" s="11">
+      <c r="P35" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q35" s="11"/>
@@ -6629,7 +6629,7 @@
         <v>51</v>
       </c>
       <c r="O42" s="11"/>
-      <c r="P42" s="11">
+      <c r="P42" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q42" s="11"/>
@@ -7286,7 +7286,7 @@
         <v>51</v>
       </c>
       <c r="O52" s="11"/>
-      <c r="P52" s="11">
+      <c r="P52" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q52" s="11"/>
@@ -7943,7 +7943,7 @@
         <v>51</v>
       </c>
       <c r="O62" s="11"/>
-      <c r="P62" s="11">
+      <c r="P62" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q62" s="11"/>
@@ -8797,7 +8797,7 @@
         <v>51</v>
       </c>
       <c r="O75" s="11"/>
-      <c r="P75" s="11">
+      <c r="P75" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q75" s="11"/>
@@ -9519,7 +9519,7 @@
         <v>51</v>
       </c>
       <c r="O86" s="11"/>
-      <c r="P86" s="11">
+      <c r="P86" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q86" s="11"/>
@@ -10044,7 +10044,7 @@
         <v>51</v>
       </c>
       <c r="O94" s="11"/>
-      <c r="P94" s="11">
+      <c r="P94" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q94" s="11"/>
@@ -10569,7 +10569,7 @@
         <v>51</v>
       </c>
       <c r="O102" s="11"/>
-      <c r="P102" s="11">
+      <c r="P102" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q102" s="11"/>
@@ -10832,7 +10832,7 @@
         <v>51</v>
       </c>
       <c r="O106" s="11"/>
-      <c r="P106" s="11">
+      <c r="P106" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q106" s="11"/>
@@ -11161,7 +11161,7 @@
         <v>51</v>
       </c>
       <c r="O111" s="11"/>
-      <c r="P111" s="11">
+      <c r="P111" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q111" s="11"/>
@@ -11814,7 +11814,7 @@
         <v>51</v>
       </c>
       <c r="O121" s="11"/>
-      <c r="P121" s="11">
+      <c r="P121" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q121" s="11"/>
@@ -12087,7 +12087,7 @@
         <v>51</v>
       </c>
       <c r="O125" s="11"/>
-      <c r="P125" s="11">
+      <c r="P125" s="11" t="b">
         <v>1</v>
       </c>
       <c r="Q125" s="11"/>
@@ -12152,7 +12152,7 @@
         <v>51</v>
       </c>
       <c r="O126" s="11"/>
-      <c r="P126" s="11">
+      <c r="P126" s="11" t="b">
         <v>1</v>
       </c>
       <c r="Q126" s="11"/>
@@ -12481,7 +12481,7 @@
         <v>51</v>
       </c>
       <c r="O131" s="11"/>
-      <c r="P131" s="11">
+      <c r="P131" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q131" s="11"/>
@@ -13209,7 +13209,7 @@
         <v>51</v>
       </c>
       <c r="O142" s="11"/>
-      <c r="P142" s="11">
+      <c r="P142" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q142" s="11"/>
@@ -13673,7 +13673,7 @@
         <v>51</v>
       </c>
       <c r="O149" s="11"/>
-      <c r="P149" s="11">
+      <c r="P149" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q149" s="11"/>
@@ -13999,7 +13999,7 @@
         <v>51</v>
       </c>
       <c r="O154" s="11"/>
-      <c r="P154" s="11">
+      <c r="P154" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q154" s="11" t="s">
@@ -14598,7 +14598,7 @@
         <v>51</v>
       </c>
       <c r="O163" s="11"/>
-      <c r="P163" s="11">
+      <c r="P163" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q163" s="11"/>
@@ -15062,7 +15062,7 @@
         <v>51</v>
       </c>
       <c r="O170" s="11"/>
-      <c r="P170" s="11">
+      <c r="P170" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q170" s="11"/>
@@ -15526,7 +15526,7 @@
         <v>51</v>
       </c>
       <c r="O177" s="11"/>
-      <c r="P177" s="11">
+      <c r="P177" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q177" s="11"/>
@@ -16553,7 +16553,7 @@
         <v>51</v>
       </c>
       <c r="O193" s="11"/>
-      <c r="P193" s="11">
+      <c r="P193" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q193" s="11"/>
@@ -17513,7 +17513,7 @@
         <v>51</v>
       </c>
       <c r="O208" s="11"/>
-      <c r="P208" s="11">
+      <c r="P208" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q208" s="11"/>
@@ -17977,7 +17977,7 @@
         <v>51</v>
       </c>
       <c r="O215" s="11"/>
-      <c r="P215" s="11">
+      <c r="P215" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q215" s="11"/>
@@ -18645,7 +18645,7 @@
         <v>51</v>
       </c>
       <c r="O225" s="11"/>
-      <c r="P225" s="11">
+      <c r="P225" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q225" s="11"/>
@@ -19237,7 +19237,7 @@
         <v>51</v>
       </c>
       <c r="O234" s="11"/>
-      <c r="P234" s="11">
+      <c r="P234" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q234" s="11"/>
@@ -19839,7 +19839,7 @@
         <v>51</v>
       </c>
       <c r="O243" s="11"/>
-      <c r="P243" s="11">
+      <c r="P243" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q243" s="11"/>
@@ -21203,7 +21203,7 @@
         <v>51</v>
       </c>
       <c r="O264" s="11"/>
-      <c r="P264" s="11">
+      <c r="P264" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q264" s="11"/>
@@ -21744,7 +21744,7 @@
         <v>51</v>
       </c>
       <c r="O272" s="11"/>
-      <c r="P272" s="11">
+      <c r="P272" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q272" s="11"/>
@@ -22281,7 +22281,7 @@
         <v>51</v>
       </c>
       <c r="O280" s="11"/>
-      <c r="P280" s="11">
+      <c r="P280" s="11" t="b">
         <v>0</v>
       </c>
       <c r="Q280" s="11"/>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M11" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="M11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
-        <v>0</v>
+        <v>FALSE</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">

--- a/.design/DB/DB設計.xlsx
+++ b/.design/DB/DB設計.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevelopmentProjects\vtuber-meikan\.design\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1DF6CD-6C4C-419C-97EA-AC3AE80DED30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0D9F5D-A609-4188-B6AD-F47D699DC18F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2311" uniqueCount="586">
   <si>
     <t>設計完了</t>
   </si>
@@ -1603,14 +1603,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>"default"</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>"japan"</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>vtuber_profiles_id</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -1766,14 +1758,6 @@
   </si>
   <si>
     <t>管理者向けのため、日本語固定</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>uuid</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>language.language_uuid</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -2363,6 +2347,14 @@
       </rPr>
       <t>UUID}</t>
     </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>"default"のUUID</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>"japan"のUUID</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -3410,7 +3402,7 @@
       </c>
       <c r="E15" s="3">
         <f ca="1">SUMIF(テーブル定義_一覧!D:D,C15,テーブル定義_一覧!I:I)</f>
-        <v>1048</v>
+        <v>1176</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
@@ -3822,7 +3814,7 @@
         <v>8</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H29" s="6"/>
     </row>
@@ -3949,7 +3941,7 @@
         <v>vtuber_profiles_uuid</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>49</v>
@@ -3980,10 +3972,10 @@
         <v/>
       </c>
       <c r="N2" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P2" s="11" t="s">
         <v>52</v>
@@ -4111,7 +4103,7 @@
         <v>51</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M4" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -4178,7 +4170,7 @@
         <v>51</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -4222,7 +4214,7 @@
         <v>73</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I6" s="11">
         <f>_xlfn.LET(
@@ -4308,7 +4300,7 @@
         <v>51</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -4352,7 +4344,7 @@
         <v>111</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I8" s="11">
         <f>_xlfn.LET(
@@ -4484,7 +4476,7 @@
         <v>118</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="I10" s="11">
         <f>_xlfn.LET(
@@ -4616,7 +4608,7 @@
         <v>122</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I12" s="11">
         <f>_xlfn.LET(
@@ -4708,10 +4700,10 @@
         <v/>
       </c>
       <c r="N13" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P13" s="11" t="s">
         <v>52</v>
@@ -4839,7 +4831,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="M15" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -4942,7 +4934,7 @@
         <v>111</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I17" s="11">
         <f>_xlfn.LET(
@@ -5074,7 +5066,7 @@
         <v>118</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I19" s="11">
         <f>_xlfn.LET(
@@ -5206,7 +5198,7 @@
         <v>122</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I21" s="11">
         <f>_xlfn.LET(
@@ -5298,10 +5290,10 @@
         <v/>
       </c>
       <c r="N22" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P22" s="11" t="s">
         <v>52</v>
@@ -5406,7 +5398,7 @@
         <v>111</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I24" s="11">
         <f>_xlfn.LET(
@@ -5538,7 +5530,7 @@
         <v>118</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I26" s="11">
         <f>_xlfn.LET(
@@ -5670,7 +5662,7 @@
         <v>122</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I28" s="11">
         <f>_xlfn.LET(
@@ -5762,10 +5754,10 @@
         <v/>
       </c>
       <c r="N29" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P29" s="11" t="s">
         <v>52</v>
@@ -5842,7 +5834,7 @@
         <v>51</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5872,7 +5864,7 @@
         <v>111</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I31" s="11">
         <f>_xlfn.LET(
@@ -6004,7 +5996,7 @@
         <v>118</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I33" s="11">
         <f>_xlfn.LET(
@@ -6136,7 +6128,7 @@
         <v>122</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I35" s="11">
         <f>_xlfn.LET(
@@ -6228,10 +6220,10 @@
         <v/>
       </c>
       <c r="N36" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O36" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P36" s="11" t="s">
         <v>52</v>
@@ -6306,7 +6298,7 @@
       <c r="S37" s="9"/>
       <c r="T37" s="9"/>
       <c r="U37" s="11" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6336,7 +6328,7 @@
         <v>111</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I38" s="11">
         <f>_xlfn.LET(
@@ -6468,7 +6460,7 @@
         <v>118</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I40" s="11">
         <f>_xlfn.LET(
@@ -6600,7 +6592,7 @@
         <v>122</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I42" s="11">
         <f>_xlfn.LET(
@@ -6692,10 +6684,10 @@
         <v/>
       </c>
       <c r="N43" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O43" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P43" s="11" t="s">
         <v>52</v>
@@ -6756,7 +6748,7 @@
         <v>51</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M44" s="11">
         <f t="shared" si="1"/>
@@ -6823,7 +6815,7 @@
         <v>51</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="M45" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -6894,14 +6886,14 @@
       </c>
       <c r="N46" s="11"/>
       <c r="O46" s="11"/>
-      <c r="P46" s="11" t="s">
-        <v>144</v>
-      </c>
+      <c r="P46" s="11"/>
       <c r="Q46" s="11"/>
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
       <c r="T46" s="9"/>
-      <c r="U46" s="11"/>
+      <c r="U46" s="11" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="47" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
@@ -6993,7 +6985,7 @@
         <v>111</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I48" s="11">
         <f>_xlfn.LET(
@@ -7125,7 +7117,7 @@
         <v>118</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I50" s="11">
         <f>_xlfn.LET(
@@ -7257,7 +7249,7 @@
         <v>122</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I52" s="11">
         <f>_xlfn.LET(
@@ -7349,10 +7341,10 @@
         <v/>
       </c>
       <c r="N53" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O53" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P53" s="11" t="s">
         <v>52</v>
@@ -7413,7 +7405,7 @@
         <v>51</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M54" s="11">
         <f t="shared" si="1"/>
@@ -7480,7 +7472,7 @@
         <v>51</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M55" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -7587,7 +7579,7 @@
         <v>152</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I57" s="11">
         <f>_xlfn.LET(
@@ -7650,7 +7642,7 @@
         <v>111</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I58" s="11">
         <f>_xlfn.LET(
@@ -7782,7 +7774,7 @@
         <v>118</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I60" s="11">
         <f>_xlfn.LET(
@@ -7914,7 +7906,7 @@
         <v>122</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I62" s="11">
         <f>_xlfn.LET(
@@ -8006,10 +7998,10 @@
         <v/>
       </c>
       <c r="N63" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O63" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P63" s="11" t="s">
         <v>52</v>
@@ -8070,7 +8062,7 @@
         <v>51</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M64" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -8137,7 +8129,7 @@
         <v>51</v>
       </c>
       <c r="L65" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M65" s="11">
         <f t="shared" si="1"/>
@@ -8204,7 +8196,7 @@
         <v>51</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="M66" s="11">
         <f t="shared" ref="M66:M129" ca="1" si="4">_xlfn.SINGLE(IF(K66="","",IF(L66="","参照先未定義",_xlfn.XLOOKUP(L66,B:B,C:C,"エラー"))))</f>
@@ -8374,7 +8366,7 @@
         <v>161</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I69" s="11">
         <f>_xlfn.LET(
@@ -8504,7 +8496,7 @@
         <v>111</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I71" s="11">
         <f>_xlfn.LET(
@@ -8636,7 +8628,7 @@
         <v>118</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I73" s="11">
         <f>_xlfn.LET(
@@ -8768,7 +8760,7 @@
         <v>122</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I75" s="11">
         <f>_xlfn.LET(
@@ -8860,10 +8852,10 @@
         <v/>
       </c>
       <c r="N76" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O76" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P76" s="11" t="s">
         <v>52</v>
@@ -9119,7 +9111,7 @@
         <v>51</v>
       </c>
       <c r="L80" s="9" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="M80" s="11">
         <f t="shared" ca="1" si="4"/>
@@ -9184,7 +9176,7 @@
         <v>51</v>
       </c>
       <c r="L81" s="9" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="M81" s="11">
         <f t="shared" ca="1" si="4"/>
@@ -9226,7 +9218,7 @@
         <v>111</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I82" s="11">
         <f>_xlfn.LET(
@@ -9358,7 +9350,7 @@
         <v>118</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I84" s="11">
         <f>_xlfn.LET(
@@ -9490,7 +9482,7 @@
         <v>122</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I86" s="11">
         <f>_xlfn.LET(
@@ -9582,10 +9574,10 @@
         <v/>
       </c>
       <c r="N87" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O87" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P87" s="11" t="s">
         <v>52</v>
@@ -9721,7 +9713,7 @@
       <c r="S89" s="9"/>
       <c r="T89" s="9"/>
       <c r="U89" s="11" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="90" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9751,7 +9743,7 @@
         <v>111</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I90" s="11">
         <f>_xlfn.LET(
@@ -9883,7 +9875,7 @@
         <v>118</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I92" s="11">
         <f>_xlfn.LET(
@@ -10015,7 +10007,7 @@
         <v>122</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I94" s="11">
         <f>_xlfn.LET(
@@ -10107,10 +10099,10 @@
         <v/>
       </c>
       <c r="N95" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O95" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P95" s="11" t="s">
         <v>52</v>
@@ -10246,7 +10238,7 @@
       <c r="S97" s="9"/>
       <c r="T97" s="9"/>
       <c r="U97" s="11" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="98" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10276,7 +10268,7 @@
         <v>111</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I98" s="11">
         <f>_xlfn.LET(
@@ -10408,7 +10400,7 @@
         <v>118</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I100" s="11">
         <f>_xlfn.LET(
@@ -10540,7 +10532,7 @@
         <v>122</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I102" s="11">
         <f>_xlfn.LET(
@@ -10632,10 +10624,10 @@
         <v/>
       </c>
       <c r="N103" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O103" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P103" s="11" t="s">
         <v>52</v>
@@ -10710,7 +10702,7 @@
       <c r="S104" s="9"/>
       <c r="T104" s="9"/>
       <c r="U104" s="11" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10803,7 +10795,7 @@
         <v>193</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I106" s="11">
         <f>_xlfn.LET(
@@ -10868,7 +10860,7 @@
         <v>111</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I107" s="11">
         <f>_xlfn.LET(
@@ -11000,7 +10992,7 @@
         <v>118</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I109" s="11">
         <f>_xlfn.LET(
@@ -11132,7 +11124,7 @@
         <v>122</v>
       </c>
       <c r="H111" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I111" s="11">
         <f>_xlfn.LET(
@@ -11224,10 +11216,10 @@
         <v/>
       </c>
       <c r="N112" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O112" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P112" s="11" t="s">
         <v>52</v>
@@ -11288,7 +11280,7 @@
         <v>51</v>
       </c>
       <c r="L113" s="9" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M113" s="11">
         <f t="shared" ca="1" si="4"/>
@@ -11359,7 +11351,7 @@
       <c r="O114" s="11"/>
       <c r="P114" s="11"/>
       <c r="Q114" s="11" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="R114" s="9"/>
       <c r="S114" s="9"/>
@@ -11422,7 +11414,7 @@
       <c r="O115" s="11"/>
       <c r="P115" s="11"/>
       <c r="Q115" s="11" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="R115" s="9"/>
       <c r="S115" s="9"/>
@@ -11450,13 +11442,13 @@
         <v>画面文言</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="G116" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="H116" s="11" t="s">
         <v>523</v>
-      </c>
-      <c r="H116" s="11" t="s">
-        <v>527</v>
       </c>
       <c r="I116" s="11" t="str">
         <f>_xlfn.LET(
@@ -11485,13 +11477,13 @@
       <c r="O116" s="11"/>
       <c r="P116" s="11"/>
       <c r="Q116" s="11" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="R116" s="9"/>
       <c r="S116" s="9"/>
       <c r="T116" s="9"/>
       <c r="U116" s="11" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="117" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11521,7 +11513,7 @@
         <v>111</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I117" s="11">
         <f>_xlfn.LET(
@@ -11653,7 +11645,7 @@
         <v>118</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I119" s="11">
         <f>_xlfn.LET(
@@ -11785,7 +11777,7 @@
         <v>122</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I121" s="11">
         <f>_xlfn.LET(
@@ -11877,10 +11869,10 @@
         <v/>
       </c>
       <c r="N122" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O122" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P122" s="11" t="s">
         <v>52</v>
@@ -11918,7 +11910,7 @@
         <v>204</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>521</v>
+        <v>71</v>
       </c>
       <c r="I123" s="11">
         <f>_xlfn.LET(
@@ -11934,18 +11926,14 @@
         )
     )
 )</f>
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="J123" s="11"/>
-      <c r="K123" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="L123" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="M123" s="11">
-        <f t="shared" ca="1" si="4"/>
-        <v>102</v>
+      <c r="K123" s="11"/>
+      <c r="L123" s="9"/>
+      <c r="M123" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N123" s="11" t="s">
         <v>475</v>
@@ -12010,7 +11998,7 @@
         <v>51</v>
       </c>
       <c r="L124" s="9" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="M124" s="11">
         <f t="shared" ca="1" si="4"/>
@@ -12058,7 +12046,7 @@
         <v>209</v>
       </c>
       <c r="H125" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I125" s="11">
         <f>_xlfn.LET(
@@ -12123,7 +12111,7 @@
         <v>211</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I126" s="11">
         <f>_xlfn.LET(
@@ -12188,7 +12176,7 @@
         <v>111</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I127" s="11">
         <f>_xlfn.LET(
@@ -12320,7 +12308,7 @@
         <v>118</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I129" s="11">
         <f>_xlfn.LET(
@@ -12452,7 +12440,7 @@
         <v>122</v>
       </c>
       <c r="H131" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I131" s="11">
         <f>_xlfn.LET(
@@ -12544,10 +12532,10 @@
         <v/>
       </c>
       <c r="N132" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O132" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P132" s="11" t="s">
         <v>52</v>
@@ -12608,7 +12596,7 @@
         <v>51</v>
       </c>
       <c r="L133" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M133" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -12673,7 +12661,7 @@
         <v>51</v>
       </c>
       <c r="L134" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M134" s="11">
         <f t="shared" si="7"/>
@@ -12740,7 +12728,7 @@
         <v>51</v>
       </c>
       <c r="L135" s="9" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M135" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -12851,7 +12839,7 @@
         <v>219</v>
       </c>
       <c r="H137" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I137" s="11">
         <f>_xlfn.LET(
@@ -12916,7 +12904,7 @@
         <v>111</v>
       </c>
       <c r="H138" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I138" s="11">
         <f>_xlfn.LET(
@@ -13048,7 +13036,7 @@
         <v>118</v>
       </c>
       <c r="H140" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I140" s="11">
         <f>_xlfn.LET(
@@ -13180,7 +13168,7 @@
         <v>122</v>
       </c>
       <c r="H142" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I142" s="11">
         <f>_xlfn.LET(
@@ -13272,10 +13260,10 @@
         <v/>
       </c>
       <c r="N143" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O143" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P143" s="11" t="s">
         <v>52</v>
@@ -13350,7 +13338,7 @@
       <c r="S144" s="9"/>
       <c r="T144" s="9"/>
       <c r="U144" s="11" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="145" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13380,7 +13368,7 @@
         <v>111</v>
       </c>
       <c r="H145" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I145" s="11">
         <f>_xlfn.LET(
@@ -13512,7 +13500,7 @@
         <v>118</v>
       </c>
       <c r="H147" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I147" s="11">
         <f>_xlfn.LET(
@@ -13644,7 +13632,7 @@
         <v>122</v>
       </c>
       <c r="H149" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I149" s="11">
         <f>_xlfn.LET(
@@ -13736,10 +13724,10 @@
         <v/>
       </c>
       <c r="N150" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O150" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P150" s="11" t="s">
         <v>52</v>
@@ -13928,7 +13916,7 @@
         <v>51</v>
       </c>
       <c r="L153" s="9" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="M153" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -13970,7 +13958,7 @@
         <v>226</v>
       </c>
       <c r="H154" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I154" s="11">
         <f>_xlfn.LET(
@@ -14060,7 +14048,7 @@
         <v>51</v>
       </c>
       <c r="L155" s="9" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="M155" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -14102,7 +14090,7 @@
         <v>231</v>
       </c>
       <c r="H156" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I156" s="11">
         <f>_xlfn.LET(
@@ -14190,7 +14178,7 @@
         <v>51</v>
       </c>
       <c r="L157" s="9" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="M157" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -14201,7 +14189,7 @@
       </c>
       <c r="O157" s="11"/>
       <c r="P157" s="11" t="s">
-        <v>478</v>
+        <v>584</v>
       </c>
       <c r="Q157" s="11"/>
       <c r="R157" s="9"/>
@@ -14259,7 +14247,7 @@
         <v>51</v>
       </c>
       <c r="L158" s="9" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M158" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -14270,7 +14258,7 @@
       </c>
       <c r="O158" s="11"/>
       <c r="P158" s="11" t="s">
-        <v>479</v>
+        <v>585</v>
       </c>
       <c r="Q158" s="11"/>
       <c r="R158" s="9"/>
@@ -14305,7 +14293,7 @@
         <v>111</v>
       </c>
       <c r="H159" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I159" s="11">
         <f>_xlfn.LET(
@@ -14437,7 +14425,7 @@
         <v>118</v>
       </c>
       <c r="H161" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I161" s="11">
         <f>_xlfn.LET(
@@ -14569,7 +14557,7 @@
         <v>122</v>
       </c>
       <c r="H163" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I163" s="11">
         <f>_xlfn.LET(
@@ -14661,10 +14649,10 @@
         <v/>
       </c>
       <c r="N164" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O164" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P164" s="11" t="s">
         <v>52</v>
@@ -14739,7 +14727,7 @@
       <c r="S165" s="9"/>
       <c r="T165" s="9"/>
       <c r="U165" s="11" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="166" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14769,7 +14757,7 @@
         <v>111</v>
       </c>
       <c r="H166" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I166" s="11">
         <f>_xlfn.LET(
@@ -14901,7 +14889,7 @@
         <v>118</v>
       </c>
       <c r="H168" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I168" s="11">
         <f>_xlfn.LET(
@@ -15033,7 +15021,7 @@
         <v>122</v>
       </c>
       <c r="H170" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I170" s="11">
         <f>_xlfn.LET(
@@ -15125,10 +15113,10 @@
         <v/>
       </c>
       <c r="N171" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O171" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P171" s="11" t="s">
         <v>52</v>
@@ -15203,7 +15191,7 @@
       <c r="S172" s="9"/>
       <c r="T172" s="9"/>
       <c r="U172" s="11" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="173" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15233,7 +15221,7 @@
         <v>111</v>
       </c>
       <c r="H173" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I173" s="11">
         <f>_xlfn.LET(
@@ -15365,7 +15353,7 @@
         <v>118</v>
       </c>
       <c r="H175" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I175" s="11">
         <f>_xlfn.LET(
@@ -15497,7 +15485,7 @@
         <v>122</v>
       </c>
       <c r="H177" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I177" s="11">
         <f>_xlfn.LET(
@@ -15548,7 +15536,7 @@
         <v>177</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E178" s="11" t="s">
         <v>239</v>
@@ -15589,10 +15577,10 @@
         <v/>
       </c>
       <c r="N178" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O178" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P178" s="11" t="s">
         <v>52</v>
@@ -15718,7 +15706,7 @@
         <v>51</v>
       </c>
       <c r="L180" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M180" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -16260,7 +16248,7 @@
         <v>111</v>
       </c>
       <c r="H189" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I189" s="11">
         <f>_xlfn.LET(
@@ -16392,7 +16380,7 @@
         <v>118</v>
       </c>
       <c r="H191" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I191" s="11">
         <f>_xlfn.LET(
@@ -16524,7 +16512,7 @@
         <v>122</v>
       </c>
       <c r="H193" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I193" s="11">
         <f>_xlfn.LET(
@@ -16616,10 +16604,10 @@
         <v/>
       </c>
       <c r="N194" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O194" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P194" s="11" t="s">
         <v>52</v>
@@ -17220,7 +17208,7 @@
         <v>111</v>
       </c>
       <c r="H204" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I204" s="11">
         <f>_xlfn.LET(
@@ -17352,7 +17340,7 @@
         <v>118</v>
       </c>
       <c r="H206" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I206" s="11">
         <f>_xlfn.LET(
@@ -17484,7 +17472,7 @@
         <v>122</v>
       </c>
       <c r="H208" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I208" s="11">
         <f>_xlfn.LET(
@@ -17576,10 +17564,10 @@
         <v/>
       </c>
       <c r="N209" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O209" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P209" s="11" t="s">
         <v>52</v>
@@ -17684,7 +17672,7 @@
         <v>111</v>
       </c>
       <c r="H211" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I211" s="11">
         <f>_xlfn.LET(
@@ -17816,7 +17804,7 @@
         <v>118</v>
       </c>
       <c r="H213" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I213" s="11">
         <f>_xlfn.LET(
@@ -17948,7 +17936,7 @@
         <v>122</v>
       </c>
       <c r="H215" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I215" s="11">
         <f>_xlfn.LET(
@@ -17999,7 +17987,7 @@
         <v>215</v>
       </c>
       <c r="D216" s="11" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E216" s="11" t="s">
         <v>104</v>
@@ -18040,10 +18028,10 @@
         <v/>
       </c>
       <c r="N216" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O216" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P216" s="11" t="s">
         <v>52</v>
@@ -18067,14 +18055,14 @@
         <v>216</v>
       </c>
       <c r="D217" s="11" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E217" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E217" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>いいね</v>
       </c>
       <c r="F217" s="11" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G217" s="11" t="s">
         <v>264</v>
@@ -18103,7 +18091,7 @@
         <v>464</v>
       </c>
       <c r="L217" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M217" s="11">
         <f t="shared" ca="1" si="9"/>
@@ -18113,11 +18101,11 @@
         <v>51</v>
       </c>
       <c r="O217" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P217" s="11"/>
       <c r="Q217" s="11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="R217" s="9"/>
       <c r="S217" s="9"/>
@@ -18145,7 +18133,7 @@
         <v>いいね</v>
       </c>
       <c r="F218" s="11" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="G218" s="11" t="s">
         <v>265</v>
@@ -18174,7 +18162,7 @@
         <v>464</v>
       </c>
       <c r="L218" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M218" s="11">
         <f t="shared" ca="1" si="9"/>
@@ -18184,11 +18172,11 @@
         <v>51</v>
       </c>
       <c r="O218" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P218" s="11"/>
       <c r="Q218" s="11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="R218" s="9"/>
       <c r="S218" s="9"/>
@@ -18216,13 +18204,13 @@
         <v>いいね</v>
       </c>
       <c r="F219" s="11" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G219" s="11" t="s">
         <v>266</v>
       </c>
       <c r="H219" s="11" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="I219" s="11" t="str">
         <f>_xlfn.LET(
@@ -18251,11 +18239,11 @@
         <v>51</v>
       </c>
       <c r="O219" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P219" s="11"/>
       <c r="Q219" s="11" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="R219" s="9"/>
       <c r="S219" s="9"/>
@@ -18283,13 +18271,13 @@
         <v>いいね</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G220" s="11" t="s">
         <v>267</v>
       </c>
       <c r="H220" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I220" s="11">
         <f>_xlfn.LET(
@@ -18352,7 +18340,7 @@
         <v>111</v>
       </c>
       <c r="H221" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I221" s="11">
         <f>_xlfn.LET(
@@ -18484,7 +18472,7 @@
         <v>118</v>
       </c>
       <c r="H223" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I223" s="11">
         <f>_xlfn.LET(
@@ -18616,7 +18604,7 @@
         <v>122</v>
       </c>
       <c r="H225" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I225" s="11">
         <f>_xlfn.LET(
@@ -18708,10 +18696,10 @@
         <v/>
       </c>
       <c r="N226" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O226" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P226" s="11" t="s">
         <v>52</v>
@@ -18837,7 +18825,7 @@
         <v>51</v>
       </c>
       <c r="L228" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M228" s="11">
         <f t="shared" si="9"/>
@@ -18944,7 +18932,7 @@
         <v>111</v>
       </c>
       <c r="H230" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I230" s="11">
         <f>_xlfn.LET(
@@ -19076,7 +19064,7 @@
         <v>118</v>
       </c>
       <c r="H232" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I232" s="11">
         <f>_xlfn.LET(
@@ -19208,7 +19196,7 @@
         <v>122</v>
       </c>
       <c r="H234" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I234" s="11">
         <f>_xlfn.LET(
@@ -19300,10 +19288,10 @@
         <v/>
       </c>
       <c r="N235" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O235" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P235" s="11" t="s">
         <v>52</v>
@@ -19364,7 +19352,7 @@
         <v>51</v>
       </c>
       <c r="L236" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M236" s="11">
         <f t="shared" si="9"/>
@@ -19374,7 +19362,7 @@
         <v>51</v>
       </c>
       <c r="O236" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P236" s="11"/>
       <c r="Q236" s="11" t="s">
@@ -19435,7 +19423,7 @@
         <v>51</v>
       </c>
       <c r="L237" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M237" s="11">
         <f t="shared" si="9"/>
@@ -19445,7 +19433,7 @@
         <v>51</v>
       </c>
       <c r="O237" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P237" s="11"/>
       <c r="Q237" s="11" t="s">
@@ -19546,7 +19534,7 @@
         <v>111</v>
       </c>
       <c r="H239" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I239" s="11">
         <f>_xlfn.LET(
@@ -19678,7 +19666,7 @@
         <v>118</v>
       </c>
       <c r="H241" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I241" s="11">
         <f>_xlfn.LET(
@@ -19810,7 +19798,7 @@
         <v>122</v>
       </c>
       <c r="H243" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I243" s="11">
         <f>_xlfn.LET(
@@ -19902,10 +19890,10 @@
         <v/>
       </c>
       <c r="N244" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O244" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P244" s="11" t="s">
         <v>52</v>
@@ -19937,7 +19925,7 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G245" s="11" t="s">
         <v>54</v>
@@ -19966,7 +19954,7 @@
         <v>461</v>
       </c>
       <c r="L245" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M245" s="11">
         <f t="shared" si="9"/>
@@ -19976,11 +19964,11 @@
         <v>51</v>
       </c>
       <c r="O245" s="11" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="P245" s="11"/>
       <c r="Q245" s="11" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="R245" s="9"/>
       <c r="S245" s="9"/>
@@ -20037,7 +20025,7 @@
         <v>464</v>
       </c>
       <c r="L246" s="9" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M246" s="11">
         <f t="shared" ref="M246:M280" ca="1" si="11">IF(K246="","",IF(L246="","参照先未定義",_xlfn.XLOOKUP(L246,B:B,C:C,"エラー")))</f>
@@ -20047,11 +20035,11 @@
         <v>51</v>
       </c>
       <c r="O246" s="11" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="P246" s="11"/>
       <c r="Q246" s="11" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="R246" s="9"/>
       <c r="S246" s="9"/>
@@ -20910,7 +20898,7 @@
         <v>111</v>
       </c>
       <c r="H260" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I260" s="11">
         <f>_xlfn.LET(
@@ -21042,7 +21030,7 @@
         <v>118</v>
       </c>
       <c r="H262" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I262" s="11">
         <f>_xlfn.LET(
@@ -21174,7 +21162,7 @@
         <v>122</v>
       </c>
       <c r="H264" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I264" s="11">
         <f>_xlfn.LET(
@@ -21266,10 +21254,10 @@
         <v/>
       </c>
       <c r="N265" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O265" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P265" s="11" t="s">
         <v>52</v>
@@ -21301,7 +21289,7 @@
         <v>プロフィールのタグ</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G266" s="11" t="s">
         <v>54</v>
@@ -21330,7 +21318,7 @@
         <v>51</v>
       </c>
       <c r="L266" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M266" s="11">
         <f t="shared" si="11"/>
@@ -21340,11 +21328,11 @@
         <v>51</v>
       </c>
       <c r="O266" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P266" s="11"/>
       <c r="Q266" s="11" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="R266" s="9"/>
       <c r="S266" s="9"/>
@@ -21372,7 +21360,7 @@
         <v>プロフィールのタグ</v>
       </c>
       <c r="F267" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G267" s="11" t="s">
         <v>130</v>
@@ -21401,7 +21389,7 @@
         <v>461</v>
       </c>
       <c r="L267" s="9" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="M267" s="11">
         <f t="shared" ca="1" si="11"/>
@@ -21411,11 +21399,11 @@
         <v>51</v>
       </c>
       <c r="O267" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P267" s="11"/>
       <c r="Q267" s="11" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="R267" s="9"/>
       <c r="S267" s="9"/>
@@ -21451,7 +21439,7 @@
         <v>111</v>
       </c>
       <c r="H268" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I268" s="11">
         <f>_xlfn.LET(
@@ -21583,7 +21571,7 @@
         <v>118</v>
       </c>
       <c r="H270" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I270" s="11">
         <f>_xlfn.LET(
@@ -21715,7 +21703,7 @@
         <v>122</v>
       </c>
       <c r="H272" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I272" s="11">
         <f>_xlfn.LET(
@@ -21766,10 +21754,10 @@
         <v>272</v>
       </c>
       <c r="D273" s="11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E273" s="11" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F273" s="11" t="str">
         <f>D273&amp;"_uuid"</f>
@@ -21807,10 +21795,10 @@
         <v/>
       </c>
       <c r="N273" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O273" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P273" s="11" t="s">
         <v>52</v>
@@ -21842,7 +21830,7 @@
         <v>プロフィールの活動ジャンル</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G274" s="11" t="s">
         <v>54</v>
@@ -21871,7 +21859,7 @@
         <v>51</v>
       </c>
       <c r="L274" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M274" s="11">
         <f t="shared" si="11"/>
@@ -21881,11 +21869,11 @@
         <v>51</v>
       </c>
       <c r="O274" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P274" s="11"/>
       <c r="Q274" s="11" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="R274" s="9"/>
       <c r="S274" s="9"/>
@@ -21913,13 +21901,13 @@
         <v>プロフィールの活動ジャンル</v>
       </c>
       <c r="F275" s="11" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G275" s="11" t="s">
         <v>74</v>
       </c>
       <c r="H275" s="11" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="I275" s="11">
         <f>_xlfn.LET(
@@ -21948,11 +21936,11 @@
         <v>51</v>
       </c>
       <c r="O275" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P275" s="11"/>
       <c r="Q275" s="11" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="R275" s="9"/>
       <c r="S275" s="9"/>
@@ -21988,7 +21976,7 @@
         <v>111</v>
       </c>
       <c r="H276" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I276" s="11">
         <f>_xlfn.LET(
@@ -22120,7 +22108,7 @@
         <v>118</v>
       </c>
       <c r="H278" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I278" s="11">
         <f>_xlfn.LET(
@@ -22252,7 +22240,7 @@
         <v>122</v>
       </c>
       <c r="H280" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I280" s="11">
         <f>_xlfn.LET(
@@ -22758,7 +22746,7 @@
         <v>332</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>295</v>
@@ -23633,46 +23621,46 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="38" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="J1" s="38" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="K1" s="26" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="23">
@@ -23722,10 +23710,10 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C3" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23775,7 +23763,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C4" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23825,7 +23813,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="27"/>
       <c r="B5" s="24" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C5" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23875,7 +23863,7 @@
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="27"/>
       <c r="B6" s="24" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C6" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23925,7 +23913,7 @@
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="27"/>
       <c r="B7" s="24" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C7" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23975,7 +23963,7 @@
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="27"/>
       <c r="B8" s="24" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C8" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -24174,40 +24162,40 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C12" s="39" t="s">
+        <v>566</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>582</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>567</v>
+      </c>
+      <c r="F12" s="34" t="s">
         <v>570</v>
       </c>
-      <c r="D12" s="34" t="s">
-        <v>586</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>571</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>574</v>
-      </c>
       <c r="G12" s="34" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="J12" s="39" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="K12" s="34" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="L12" s="34" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="M12" s="34">
         <v>1</v>
@@ -24216,37 +24204,37 @@
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="27"/>
       <c r="B13" s="25" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="K13" s="34" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="L13" s="34" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="M13" s="34">
         <v>1</v>
@@ -24255,28 +24243,28 @@
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="27"/>
       <c r="B14" s="25" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E14" s="34" t="s">
+        <v>569</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="G14" s="34" t="s">
         <v>573</v>
       </c>
-      <c r="F14" s="34" t="s">
-        <v>576</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>577</v>
-      </c>
       <c r="H14" s="39" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="J14" s="39"/>
       <c r="K14" s="34"/>
@@ -24286,22 +24274,22 @@
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="27"/>
       <c r="B15" s="25" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C15" s="39" t="s">
+        <v>566</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>583</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>567</v>
+      </c>
+      <c r="F15" s="34" t="s">
         <v>570</v>
       </c>
-      <c r="D15" s="34" t="s">
-        <v>587</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>571</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>574</v>
-      </c>
       <c r="G15" s="34" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
@@ -24313,22 +24301,22 @@
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="27"/>
       <c r="B16" s="25" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
@@ -24340,22 +24328,22 @@
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="27"/>
       <c r="B17" s="25" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="E17" s="34" t="s">
+        <v>569</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="G17" s="34" t="s">
         <v>573</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>576</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>577</v>
       </c>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
@@ -24367,7 +24355,7 @@
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="27"/>
       <c r="B18" s="25" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
@@ -24384,7 +24372,7 @@
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="27"/>
       <c r="B19" s="25" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
@@ -24401,7 +24389,7 @@
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="27"/>
       <c r="B20" s="25" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -24418,7 +24406,7 @@
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="27"/>
       <c r="B21" s="25" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
@@ -24435,7 +24423,7 @@
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="27"/>
       <c r="B22" s="25" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
@@ -24452,7 +24440,7 @@
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="27"/>
       <c r="B23" s="25" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
@@ -24469,7 +24457,7 @@
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="27"/>
       <c r="B24" s="25" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
@@ -24486,7 +24474,7 @@
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="27"/>
       <c r="B25" s="25" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
@@ -24503,7 +24491,7 @@
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="27"/>
       <c r="B26" s="25" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
@@ -24520,7 +24508,7 @@
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="27"/>
       <c r="B27" s="25" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -24537,7 +24525,7 @@
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="27"/>
       <c r="B28" s="25" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -24554,7 +24542,7 @@
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="27"/>
       <c r="B29" s="25" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -24571,7 +24559,7 @@
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="27"/>
       <c r="B30" s="25" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
@@ -24588,7 +24576,7 @@
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="27"/>
       <c r="B31" s="25" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
@@ -24637,28 +24625,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="37" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="D1" s="36" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="23">
@@ -24684,10 +24672,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C3" s="33" t="s">
         <v>110</v>
@@ -24708,7 +24696,7 @@
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C4" s="33" t="s">
         <v>111</v>
@@ -24729,16 +24717,16 @@
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="27"/>
       <c r="B5" s="24" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D5" s="33" t="s">
         <v>71</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F5" s="33" t="s">
         <v>71</v>
@@ -24774,19 +24762,19 @@
         <v>41</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -24807,33 +24795,33 @@
         <v>115</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
+        <v>556</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>566</v>
+      </c>
+      <c r="D9" s="34" t="s">
         <v>560</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>539</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>570</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>564</v>
-      </c>
       <c r="E9" s="39" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="G9" s="18">
         <v>0</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
   </sheetData>

--- a/.design/DB/DB設計.xlsx
+++ b/.design/DB/DB設計.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevelopmentProjects\vtuber-meikan\.design\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0D9F5D-A609-4188-B6AD-F47D699DC18F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166AA61B-A5D9-4426-9D57-DC7880444600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2311" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2283" uniqueCount="588">
   <si>
     <t>設計完了</t>
   </si>
@@ -1708,10 +1708,6 @@
   </si>
   <si>
     <t>boolean</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>UUID</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -2355,6 +2351,18 @@
   </si>
   <si>
     <t>"japan"のUUID</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>serial</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -3009,7 +3017,7 @@
     <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C2,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B2" s="2">
         <f t="shared" ref="B2:B29" si="0">ROW()-1</f>
@@ -3025,7 +3033,7 @@
       </c>
       <c r="E2" s="3">
         <f ca="1">SUMIF(テーブル定義_一覧!D:D,C2,テーブル定義_一覧!I:I)</f>
-        <v>1288</v>
+        <v>1192</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>8</v>
@@ -3038,7 +3046,7 @@
     <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C3,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B3" s="2">
         <f t="shared" si="0"/>
@@ -3067,7 +3075,7 @@
     <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C4,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B4" s="2">
         <f t="shared" si="0"/>
@@ -3096,7 +3104,7 @@
     <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C5,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B5" s="2">
         <f t="shared" si="0"/>
@@ -3125,7 +3133,7 @@
     <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C6,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B6" s="2">
         <f t="shared" si="0"/>
@@ -3154,7 +3162,7 @@
     <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C7,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B7" s="2">
         <f t="shared" si="0"/>
@@ -3183,7 +3191,7 @@
     <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C8,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B8" s="2">
         <f t="shared" si="0"/>
@@ -3212,7 +3220,7 @@
     <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C9,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B9" s="2">
         <f t="shared" si="0"/>
@@ -3241,7 +3249,7 @@
     <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C10,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B10" s="2">
         <f t="shared" si="0"/>
@@ -3270,7 +3278,7 @@
     <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C11,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B11" s="2">
         <f t="shared" si="0"/>
@@ -3299,7 +3307,7 @@
     <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C12,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B12" s="2">
         <f t="shared" si="0"/>
@@ -3328,7 +3336,7 @@
     <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C13,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B13" s="2">
         <f t="shared" si="0"/>
@@ -3357,7 +3365,7 @@
     <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C14,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B14" s="2">
         <f t="shared" si="0"/>
@@ -3386,7 +3394,7 @@
     <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C15,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B15" s="2">
         <f t="shared" si="0"/>
@@ -3415,7 +3423,7 @@
     <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C16,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B16" s="2">
         <f t="shared" si="0"/>
@@ -3444,7 +3452,7 @@
     <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C17,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B17" s="2">
         <f t="shared" si="0"/>
@@ -3473,7 +3481,7 @@
     <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C18,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B18" s="2">
         <f t="shared" si="0"/>
@@ -3502,7 +3510,7 @@
     <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C19,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B19" s="2">
         <f t="shared" si="0"/>
@@ -3531,7 +3539,7 @@
     <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C20,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B20" s="2">
         <f t="shared" si="0"/>
@@ -3560,7 +3568,7 @@
     <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C21,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B21" s="2">
         <f t="shared" si="0"/>
@@ -3589,7 +3597,7 @@
     <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C22,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B22" s="2">
         <f t="shared" si="0"/>
@@ -3618,7 +3626,7 @@
     <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C23,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B23" s="2">
         <f t="shared" si="0"/>
@@ -3647,7 +3655,7 @@
     <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C24,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="0"/>
@@ -3676,7 +3684,7 @@
     <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C25,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B25" s="4">
         <f t="shared" si="0"/>
@@ -3705,7 +3713,7 @@
     <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C26,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="0"/>
@@ -3734,7 +3742,7 @@
     <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C27,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B27" s="4">
         <f t="shared" si="0"/>
@@ -3763,7 +3771,7 @@
     <row r="28" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C28,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B28" s="4">
         <f t="shared" si="0"/>
@@ -3792,7 +3800,7 @@
     <row r="29" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C29,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
+        <v/>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="0"/>
@@ -3919,12 +3927,10 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A2" s="9"/>
       <c r="B2" s="9" t="str">
         <f>D2&amp;"."&amp;F2</f>
-        <v>vtuber_profiles.vtuber_profiles_uuid</v>
+        <v>vtuber_profiles.vtuber_profiles_sequence_id</v>
       </c>
       <c r="C2" s="10">
         <f t="shared" ref="C2:C198" si="0">ROW()-1</f>
@@ -3937,14 +3943,14 @@
         <v>48</v>
       </c>
       <c r="F2" s="11" t="str">
-        <f>D2&amp;"_uuid"</f>
-        <v>vtuber_profiles_uuid</v>
+        <f>D2&amp;"_sequence_id"</f>
+        <v>vtuber_profiles_sequence_id</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>503</v>
+        <v>585</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>49</v>
+        <v>586</v>
       </c>
       <c r="I2" s="11">
         <f>_xlfn.LET(
@@ -3960,7 +3966,7 @@
         )
     )
 )</f>
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>475</v>
@@ -3978,7 +3984,7 @@
         <v>484</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>52</v>
+        <v>587</v>
       </c>
       <c r="Q2" s="11"/>
       <c r="R2" s="9"/>
@@ -4103,7 +4109,7 @@
         <v>51</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M4" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -4170,7 +4176,7 @@
         <v>51</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -4300,7 +4306,7 @@
         <v>51</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -4647,9 +4653,7 @@
       <c r="U12" s="11"/>
     </row>
     <row r="13" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A13" s="9"/>
       <c r="B13" s="9" t="str">
         <f t="shared" si="2"/>
         <v>join_group.join_group_uuid</v>
@@ -4831,7 +4835,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="M15" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -5237,9 +5241,7 @@
       <c r="U21" s="11"/>
     </row>
     <row r="22" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A22" s="9"/>
       <c r="B22" s="9" t="str">
         <f t="shared" si="2"/>
         <v>tag.tag_uuid</v>
@@ -5701,9 +5703,7 @@
       <c r="U28" s="11"/>
     </row>
     <row r="29" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A29" s="9"/>
       <c r="B29" s="9" t="str">
         <f t="shared" si="2"/>
         <v>badge.badge_uuid</v>
@@ -5834,7 +5834,7 @@
         <v>51</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6167,9 +6167,7 @@
       <c r="U35" s="11"/>
     </row>
     <row r="36" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A36" s="9"/>
       <c r="B36" s="9" t="str">
         <f t="shared" si="2"/>
         <v>activity_status.activity_status_uuid</v>
@@ -6298,7 +6296,7 @@
       <c r="S37" s="9"/>
       <c r="T37" s="9"/>
       <c r="U37" s="11" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6631,9 +6629,7 @@
       <c r="U42" s="11"/>
     </row>
     <row r="43" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A43" s="9"/>
       <c r="B43" s="9" t="str">
         <f t="shared" si="2"/>
         <v>sns_link.sns_link_uuid</v>
@@ -6748,11 +6744,11 @@
         <v>51</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="M44" s="11">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>506</v>
+      </c>
+      <c r="M44" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>エラー</v>
       </c>
       <c r="N44" s="11" t="s">
         <v>51</v>
@@ -6815,7 +6811,7 @@
         <v>51</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="M45" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -7288,9 +7284,7 @@
       <c r="U52" s="11"/>
     </row>
     <row r="53" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A53" s="9"/>
       <c r="B53" s="9" t="str">
         <f t="shared" si="2"/>
         <v>bbs_res.bbs_res_uuid</v>
@@ -7405,11 +7399,11 @@
         <v>51</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="M54" s="11">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>506</v>
+      </c>
+      <c r="M54" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>エラー</v>
       </c>
       <c r="N54" s="11" t="s">
         <v>51</v>
@@ -7472,7 +7466,7 @@
         <v>51</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M55" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -7945,9 +7939,7 @@
       <c r="U62" s="11"/>
     </row>
     <row r="63" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A63" s="9"/>
       <c r="B63" s="9" t="str">
         <f t="shared" ref="B63:B125" si="3">D63&amp;"."&amp;F63</f>
         <v>page_author.page_author_uuid</v>
@@ -8062,7 +8054,7 @@
         <v>51</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M64" s="11">
         <f t="shared" ca="1" si="1"/>
@@ -8129,11 +8121,11 @@
         <v>51</v>
       </c>
       <c r="L65" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="M65" s="11">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>506</v>
+      </c>
+      <c r="M65" s="11" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>エラー</v>
       </c>
       <c r="N65" s="11" t="s">
         <v>51</v>
@@ -8196,7 +8188,7 @@
         <v>51</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M66" s="11">
         <f t="shared" ref="M66:M129" ca="1" si="4">_xlfn.SINGLE(IF(K66="","",IF(L66="","参照先未定義",_xlfn.XLOOKUP(L66,B:B,C:C,"エラー"))))</f>
@@ -8799,9 +8791,7 @@
       <c r="U75" s="11"/>
     </row>
     <row r="76" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A76" s="9"/>
       <c r="B76" s="9" t="str">
         <f t="shared" si="3"/>
         <v>contact.contact_uuid</v>
@@ -9111,7 +9101,7 @@
         <v>51</v>
       </c>
       <c r="L80" s="9" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="M80" s="11">
         <f t="shared" ca="1" si="4"/>
@@ -9176,7 +9166,7 @@
         <v>51</v>
       </c>
       <c r="L81" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="M81" s="11">
         <f t="shared" ca="1" si="4"/>
@@ -9521,9 +9511,7 @@
       <c r="U86" s="11"/>
     </row>
     <row r="87" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A87" s="9"/>
       <c r="B87" s="9" t="str">
         <f t="shared" si="3"/>
         <v>priority.priority_uuid</v>
@@ -9713,7 +9701,7 @@
       <c r="S89" s="9"/>
       <c r="T89" s="9"/>
       <c r="U89" s="11" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="90" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10046,9 +10034,7 @@
       <c r="U94" s="11"/>
     </row>
     <row r="95" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A95" s="9"/>
       <c r="B95" s="9" t="str">
         <f t="shared" si="3"/>
         <v>response_status.response_status_uuid</v>
@@ -10238,7 +10224,7 @@
       <c r="S97" s="9"/>
       <c r="T97" s="9"/>
       <c r="U97" s="11" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="98" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10571,9 +10557,7 @@
       <c r="U102" s="11"/>
     </row>
     <row r="103" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A103" s="9"/>
       <c r="B103" s="9" t="str">
         <f t="shared" si="3"/>
         <v>language.language_uuid</v>
@@ -10702,7 +10686,7 @@
       <c r="S104" s="9"/>
       <c r="T104" s="9"/>
       <c r="U104" s="11" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11163,9 +11147,7 @@
       <c r="U111" s="11"/>
     </row>
     <row r="112" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A112" s="9"/>
       <c r="B112" s="9" t="str">
         <f t="shared" si="3"/>
         <v>screen_word.screen_word_uuid</v>
@@ -11280,7 +11262,7 @@
         <v>51</v>
       </c>
       <c r="L113" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="M113" s="11">
         <f t="shared" ca="1" si="4"/>
@@ -11351,7 +11333,7 @@
       <c r="O114" s="11"/>
       <c r="P114" s="11"/>
       <c r="Q114" s="11" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="R114" s="9"/>
       <c r="S114" s="9"/>
@@ -11414,7 +11396,7 @@
       <c r="O115" s="11"/>
       <c r="P115" s="11"/>
       <c r="Q115" s="11" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="R115" s="9"/>
       <c r="S115" s="9"/>
@@ -11442,13 +11424,13 @@
         <v>画面文言</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G116" s="11" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H116" s="11" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I116" s="11" t="str">
         <f>_xlfn.LET(
@@ -11477,13 +11459,13 @@
       <c r="O116" s="11"/>
       <c r="P116" s="11"/>
       <c r="Q116" s="11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="R116" s="9"/>
       <c r="S116" s="9"/>
       <c r="T116" s="9"/>
       <c r="U116" s="11" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="117" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11816,9 +11798,7 @@
       <c r="U121" s="11"/>
     </row>
     <row r="122" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A122" s="9"/>
       <c r="B122" s="9" t="str">
         <f t="shared" si="3"/>
         <v>sns_support.sns_support_uuid</v>
@@ -11998,7 +11978,7 @@
         <v>51</v>
       </c>
       <c r="L124" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M124" s="11">
         <f t="shared" ca="1" si="4"/>
@@ -12479,9 +12459,7 @@
       <c r="U131" s="11"/>
     </row>
     <row r="132" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A132" s="9"/>
       <c r="B132" s="9" t="str">
         <f t="shared" si="6"/>
         <v>profile_report.profile_report_uuid</v>
@@ -12596,7 +12574,7 @@
         <v>51</v>
       </c>
       <c r="L133" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M133" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -12661,11 +12639,11 @@
         <v>51</v>
       </c>
       <c r="L134" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="M134" s="11">
-        <f t="shared" si="7"/>
-        <v>1</v>
+        <v>506</v>
+      </c>
+      <c r="M134" s="11" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>エラー</v>
       </c>
       <c r="N134" s="11" t="s">
         <v>51</v>
@@ -12728,7 +12706,7 @@
         <v>51</v>
       </c>
       <c r="L135" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="M135" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -13207,9 +13185,7 @@
       <c r="U142" s="11"/>
     </row>
     <row r="143" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A143" s="9"/>
       <c r="B143" s="9" t="str">
         <f t="shared" si="6"/>
         <v>report_reason.report_reason_uuid</v>
@@ -13338,7 +13314,7 @@
       <c r="S144" s="9"/>
       <c r="T144" s="9"/>
       <c r="U144" s="11" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="145" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13671,9 +13647,7 @@
       <c r="U149" s="11"/>
     </row>
     <row r="150" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A150" s="9"/>
       <c r="B150" s="9" t="str">
         <f t="shared" si="6"/>
         <v>users.users_uuid</v>
@@ -13916,7 +13890,7 @@
         <v>51</v>
       </c>
       <c r="L153" s="9" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M153" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -14048,7 +14022,7 @@
         <v>51</v>
       </c>
       <c r="L155" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="M155" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -14178,7 +14152,7 @@
         <v>51</v>
       </c>
       <c r="L157" s="9" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M157" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -14189,7 +14163,7 @@
       </c>
       <c r="O157" s="11"/>
       <c r="P157" s="11" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="Q157" s="11"/>
       <c r="R157" s="9"/>
@@ -14247,7 +14221,7 @@
         <v>51</v>
       </c>
       <c r="L158" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="M158" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -14258,7 +14232,7 @@
       </c>
       <c r="O158" s="11"/>
       <c r="P158" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="Q158" s="11"/>
       <c r="R158" s="9"/>
@@ -14596,9 +14570,7 @@
       <c r="U163" s="11"/>
     </row>
     <row r="164" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A164" s="9"/>
       <c r="B164" s="9" t="str">
         <f t="shared" si="6"/>
         <v>theme.theme_uuid</v>
@@ -14727,7 +14699,7 @@
       <c r="S165" s="9"/>
       <c r="T165" s="9"/>
       <c r="U165" s="11" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="166" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15060,9 +15032,7 @@
       <c r="U170" s="11"/>
     </row>
     <row r="171" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A171" s="9"/>
       <c r="B171" s="9" t="str">
         <f t="shared" si="6"/>
         <v>user_role.user_role_uuid</v>
@@ -15191,7 +15161,7 @@
       <c r="S172" s="9"/>
       <c r="T172" s="9"/>
       <c r="U172" s="11" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="173" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15524,9 +15494,7 @@
       <c r="U177" s="11"/>
     </row>
     <row r="178" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A178" s="9"/>
       <c r="B178" s="9" t="str">
         <f t="shared" si="6"/>
         <v>images_contents.images_contents_uuid</v>
@@ -15706,7 +15674,7 @@
         <v>51</v>
       </c>
       <c r="L180" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M180" s="11">
         <f t="shared" ca="1" si="7"/>
@@ -16551,9 +16519,7 @@
       <c r="U193" s="11"/>
     </row>
     <row r="194" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A194" s="9"/>
       <c r="B194" s="9" t="str">
         <f t="shared" si="8"/>
         <v>images_system.images_system_uuid</v>
@@ -17511,9 +17477,7 @@
       <c r="U208" s="11"/>
     </row>
     <row r="209" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A209" s="9"/>
       <c r="B209" s="9" t="str">
         <f t="shared" si="8"/>
         <v>screen_element.screen_element_uuid</v>
@@ -17975,9 +17939,7 @@
       <c r="U215" s="11"/>
     </row>
     <row r="216" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A216" s="9"/>
       <c r="B216" s="9" t="str">
         <f t="shared" si="8"/>
         <v>likes.likes_uuid</v>
@@ -18091,7 +18053,7 @@
         <v>464</v>
       </c>
       <c r="L217" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M217" s="11">
         <f t="shared" ca="1" si="9"/>
@@ -18162,7 +18124,7 @@
         <v>464</v>
       </c>
       <c r="L218" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M218" s="11">
         <f t="shared" ca="1" si="9"/>
@@ -18643,9 +18605,7 @@
       <c r="U225" s="11"/>
     </row>
     <row r="226" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A226" s="9"/>
       <c r="B226" s="9" t="str">
         <f t="shared" si="8"/>
         <v>movie_link.movie_link_uuid</v>
@@ -18825,11 +18785,11 @@
         <v>51</v>
       </c>
       <c r="L228" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="M228" s="11">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>506</v>
+      </c>
+      <c r="M228" s="11" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>エラー</v>
       </c>
       <c r="N228" s="11" t="s">
         <v>51</v>
@@ -19235,9 +19195,7 @@
       <c r="U234" s="11"/>
     </row>
     <row r="235" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A235" s="9"/>
       <c r="B235" s="9" t="str">
         <f t="shared" si="8"/>
         <v>relation.relation_uuid</v>
@@ -19352,11 +19310,11 @@
         <v>51</v>
       </c>
       <c r="L236" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="M236" s="11">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>506</v>
+      </c>
+      <c r="M236" s="11" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>エラー</v>
       </c>
       <c r="N236" s="11" t="s">
         <v>51</v>
@@ -19423,11 +19381,11 @@
         <v>51</v>
       </c>
       <c r="L237" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="M237" s="11">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>506</v>
+      </c>
+      <c r="M237" s="11" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>エラー</v>
       </c>
       <c r="N237" s="11" t="s">
         <v>51</v>
@@ -19837,9 +19795,7 @@
       <c r="U243" s="11"/>
     </row>
     <row r="244" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A244" s="9"/>
       <c r="B244" s="9" t="str">
         <f t="shared" si="8"/>
         <v>vtuber_profiles_lang.vtuber_profiles_lang_uuid</v>
@@ -19954,11 +19910,11 @@
         <v>461</v>
       </c>
       <c r="L245" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="M245" s="11">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>506</v>
+      </c>
+      <c r="M245" s="11" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>エラー</v>
       </c>
       <c r="N245" s="11" t="s">
         <v>51</v>
@@ -20025,7 +19981,7 @@
         <v>464</v>
       </c>
       <c r="L246" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="M246" s="11">
         <f t="shared" ref="M246:M280" ca="1" si="11">IF(K246="","",IF(L246="","参照先未定義",_xlfn.XLOOKUP(L246,B:B,C:C,"エラー")))</f>
@@ -21201,9 +21157,7 @@
       <c r="U264" s="11"/>
     </row>
     <row r="265" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A265" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A265" s="9"/>
       <c r="B265" s="9" t="str">
         <f t="shared" ref="B265:B267" si="14">D265&amp;"."&amp;F265</f>
         <v>profile_tag.profile_tag_uuid</v>
@@ -21318,11 +21272,11 @@
         <v>51</v>
       </c>
       <c r="L266" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="M266" s="11">
-        <f t="shared" si="11"/>
-        <v>1</v>
+        <v>506</v>
+      </c>
+      <c r="M266" s="11" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>エラー</v>
       </c>
       <c r="N266" s="11" t="s">
         <v>51</v>
@@ -21389,7 +21343,7 @@
         <v>461</v>
       </c>
       <c r="L267" s="9" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="M267" s="11">
         <f t="shared" ca="1" si="11"/>
@@ -21742,9 +21696,7 @@
       <c r="U272" s="11"/>
     </row>
     <row r="273" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A273" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="A273" s="9"/>
       <c r="B273" s="9" t="str">
         <f t="shared" si="12"/>
         <v>profile_activity.profile_activity_uuid</v>
@@ -21859,11 +21811,11 @@
         <v>51</v>
       </c>
       <c r="L274" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="M274" s="11">
-        <f t="shared" si="11"/>
-        <v>1</v>
+        <v>506</v>
+      </c>
+      <c r="M274" s="11" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>エラー</v>
       </c>
       <c r="N274" s="11" t="s">
         <v>51</v>
@@ -23621,46 +23573,46 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="38" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="J1" s="38" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K1" s="26" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="23">
@@ -23710,10 +23662,10 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C3" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23763,7 +23715,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C4" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23813,7 +23765,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="27"/>
       <c r="B5" s="24" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C5" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23863,7 +23815,7 @@
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="27"/>
       <c r="B6" s="24" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C6" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23913,7 +23865,7 @@
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="27"/>
       <c r="B7" s="24" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C7" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23963,7 +23915,7 @@
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="27"/>
       <c r="B8" s="24" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C8" s="33" t="str" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -24162,40 +24114,40 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C12" s="39" t="s">
+        <v>565</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>581</v>
+      </c>
+      <c r="E12" s="34" t="s">
         <v>566</v>
       </c>
-      <c r="D12" s="34" t="s">
-        <v>582</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>567</v>
-      </c>
       <c r="F12" s="34" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H12" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J12" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K12" s="34" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="L12" s="34" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="M12" s="34">
         <v>1</v>
@@ -24204,37 +24156,37 @@
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="27"/>
       <c r="B13" s="25" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K13" s="34" t="s">
+        <v>579</v>
+      </c>
+      <c r="L13" s="34" t="s">
         <v>580</v>
-      </c>
-      <c r="L13" s="34" t="s">
-        <v>581</v>
       </c>
       <c r="M13" s="34">
         <v>1</v>
@@ -24243,28 +24195,28 @@
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="27"/>
       <c r="B14" s="25" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F14" s="34" t="s">
+        <v>571</v>
+      </c>
+      <c r="G14" s="34" t="s">
         <v>572</v>
       </c>
-      <c r="G14" s="34" t="s">
-        <v>573</v>
-      </c>
       <c r="H14" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="J14" s="39"/>
       <c r="K14" s="34"/>
@@ -24274,22 +24226,22 @@
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="27"/>
       <c r="B15" s="25" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C15" s="39" t="s">
+        <v>565</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>582</v>
+      </c>
+      <c r="E15" s="34" t="s">
         <v>566</v>
       </c>
-      <c r="D15" s="34" t="s">
-        <v>583</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>567</v>
-      </c>
       <c r="F15" s="34" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
@@ -24301,22 +24253,22 @@
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="27"/>
       <c r="B16" s="25" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
@@ -24328,22 +24280,22 @@
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="27"/>
       <c r="B17" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F17" s="34" t="s">
+        <v>571</v>
+      </c>
+      <c r="G17" s="34" t="s">
         <v>572</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>573</v>
       </c>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
@@ -24355,7 +24307,7 @@
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="27"/>
       <c r="B18" s="25" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
@@ -24372,7 +24324,7 @@
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="27"/>
       <c r="B19" s="25" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
@@ -24389,7 +24341,7 @@
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="27"/>
       <c r="B20" s="25" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -24406,7 +24358,7 @@
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="27"/>
       <c r="B21" s="25" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
@@ -24423,7 +24375,7 @@
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="27"/>
       <c r="B22" s="25" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
@@ -24440,7 +24392,7 @@
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="27"/>
       <c r="B23" s="25" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
@@ -24457,7 +24409,7 @@
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="27"/>
       <c r="B24" s="25" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
@@ -24474,7 +24426,7 @@
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="27"/>
       <c r="B25" s="25" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
@@ -24491,7 +24443,7 @@
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="27"/>
       <c r="B26" s="25" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
@@ -24508,7 +24460,7 @@
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="27"/>
       <c r="B27" s="25" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -24525,7 +24477,7 @@
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="27"/>
       <c r="B28" s="25" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -24542,7 +24494,7 @@
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="27"/>
       <c r="B29" s="25" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -24559,7 +24511,7 @@
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="27"/>
       <c r="B30" s="25" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
@@ -24576,7 +24528,7 @@
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="27"/>
       <c r="B31" s="25" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
@@ -24625,28 +24577,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="37" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D1" s="36" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="23">
@@ -24672,10 +24624,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C3" s="33" t="s">
         <v>110</v>
@@ -24696,7 +24648,7 @@
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C4" s="33" t="s">
         <v>111</v>
@@ -24717,16 +24669,16 @@
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="27"/>
       <c r="B5" s="24" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D5" s="33" t="s">
         <v>71</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F5" s="33" t="s">
         <v>71</v>
@@ -24762,19 +24714,19 @@
         <v>41</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -24795,33 +24747,33 @@
         <v>115</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G9" s="18">
         <v>0</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
   </sheetData>

--- a/.design/DB/DB設計.xlsx
+++ b/.design/DB/DB設計.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/segar/Documents/GitHub/vtuber-meikan/.design/DB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EDBA07-8BC5-4F42-9058-8A4F80EBE37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773B2E03-20B0-8041-8A43-E448DE0739F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テーブル一覧" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="監査列" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">テーブル一覧!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">テーブル一覧!$B$1:$I$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">テーブル定義_一覧!$A$1:$U$277</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">型とバイト数!$A$2:$G$2</definedName>
   </definedNames>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="611">
   <si>
     <t>設計完了</t>
   </si>
@@ -576,9 +576,6 @@
   </si>
   <si>
     <t>対応状況(物理名)</t>
-  </si>
-  <si>
-    <t>priority</t>
   </si>
   <si>
     <t>優先度</t>
@@ -1673,17 +1670,6 @@
   </si>
   <si>
     <t>管理者向けのため、日本語固定</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>文言種別</t>
-    <rPh sb="0" eb="4">
-      <t>モンゴンシュベツ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>message_type</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -2438,12 +2424,202 @@
     <t>images_system.images_system_sequence_id</t>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>DMLマスタ作成完了</t>
+    <rPh sb="6" eb="10">
+      <t xml:space="preserve">サクセイカンリョウ </t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>activity_status</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>活動開始前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(VTuber</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>準備中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>活動中</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>卒業済み</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>その他</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>active</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>other</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>graduete</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>休止中</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">キュウシチュウ </t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>deactive</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ready</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>{activity_status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>テーブルのreadyのID}</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>{activity_status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>テーブルのactiveのID}</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>{activity_status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>テーブルのgraduateのID}</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>{activity_status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>テーブルのotherのID}</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>{activity_status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>テーブルのdeactiveのID}</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>priority</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>message_id_table</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>メッセージID参照元テーブル</t>
+    <rPh sb="7" eb="10">
+      <t xml:space="preserve">サンショウモト </t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>VプロフィールID</t>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2552,6 +2728,21 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2712,7 +2903,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2831,6 +3022,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3048,859 +3245,905 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H29"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="2" width="3.83203125" customWidth="1"/>
-    <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5" customWidth="1"/>
-    <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="110.6640625" customWidth="1"/>
-    <col min="8" max="26" width="8.6640625" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="3.83203125" customWidth="1"/>
+    <col min="4" max="4" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.5" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="110.6640625" customWidth="1"/>
+    <col min="9" max="27" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1">
+    <row r="1" spans="1:9" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1">
+    <row r="2" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A2" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C2,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D2,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B2" s="2">
-        <f t="shared" ref="B2:B29" si="0">ROW()-1</f>
+      <c r="B2" s="1"/>
+      <c r="C2" s="2">
+        <f t="shared" ref="C2:C29" si="0">ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="C2:C29" ca="1">_xlfn.UNIQUE(_xlfn._xlws.FILTER(テーブル定義_一覧!D:D,(テーブル定義_一覧!D:D&lt;&gt;"")*(テーブル定義_一覧!D:D&lt;&gt;"テーブル名(物理名)")))</f>
+      <c r="D2" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="D2:D29" ca="1">_xlfn.UNIQUE(_xlfn._xlws.FILTER(テーブル定義_一覧!D:D,(テーブル定義_一覧!D:D&lt;&gt;"")*(テーブル定義_一覧!D:D&lt;&gt;"テーブル名(物理名)")))</f>
         <v>vtuber_profiles</v>
       </c>
-      <c r="D2" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C2,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E2" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D2,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>Vtuberプロフィール</v>
       </c>
-      <c r="E2" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C2,テーブル定義_一覧!I:I)</f>
+      <c r="F2" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D2,テーブル定義_一覧!I:I)</f>
         <v>904</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1">
+      <c r="H2" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A3" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C3,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D3,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1"/>
+      <c r="C3" s="2">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="str">
+      <c r="D3" s="3" t="str">
         <f ca="1"/>
         <v>join_group</v>
       </c>
-      <c r="D3" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C3,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E3" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D3,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>所属</v>
       </c>
-      <c r="E3" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C3,テーブル定義_一覧!I:I)</f>
+      <c r="F3" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D3,テーブル定義_一覧!I:I)</f>
         <v>1224</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A4" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C4,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D4,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1"/>
+      <c r="C4" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="str">
+      <c r="D4" s="3" t="str">
         <f ca="1"/>
         <v>tag</v>
       </c>
-      <c r="D4" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C4,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E4" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D4,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>タグ</v>
       </c>
-      <c r="E4" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C4,テーブル定義_一覧!I:I)</f>
+      <c r="F4" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D4,テーブル定義_一覧!I:I)</f>
         <v>680</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" ht="18.75" customHeight="1">
       <c r="A5" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C5,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D5,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="str">
+      <c r="D5" s="3" t="str">
         <f ca="1"/>
         <v>badge</v>
       </c>
-      <c r="D5" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C5,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E5" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D5,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>バッジ</v>
       </c>
-      <c r="E5" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C5,テーブル定義_一覧!I:I)</f>
+      <c r="F5" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D5,テーブル定義_一覧!I:I)</f>
         <v>872</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" ht="18.75" customHeight="1">
       <c r="A6" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C6,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D6,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="str">
+      <c r="D6" s="3" t="str">
         <f ca="1"/>
         <v>activity_status</v>
       </c>
-      <c r="D6" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C6,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E6" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D6,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>活動状態</v>
       </c>
-      <c r="E6" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C6,テーブル定義_一覧!I:I)</f>
+      <c r="F6" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D6,テーブル定義_一覧!I:I)</f>
         <v>744</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A7" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C7,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D7,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1"/>
+      <c r="C7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="str">
+      <c r="D7" s="3" t="str">
         <f ca="1"/>
         <v>sns_link</v>
       </c>
-      <c r="D7" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C7,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E7" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D7,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>SNSリンク</v>
       </c>
-      <c r="E7" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C7,テーブル定義_一覧!I:I)</f>
+      <c r="F7" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D7,テーブル定義_一覧!I:I)</f>
         <v>1000</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A8" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C8,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D8,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1"/>
+      <c r="C8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="str">
+      <c r="D8" s="3" t="str">
         <f ca="1"/>
         <v>bbs_res</v>
       </c>
-      <c r="D8" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C8,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E8" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D8,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>BBS</v>
       </c>
-      <c r="E8" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C8,テーブル定義_一覧!I:I)</f>
+      <c r="F8" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D8,テーブル定義_一覧!I:I)</f>
         <v>808</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A9" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C9,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D9,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1"/>
+      <c r="C9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="str">
+      <c r="D9" s="3" t="str">
         <f ca="1"/>
         <v>page_author</v>
       </c>
-      <c r="D9" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C9,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E9" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D9,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>ページ編集者</v>
       </c>
-      <c r="E9" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C9,テーブル定義_一覧!I:I)</f>
+      <c r="F9" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D9,テーブル定義_一覧!I:I)</f>
         <v>872</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A10" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C10,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D10,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1"/>
+      <c r="C10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C10" s="3" t="str">
+      <c r="D10" s="3" t="str">
         <f ca="1"/>
         <v>contact</v>
       </c>
-      <c r="D10" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C10,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E10" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D10,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>問い合わせ</v>
       </c>
-      <c r="E10" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C10,テーブル定義_一覧!I:I)</f>
+      <c r="F10" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D10,テーブル定義_一覧!I:I)</f>
         <v>4824</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" ht="18.75" customHeight="1">
       <c r="A11" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C11,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D11,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1"/>
+      <c r="C11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C11" s="3" t="str">
+      <c r="D11" s="3" t="str">
         <f ca="1"/>
         <v>priority</v>
       </c>
-      <c r="D11" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C11,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E11" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D11,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>優先度</v>
       </c>
-      <c r="E11" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C11,テーブル定義_一覧!I:I)</f>
+      <c r="F11" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D11,テーブル定義_一覧!I:I)</f>
         <v>808</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9" ht="18.75" customHeight="1">
       <c r="A12" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C12,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D12,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1"/>
+      <c r="C12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C12" s="3" t="str">
+      <c r="D12" s="3" t="str">
         <f ca="1"/>
         <v>response_status</v>
       </c>
-      <c r="D12" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C12,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E12" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D12,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>対応状況</v>
       </c>
-      <c r="E12" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C12,テーブル定義_一覧!I:I)</f>
+      <c r="F12" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D12,テーブル定義_一覧!I:I)</f>
         <v>808</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9" ht="18.75" customHeight="1">
       <c r="A13" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C13,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D13,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C13" s="3" t="str">
+      <c r="D13" s="3" t="str">
         <f ca="1"/>
         <v>language</v>
       </c>
-      <c r="D13" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C13,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E13" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D13,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>表示言語</v>
       </c>
-      <c r="E13" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C13,テーブル定義_一覧!I:I)</f>
+      <c r="F13" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D13,テーブル定義_一覧!I:I)</f>
         <v>848</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9" ht="18.75" customHeight="1">
       <c r="A14" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C14,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D14,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C14" s="3" t="str">
+      <c r="D14" s="3" t="str">
         <f ca="1"/>
         <v>screen_word</v>
       </c>
-      <c r="D14" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C14,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E14" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D14,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>画面文言</v>
       </c>
-      <c r="E14" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C14,テーブル定義_一覧!I:I)</f>
+      <c r="F14" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D14,テーブル定義_一覧!I:I)</f>
         <v>744</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9" ht="18.75" customHeight="1">
       <c r="A15" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C15,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D15,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1"/>
+      <c r="C15" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C15" s="3" t="str">
+      <c r="D15" s="3" t="str">
         <f ca="1"/>
         <v>sns_support</v>
       </c>
-      <c r="D15" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C15,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E15" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D15,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>サポートするSNS</v>
       </c>
-      <c r="E15" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C15,テーブル定義_一覧!I:I)</f>
+      <c r="F15" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D15,テーブル定義_一覧!I:I)</f>
         <v>984</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A16" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C16,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D16,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1"/>
+      <c r="C16" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C16" s="3" t="str">
+      <c r="D16" s="3" t="str">
         <f ca="1"/>
         <v>profile_report</v>
       </c>
-      <c r="D16" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C16,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E16" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D16,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>プロフィール通報</v>
       </c>
-      <c r="E16" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C16,テーブル定義_一覧!I:I)</f>
+      <c r="F16" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D16,テーブル定義_一覧!I:I)</f>
         <v>840</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9" ht="18.75" customHeight="1">
       <c r="A17" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C17,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D17,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1"/>
+      <c r="C17" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C17" s="3" t="str">
+      <c r="D17" s="3" t="str">
         <f ca="1"/>
         <v>report_reason</v>
       </c>
-      <c r="D17" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C17,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E17" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D17,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>通報理由</v>
       </c>
-      <c r="E17" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C17,テーブル定義_一覧!I:I)</f>
+      <c r="F17" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D17,テーブル定義_一覧!I:I)</f>
         <v>808</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A18" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C18,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D18,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1"/>
+      <c r="C18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C18" s="3" t="str">
+      <c r="D18" s="3" t="str">
         <f ca="1"/>
         <v>users</v>
       </c>
-      <c r="D18" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C18,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E18" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D18,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>ユーザー</v>
       </c>
-      <c r="E18" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C18,テーブル定義_一覧!I:I)</f>
+      <c r="F18" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D18,テーブル定義_一覧!I:I)</f>
         <v>1456</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9" ht="18.75" customHeight="1">
       <c r="A19" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C19,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D19,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1"/>
+      <c r="C19" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C19" s="3" t="str">
+      <c r="D19" s="3" t="str">
         <f ca="1"/>
         <v>theme</v>
       </c>
-      <c r="D19" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C19,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E19" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D19,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>画面テーマ</v>
       </c>
-      <c r="E19" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C19,テーブル定義_一覧!I:I)</f>
+      <c r="F19" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D19,テーブル定義_一覧!I:I)</f>
         <v>808</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9" ht="18.75" customHeight="1">
       <c r="A20" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C20,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D20,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="1"/>
+      <c r="C20" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C20" s="3" t="str">
+      <c r="D20" s="3" t="str">
         <f ca="1"/>
         <v>user_role</v>
       </c>
-      <c r="D20" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C20,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E20" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D20,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>ユーザー権限</v>
       </c>
-      <c r="E20" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C20,テーブル定義_一覧!I:I)</f>
+      <c r="F20" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D20,テーブル定義_一覧!I:I)</f>
         <v>744</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A21" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C21,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D21,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1"/>
+      <c r="C21" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C21" s="3" t="str">
+      <c r="D21" s="3" t="str">
         <f ca="1"/>
         <v>images_contents</v>
       </c>
-      <c r="D21" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C21,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E21" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D21,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>画像(ユーザー投稿)</v>
       </c>
-      <c r="E21" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C21,テーブル定義_一覧!I:I)</f>
+      <c r="F21" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D21,テーブル定義_一覧!I:I)</f>
         <v>12240</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" ht="18.75" customHeight="1">
       <c r="A22" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C22,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D22,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1"/>
+      <c r="C22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C22" s="3" t="str">
+      <c r="D22" s="3" t="str">
         <f ca="1"/>
         <v>images_system</v>
       </c>
-      <c r="D22" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C22,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E22" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D22,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>画像(システム管理)</v>
       </c>
-      <c r="E22" s="3">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C22,テーブル定義_一覧!I:I)</f>
+      <c r="F22" s="3">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D22,テーブル定義_一覧!I:I)</f>
         <v>12208</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9" ht="18.75" customHeight="1">
       <c r="A23" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C23,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D23,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="1"/>
+      <c r="C23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C23" s="5" t="str">
+      <c r="D23" s="5" t="str">
         <f ca="1"/>
         <v>screen_element</v>
       </c>
-      <c r="D23" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C23,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E23" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D23,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>画面要素</v>
       </c>
-      <c r="E23" s="5">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C23,テーブル定義_一覧!I:I)</f>
+      <c r="F23" s="5">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D23,テーブル定義_一覧!I:I)</f>
         <v>808</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A24" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C24,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D24,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="1"/>
+      <c r="C24" s="4">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C24" s="6" t="str">
+      <c r="D24" s="6" t="str">
         <f ca="1"/>
         <v>likes</v>
       </c>
-      <c r="D24" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C24,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E24" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D24,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>いいね</v>
       </c>
-      <c r="E24" s="6">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C24,テーブル定義_一覧!I:I)</f>
+      <c r="F24" s="6">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D24,テーブル定義_一覧!I:I)</f>
         <v>808</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1">
+      <c r="H24" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A25" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C25,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D25,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="1"/>
+      <c r="C25" s="4">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C25" s="6" t="str">
+      <c r="D25" s="6" t="str">
         <f ca="1"/>
         <v>movie_link</v>
       </c>
-      <c r="D25" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C25,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E25" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D25,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>動画リンク</v>
       </c>
-      <c r="E25" s="6">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C25,テーブル定義_一覧!I:I)</f>
+      <c r="F25" s="6">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D25,テーブル定義_一覧!I:I)</f>
         <v>712</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>447</v>
-      </c>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1">
+      <c r="H25" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A26" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C26,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D26,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="1"/>
+      <c r="C26" s="4">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C26" s="6" t="str">
+      <c r="D26" s="6" t="str">
         <f ca="1"/>
         <v>relation</v>
       </c>
-      <c r="D26" s="3" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C26,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E26" s="3" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D26,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>関係値</v>
       </c>
-      <c r="E26" s="6">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C26,テーブル定義_一覧!I:I)</f>
+      <c r="F26" s="6">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D26,テーブル定義_一覧!I:I)</f>
         <v>1000</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1">
+      <c r="H26" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" spans="1:9" ht="18.75" hidden="1" customHeight="1">
       <c r="A27" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C27,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D27,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="1"/>
+      <c r="C27" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C27" s="8" t="str">
+      <c r="D27" s="8" t="str">
         <f ca="1"/>
         <v>vtuber_profiles_lang</v>
       </c>
-      <c r="D27" s="5" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C27,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E27" s="5" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D27,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>Vtuberプロフィール(各言語)</v>
       </c>
-      <c r="E27" s="8">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C27,テーブル定義_一覧!I:I)</f>
+      <c r="F27" s="8">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D27,テーブル定義_一覧!I:I)</f>
         <v>5864</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="1:8" ht="18">
+      <c r="H27" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="1:9" ht="18" hidden="1">
       <c r="A28" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C28,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D28,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="1"/>
+      <c r="C28" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C28" s="6" t="str">
+      <c r="D28" s="6" t="str">
         <f ca="1"/>
         <v>profile_tag</v>
       </c>
-      <c r="D28" s="6" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C28,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E28" s="6" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D28,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>プロフィールのタグ</v>
       </c>
-      <c r="E28" s="6">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C28,テーブル定義_一覧!I:I)</f>
+      <c r="F28" s="6">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D28,テーブル定義_一覧!I:I)</f>
         <v>744</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="G28" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G28" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" spans="1:8" ht="18">
+      <c r="H28" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="I28" s="6"/>
+    </row>
+    <row r="29" spans="1:9" ht="18" hidden="1">
       <c r="A29" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C29,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
+        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$D29,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="1"/>
+      <c r="C29" s="4">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C29" s="18" t="str">
+      <c r="D29" s="18" t="str">
         <f ca="1"/>
         <v>profile_activity</v>
       </c>
-      <c r="D29" s="6" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C29,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
+      <c r="E29" s="6" t="str">
+        <f ca="1">_xlfn.XLOOKUP(D29,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
         <v>プロフィールの活動ジャンル</v>
       </c>
-      <c r="E29" s="6">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C29,テーブル定義_一覧!I:I)</f>
+      <c r="F29" s="6">
+        <f ca="1">SUMIF(テーブル定義_一覧!D:D,D29,テーブル定義_一覧!I:I)</f>
         <v>840</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="G29" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="H29" s="6"/>
+      <c r="H29" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="I29" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H29" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:I29" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="システム管理(静的)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -4012,10 +4255,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>550</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>553</v>
       </c>
       <c r="F2" s="11" t="str">
         <f>D2&amp;"_sequence_id"</f>
@@ -4026,7 +4269,7 @@
         <v>VtuberプロフィールID</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="I2" s="11">
         <f>_xlfn.LET(
@@ -4045,7 +4288,7 @@
         <v>32</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K2" s="11"/>
       <c r="L2" s="9"/>
@@ -4054,13 +4297,13 @@
         <v/>
       </c>
       <c r="N2" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q2" s="11"/>
       <c r="R2" s="9"/>
@@ -4089,7 +4332,7 @@
         <v>Vtuberプロフィール</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>50</v>
@@ -4121,10 +4364,10 @@
         <v/>
       </c>
       <c r="N3" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
@@ -4132,7 +4375,7 @@
       <c r="S3" s="9"/>
       <c r="T3" s="9"/>
       <c r="U3" s="11" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="18.75" customHeight="1">
@@ -4156,7 +4399,7 @@
         <v>Vtuberプロフィール</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>54</v>
@@ -4185,7 +4428,7 @@
         <v>48</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="M4" s="11">
         <f ca="1">IF(K4="","",IF(L4="","参照先未定義",_xlfn.XLOOKUP(L4,B:B,C:C,"エラー")))</f>
@@ -4195,7 +4438,7 @@
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
       <c r="Q4" s="11" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
@@ -4223,7 +4466,7 @@
         <v>Vtuberプロフィール</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>61</v>
@@ -4252,7 +4495,7 @@
         <v>48</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="M5" s="11">
         <f ca="1">IF(K5="","",IF(L5="","参照先未定義",_xlfn.XLOOKUP(L5,B:B,C:C,"エラー")))</f>
@@ -4262,7 +4505,7 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
       <c r="Q5" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
@@ -4298,7 +4541,7 @@
         <v>67</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I6" s="11">
         <f>_xlfn.LET(
@@ -4384,7 +4627,7 @@
         <v>48</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="M7" s="11">
         <f ca="1">IF(K7="","",IF(L7="","参照先未定義",_xlfn.XLOOKUP(L7,B:B,C:C,"エラー")))</f>
@@ -4396,7 +4639,7 @@
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
@@ -4430,7 +4673,7 @@
         <v>105</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I8" s="11">
         <f>_xlfn.LET(
@@ -4562,7 +4805,7 @@
         <v>112</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I10" s="11">
         <f>_xlfn.LET(
@@ -4694,7 +4937,7 @@
         <v>116</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I12" s="11">
         <f>_xlfn.LET(
@@ -4745,7 +4988,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>61</v>
@@ -4759,7 +5002,7 @@
         <v>所属ID</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I13" s="11">
         <f>_xlfn.LET(
@@ -4778,7 +5021,7 @@
         <v>32</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="9"/>
@@ -4787,13 +5030,13 @@
         <v/>
       </c>
       <c r="N13" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q13" s="11"/>
       <c r="R13" s="9"/>
@@ -4854,10 +5097,10 @@
         <v/>
       </c>
       <c r="N14" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
@@ -4918,7 +5161,7 @@
         <v>48</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="M15" s="11">
         <f ca="1">IF(K15="","",IF(L15="","参照先未定義",_xlfn.XLOOKUP(L15,B:B,C:C,"エラー")))</f>
@@ -4928,7 +5171,7 @@
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
@@ -5023,7 +5266,7 @@
         <v>105</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I17" s="11">
         <f>_xlfn.LET(
@@ -5155,7 +5398,7 @@
         <v>112</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I19" s="11">
         <f>_xlfn.LET(
@@ -5287,7 +5530,7 @@
         <v>116</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I21" s="11">
         <f>_xlfn.LET(
@@ -5352,7 +5595,7 @@
         <v>タグID</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I22" s="11">
         <f>_xlfn.LET(
@@ -5371,7 +5614,7 @@
         <v>32</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K22" s="11"/>
       <c r="L22" s="9"/>
@@ -5380,13 +5623,13 @@
         <v/>
       </c>
       <c r="N22" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P22" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q22" s="11"/>
       <c r="R22" s="9"/>
@@ -5447,10 +5690,10 @@
         <v/>
       </c>
       <c r="N23" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P23" s="11"/>
       <c r="Q23" s="11"/>
@@ -5488,7 +5731,7 @@
         <v>105</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I24" s="11">
         <f>_xlfn.LET(
@@ -5620,7 +5863,7 @@
         <v>112</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I26" s="11">
         <f>_xlfn.LET(
@@ -5752,7 +5995,7 @@
         <v>116</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I28" s="11">
         <f>_xlfn.LET(
@@ -5817,7 +6060,7 @@
         <v>バッジID</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I29" s="11">
         <f>_xlfn.LET(
@@ -5836,7 +6079,7 @@
         <v>32</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K29" s="11"/>
       <c r="L29" s="9"/>
@@ -5845,13 +6088,13 @@
         <v/>
       </c>
       <c r="N29" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P29" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q29" s="11"/>
       <c r="R29" s="9"/>
@@ -5912,10 +6155,10 @@
         <v/>
       </c>
       <c r="N30" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
@@ -5925,7 +6168,7 @@
         <v>48</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="18.75" customHeight="1">
@@ -5955,7 +6198,7 @@
         <v>105</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I31" s="11">
         <f>_xlfn.LET(
@@ -6087,7 +6330,7 @@
         <v>112</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I33" s="11">
         <f>_xlfn.LET(
@@ -6219,7 +6462,7 @@
         <v>116</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I35" s="11">
         <f>_xlfn.LET(
@@ -6270,7 +6513,7 @@
         <v>35</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>100</v>
+        <v>591</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>101</v>
@@ -6284,7 +6527,7 @@
         <v>活動状態ID</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I36" s="11">
         <f>_xlfn.LET(
@@ -6303,7 +6546,7 @@
         <v>32</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K36" s="11"/>
       <c r="L36" s="9"/>
@@ -6312,13 +6555,13 @@
         <v/>
       </c>
       <c r="N36" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O36" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P36" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q36" s="11"/>
       <c r="R36" s="9"/>
@@ -6379,10 +6622,10 @@
         <v/>
       </c>
       <c r="N37" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O37" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
@@ -6390,7 +6633,7 @@
       <c r="S37" s="9"/>
       <c r="T37" s="9"/>
       <c r="U37" s="11" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="18.75" customHeight="1">
@@ -6420,7 +6663,7 @@
         <v>105</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I38" s="11">
         <f>_xlfn.LET(
@@ -6552,7 +6795,7 @@
         <v>112</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I40" s="11">
         <f>_xlfn.LET(
@@ -6684,7 +6927,7 @@
         <v>116</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I42" s="11">
         <f>_xlfn.LET(
@@ -6749,7 +6992,7 @@
         <v>SNSリンクID</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I43" s="11">
         <f>_xlfn.LET(
@@ -6768,7 +7011,7 @@
         <v>32</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K43" s="11"/>
       <c r="L43" s="9"/>
@@ -6777,13 +7020,13 @@
         <v/>
       </c>
       <c r="N43" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O43" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P43" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q43" s="11"/>
       <c r="R43" s="9"/>
@@ -6841,7 +7084,7 @@
         <v>48</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M44" s="11">
         <f>IF(K44="","",IF(L44="","参照先未定義",_xlfn.XLOOKUP(L44,B:B,C:C,"エラー")))</f>
@@ -6853,7 +7096,7 @@
       <c r="O44" s="11"/>
       <c r="P44" s="11"/>
       <c r="Q44" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R44" s="9"/>
       <c r="S44" s="9"/>
@@ -6910,7 +7153,7 @@
         <v>48</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="M45" s="11">
         <f ca="1">IF(K45="","",IF(L45="","参照先未定義",_xlfn.XLOOKUP(L45,B:B,C:C,"エラー")))</f>
@@ -6920,7 +7163,7 @@
       <c r="O45" s="11"/>
       <c r="P45" s="11"/>
       <c r="Q45" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
@@ -7082,7 +7325,7 @@
         <v>105</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I48" s="11">
         <f>_xlfn.LET(
@@ -7214,7 +7457,7 @@
         <v>112</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I50" s="11">
         <f>_xlfn.LET(
@@ -7346,7 +7589,7 @@
         <v>116</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I52" s="11">
         <f>_xlfn.LET(
@@ -7411,7 +7654,7 @@
         <v>BBSID</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I53" s="11">
         <f>_xlfn.LET(
@@ -7430,7 +7673,7 @@
         <v>32</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K53" s="11"/>
       <c r="L53" s="9"/>
@@ -7439,13 +7682,13 @@
         <v/>
       </c>
       <c r="N53" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O53" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P53" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q53" s="11"/>
       <c r="R53" s="9"/>
@@ -7503,7 +7746,7 @@
         <v>48</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M54" s="11">
         <f>IF(K54="","",IF(L54="","参照先未定義",_xlfn.XLOOKUP(L54,B:B,C:C,"エラー")))</f>
@@ -7515,7 +7758,7 @@
       <c r="O54" s="11"/>
       <c r="P54" s="11"/>
       <c r="Q54" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R54" s="9"/>
       <c r="S54" s="9"/>
@@ -7572,7 +7815,7 @@
         <v>48</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="M55" s="11">
         <f ca="1">IF(K55="","",IF(L55="","参照先未定義",_xlfn.XLOOKUP(L55,B:B,C:C,"エラー")))</f>
@@ -7584,7 +7827,7 @@
       <c r="O55" s="11"/>
       <c r="P55" s="11"/>
       <c r="Q55" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R55" s="9"/>
       <c r="S55" s="9"/>
@@ -7681,7 +7924,7 @@
         <v>146</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I57" s="11">
         <f>_xlfn.LET(
@@ -7744,7 +7987,7 @@
         <v>105</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I58" s="11">
         <f>_xlfn.LET(
@@ -7876,7 +8119,7 @@
         <v>112</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I60" s="11">
         <f>_xlfn.LET(
@@ -8008,7 +8251,7 @@
         <v>116</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I62" s="11">
         <f>_xlfn.LET(
@@ -8073,7 +8316,7 @@
         <v>ページ編集者ID</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I63" s="11">
         <f>_xlfn.LET(
@@ -8092,7 +8335,7 @@
         <v>32</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K63" s="11"/>
       <c r="L63" s="9"/>
@@ -8101,13 +8344,13 @@
         <v/>
       </c>
       <c r="N63" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O63" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P63" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q63" s="11"/>
       <c r="R63" s="9"/>
@@ -8165,7 +8408,7 @@
         <v>48</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="M64" s="11">
         <f ca="1">IF(K64="","",IF(L64="","参照先未定義",_xlfn.XLOOKUP(L64,B:B,C:C,"エラー")))</f>
@@ -8177,7 +8420,7 @@
       <c r="O64" s="11"/>
       <c r="P64" s="11"/>
       <c r="Q64" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R64" s="9"/>
       <c r="S64" s="9"/>
@@ -8208,7 +8451,7 @@
         <v>49</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>54</v>
+        <v>610</v>
       </c>
       <c r="H65" s="11" t="s">
         <v>99</v>
@@ -8234,7 +8477,7 @@
         <v>48</v>
       </c>
       <c r="L65" s="9" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M65" s="11">
         <f>IF(K65="","",IF(L65="","参照先未定義",_xlfn.XLOOKUP(L65,B:B,C:C,"エラー")))</f>
@@ -8246,7 +8489,7 @@
       <c r="O65" s="11"/>
       <c r="P65" s="11"/>
       <c r="Q65" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R65" s="9"/>
       <c r="S65" s="9"/>
@@ -8303,7 +8546,7 @@
         <v>48</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="M66" s="11">
         <f ca="1">IF(K66="","",IF(L66="","参照先未定義",_xlfn.XLOOKUP(L66,B:B,C:C,"エラー")))</f>
@@ -8315,7 +8558,7 @@
       <c r="O66" s="11"/>
       <c r="P66" s="11"/>
       <c r="Q66" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R66" s="9"/>
       <c r="S66" s="9"/>
@@ -8475,7 +8718,7 @@
         <v>155</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I69" s="11">
         <f>_xlfn.LET(
@@ -8605,7 +8848,7 @@
         <v>105</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I71" s="11">
         <f>_xlfn.LET(
@@ -8737,7 +8980,7 @@
         <v>112</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I73" s="11">
         <f>_xlfn.LET(
@@ -8869,7 +9112,7 @@
         <v>116</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I75" s="11">
         <f>_xlfn.LET(
@@ -8934,7 +9177,7 @@
         <v>問い合わせID</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I76" s="11">
         <f>_xlfn.LET(
@@ -8953,7 +9196,7 @@
         <v>32</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K76" s="11"/>
       <c r="L76" s="9"/>
@@ -8962,13 +9205,13 @@
         <v/>
       </c>
       <c r="N76" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O76" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P76" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q76" s="11"/>
       <c r="R76" s="9"/>
@@ -9221,7 +9464,7 @@
         <v>48</v>
       </c>
       <c r="L80" s="9" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="M80" s="11">
         <f ca="1">IF(K80="","",IF(L80="","参照先未定義",_xlfn.XLOOKUP(L80,B:B,C:C,"エラー")))</f>
@@ -9231,7 +9474,7 @@
       <c r="O80" s="11"/>
       <c r="P80" s="11"/>
       <c r="Q80" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R80" s="9"/>
       <c r="S80" s="9"/>
@@ -9288,7 +9531,7 @@
         <v>48</v>
       </c>
       <c r="L81" s="9" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="M81" s="11">
         <f ca="1">IF(K81="","",IF(L81="","参照先未定義",_xlfn.XLOOKUP(L81,B:B,C:C,"エラー")))</f>
@@ -9298,7 +9541,7 @@
       <c r="O81" s="11"/>
       <c r="P81" s="11"/>
       <c r="Q81" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R81" s="9"/>
       <c r="S81" s="9"/>
@@ -9332,7 +9575,7 @@
         <v>105</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I82" s="11">
         <f>_xlfn.LET(
@@ -9464,7 +9707,7 @@
         <v>112</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I84" s="11">
         <f>_xlfn.LET(
@@ -9596,7 +9839,7 @@
         <v>116</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I86" s="11">
         <f>_xlfn.LET(
@@ -9647,10 +9890,10 @@
         <v>86</v>
       </c>
       <c r="D87" s="11" t="s">
+        <v>607</v>
+      </c>
+      <c r="E87" s="11" t="s">
         <v>171</v>
-      </c>
-      <c r="E87" s="11" t="s">
-        <v>172</v>
       </c>
       <c r="F87" s="11" t="str">
         <f>D87&amp;"_sequence_id"</f>
@@ -9661,7 +9904,7 @@
         <v>優先度ID</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I87" s="11">
         <f>_xlfn.LET(
@@ -9680,7 +9923,7 @@
         <v>32</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K87" s="11"/>
       <c r="L87" s="9"/>
@@ -9689,13 +9932,13 @@
         <v/>
       </c>
       <c r="N87" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O87" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P87" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q87" s="11"/>
       <c r="R87" s="9"/>
@@ -9756,10 +9999,10 @@
         <v/>
       </c>
       <c r="N88" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O88" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P88" s="11"/>
       <c r="Q88" s="11"/>
@@ -9789,10 +10032,10 @@
         <v>優先度</v>
       </c>
       <c r="F89" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G89" s="11" t="s">
         <v>173</v>
-      </c>
-      <c r="G89" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="H89" s="11" t="s">
         <v>51</v>
@@ -9828,7 +10071,7 @@
       <c r="S89" s="9"/>
       <c r="T89" s="9"/>
       <c r="U89" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="90" spans="1:21" ht="18.75" customHeight="1">
@@ -9858,7 +10101,7 @@
         <v>105</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I90" s="11">
         <f>_xlfn.LET(
@@ -9990,7 +10233,7 @@
         <v>112</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I92" s="11">
         <f>_xlfn.LET(
@@ -10122,7 +10365,7 @@
         <v>116</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I94" s="11">
         <f>_xlfn.LET(
@@ -10173,10 +10416,10 @@
         <v>94</v>
       </c>
       <c r="D95" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E95" s="11" t="s">
         <v>175</v>
-      </c>
-      <c r="E95" s="11" t="s">
-        <v>176</v>
       </c>
       <c r="F95" s="11" t="str">
         <f>D95&amp;"_sequence_id"</f>
@@ -10187,7 +10430,7 @@
         <v>対応状況ID</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I95" s="11">
         <f>_xlfn.LET(
@@ -10206,7 +10449,7 @@
         <v>32</v>
       </c>
       <c r="J95" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K95" s="11"/>
       <c r="L95" s="9"/>
@@ -10215,13 +10458,13 @@
         <v/>
       </c>
       <c r="N95" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O95" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P95" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q95" s="11"/>
       <c r="R95" s="9"/>
@@ -10282,10 +10525,10 @@
         <v/>
       </c>
       <c r="N96" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O96" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P96" s="11"/>
       <c r="Q96" s="11"/>
@@ -10315,10 +10558,10 @@
         <v>対応状況</v>
       </c>
       <c r="F97" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="G97" s="11" t="s">
         <v>177</v>
-      </c>
-      <c r="G97" s="11" t="s">
-        <v>178</v>
       </c>
       <c r="H97" s="11" t="s">
         <v>51</v>
@@ -10354,7 +10597,7 @@
       <c r="S97" s="9"/>
       <c r="T97" s="9"/>
       <c r="U97" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="98" spans="1:21" ht="18.75" customHeight="1">
@@ -10384,7 +10627,7 @@
         <v>105</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I98" s="11">
         <f>_xlfn.LET(
@@ -10516,7 +10759,7 @@
         <v>112</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I100" s="11">
         <f>_xlfn.LET(
@@ -10648,7 +10891,7 @@
         <v>116</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I102" s="11">
         <f>_xlfn.LET(
@@ -10699,10 +10942,10 @@
         <v>102</v>
       </c>
       <c r="D103" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E103" s="11" t="s">
         <v>179</v>
-      </c>
-      <c r="E103" s="11" t="s">
-        <v>180</v>
       </c>
       <c r="F103" s="11" t="str">
         <f>D103&amp;"_sequence_id"</f>
@@ -10713,7 +10956,7 @@
         <v>表示言語ID</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I103" s="11">
         <f>_xlfn.LET(
@@ -10732,7 +10975,7 @@
         <v>32</v>
       </c>
       <c r="J103" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K103" s="11"/>
       <c r="L103" s="9"/>
@@ -10741,13 +10984,13 @@
         <v/>
       </c>
       <c r="N103" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O103" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P103" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q103" s="11"/>
       <c r="R103" s="9"/>
@@ -10776,10 +11019,10 @@
         <v>表示言語</v>
       </c>
       <c r="F104" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="G104" s="11" t="s">
         <v>181</v>
-      </c>
-      <c r="G104" s="11" t="s">
-        <v>182</v>
       </c>
       <c r="H104" s="11" t="s">
         <v>71</v>
@@ -10808,10 +11051,10 @@
         <v/>
       </c>
       <c r="N104" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O104" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P104" s="11"/>
       <c r="Q104" s="11"/>
@@ -10819,7 +11062,7 @@
       <c r="S104" s="9"/>
       <c r="T104" s="9"/>
       <c r="U104" s="11" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="18.75" customHeight="1">
@@ -10843,10 +11086,10 @@
         <v>表示言語</v>
       </c>
       <c r="F105" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G105" s="11" t="s">
         <v>183</v>
-      </c>
-      <c r="G105" s="11" t="s">
-        <v>184</v>
       </c>
       <c r="H105" s="11" t="s">
         <v>99</v>
@@ -10869,10 +11112,10 @@
       </c>
       <c r="J105" s="11"/>
       <c r="K105" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="M105" s="11">
         <f ca="1">IF(K105="","",IF(L105="","参照先未定義",_xlfn.XLOOKUP(L105,B:B,C:C,"エラー")))</f>
@@ -10882,13 +11125,13 @@
       <c r="O105" s="11"/>
       <c r="P105" s="11"/>
       <c r="Q105" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R105" s="9"/>
       <c r="S105" s="9"/>
       <c r="T105" s="9"/>
       <c r="U105" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:21" ht="18.75" customHeight="1">
@@ -10912,13 +11155,13 @@
         <v>表示言語</v>
       </c>
       <c r="F106" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="G106" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="G106" s="11" t="s">
-        <v>187</v>
-      </c>
       <c r="H106" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I106" s="11">
         <f>_xlfn.LET(
@@ -10983,7 +11226,7 @@
         <v>105</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I107" s="11">
         <f>_xlfn.LET(
@@ -11115,7 +11358,7 @@
         <v>112</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I109" s="11">
         <f>_xlfn.LET(
@@ -11247,7 +11490,7 @@
         <v>116</v>
       </c>
       <c r="H111" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I111" s="11">
         <f>_xlfn.LET(
@@ -11298,10 +11541,10 @@
         <v>111</v>
       </c>
       <c r="D112" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E112" s="11" t="s">
         <v>188</v>
-      </c>
-      <c r="E112" s="11" t="s">
-        <v>189</v>
       </c>
       <c r="F112" s="11" t="str">
         <f>D112&amp;"_sequence_id"</f>
@@ -11312,7 +11555,7 @@
         <v>画面文言ID</v>
       </c>
       <c r="H112" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I112" s="11">
         <f>_xlfn.LET(
@@ -11331,7 +11574,7 @@
         <v>32</v>
       </c>
       <c r="J112" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K112" s="11"/>
       <c r="L112" s="9"/>
@@ -11340,13 +11583,13 @@
         <v/>
       </c>
       <c r="N112" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O112" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P112" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q112" s="11"/>
       <c r="R112" s="9"/>
@@ -11375,10 +11618,10 @@
         <v>画面文言</v>
       </c>
       <c r="F113" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="G113" s="11" t="s">
         <v>181</v>
-      </c>
-      <c r="G113" s="11" t="s">
-        <v>182</v>
       </c>
       <c r="H113" s="11" t="s">
         <v>99</v>
@@ -11404,7 +11647,7 @@
         <v>48</v>
       </c>
       <c r="L113" s="9" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="M113" s="11">
         <f ca="1">IF(K113="","",IF(L113="","参照先未定義",_xlfn.XLOOKUP(L113,B:B,C:C,"エラー")))</f>
@@ -11414,7 +11657,7 @@
       <c r="O113" s="11"/>
       <c r="P113" s="11"/>
       <c r="Q113" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="R113" s="9"/>
       <c r="S113" s="9"/>
@@ -11442,13 +11685,13 @@
         <v>画面文言</v>
       </c>
       <c r="F114" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G114" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="G114" s="11" t="s">
-        <v>191</v>
-      </c>
       <c r="H114" s="11" t="s">
-        <v>552</v>
+        <v>99</v>
       </c>
       <c r="I114" s="11">
         <f>_xlfn.LET(
@@ -11474,14 +11717,12 @@
         <v/>
       </c>
       <c r="N114" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="O114" s="11" t="s">
-        <v>453</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="O114" s="11"/>
       <c r="P114" s="11"/>
       <c r="Q114" s="11" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="R114" s="9"/>
       <c r="S114" s="9"/>
@@ -11509,10 +11750,10 @@
         <v>画面文言</v>
       </c>
       <c r="F115" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="G115" s="11" t="s">
         <v>193</v>
-      </c>
-      <c r="G115" s="11" t="s">
-        <v>194</v>
       </c>
       <c r="H115" s="11" t="s">
         <v>81</v>
@@ -11544,7 +11785,7 @@
       <c r="O115" s="11"/>
       <c r="P115" s="11"/>
       <c r="Q115" s="11" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="R115" s="9"/>
       <c r="S115" s="9"/>
@@ -11557,7 +11798,7 @@
       </c>
       <c r="B116" s="9" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>screen_word.message_type</v>
+        <v>screen_word.message_id_table</v>
       </c>
       <c r="C116" s="10">
         <f t="shared" si="0"/>
@@ -11572,13 +11813,13 @@
         <v>画面文言</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>493</v>
+        <v>608</v>
       </c>
       <c r="G116" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="H116" s="11" t="s">
         <v>492</v>
-      </c>
-      <c r="H116" s="11" t="s">
-        <v>495</v>
       </c>
       <c r="I116" s="11" t="str">
         <f>_xlfn.LET(
@@ -11607,13 +11848,13 @@
       <c r="O116" s="11"/>
       <c r="P116" s="11"/>
       <c r="Q116" s="11" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="R116" s="9"/>
       <c r="S116" s="9"/>
       <c r="T116" s="9"/>
       <c r="U116" s="11" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="117" spans="1:21" ht="18.75" customHeight="1">
@@ -11643,7 +11884,7 @@
         <v>105</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I117" s="11">
         <f>_xlfn.LET(
@@ -11775,7 +12016,7 @@
         <v>112</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I119" s="11">
         <f>_xlfn.LET(
@@ -11907,7 +12148,7 @@
         <v>116</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I121" s="11">
         <f>_xlfn.LET(
@@ -11958,10 +12199,10 @@
         <v>121</v>
       </c>
       <c r="D122" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E122" s="11" t="s">
         <v>195</v>
-      </c>
-      <c r="E122" s="11" t="s">
-        <v>196</v>
       </c>
       <c r="F122" s="11" t="str">
         <f>D122&amp;"_sequence_id"</f>
@@ -11972,7 +12213,7 @@
         <v>サポートするSNSID</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I122" s="11">
         <f>_xlfn.LET(
@@ -11991,7 +12232,7 @@
         <v>32</v>
       </c>
       <c r="J122" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K122" s="11"/>
       <c r="L122" s="9"/>
@@ -12000,13 +12241,13 @@
         <v/>
       </c>
       <c r="N122" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O122" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P122" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q122" s="11"/>
       <c r="R122" s="9"/>
@@ -12035,10 +12276,10 @@
         <v>サポートするSNS</v>
       </c>
       <c r="F123" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G123" s="11" t="s">
         <v>197</v>
-      </c>
-      <c r="G123" s="11" t="s">
-        <v>198</v>
       </c>
       <c r="H123" s="11" t="s">
         <v>65</v>
@@ -12067,10 +12308,10 @@
         <v/>
       </c>
       <c r="N123" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O123" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P123" s="11"/>
       <c r="Q123" s="11"/>
@@ -12100,10 +12341,10 @@
         <v>サポートするSNS</v>
       </c>
       <c r="F124" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="G124" s="11" t="s">
         <v>199</v>
-      </c>
-      <c r="G124" s="11" t="s">
-        <v>200</v>
       </c>
       <c r="H124" s="11" t="s">
         <v>99</v>
@@ -12129,7 +12370,7 @@
         <v>48</v>
       </c>
       <c r="L124" s="9" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="M124" s="11">
         <f ca="1">IF(K124="","",IF(L124="","参照先未定義",_xlfn.XLOOKUP(L124,B:B,C:C,"エラー")))</f>
@@ -12141,13 +12382,13 @@
       <c r="O124" s="11"/>
       <c r="P124" s="11"/>
       <c r="Q124" s="11" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="R124" s="9"/>
       <c r="S124" s="9"/>
       <c r="T124" s="9"/>
       <c r="U124" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="125" spans="1:21" ht="18.75" customHeight="1">
@@ -12171,13 +12412,13 @@
         <v>サポートするSNS</v>
       </c>
       <c r="F125" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="G125" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="G125" s="11" t="s">
-        <v>203</v>
-      </c>
       <c r="H125" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I125" s="11">
         <f>_xlfn.LET(
@@ -12236,13 +12477,13 @@
         <v>サポートするSNS</v>
       </c>
       <c r="F126" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="G126" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="G126" s="11" t="s">
-        <v>205</v>
-      </c>
       <c r="H126" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I126" s="11">
         <f>_xlfn.LET(
@@ -12307,7 +12548,7 @@
         <v>105</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I127" s="11">
         <f>_xlfn.LET(
@@ -12439,7 +12680,7 @@
         <v>112</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I129" s="11">
         <f>_xlfn.LET(
@@ -12571,7 +12812,7 @@
         <v>116</v>
       </c>
       <c r="H131" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I131" s="11">
         <f>_xlfn.LET(
@@ -12622,10 +12863,10 @@
         <v>131</v>
       </c>
       <c r="D132" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="E132" s="11" t="s">
         <v>206</v>
-      </c>
-      <c r="E132" s="11" t="s">
-        <v>207</v>
       </c>
       <c r="F132" s="11" t="str">
         <f>D132&amp;"_sequence_id"</f>
@@ -12636,7 +12877,7 @@
         <v>プロフィール通報ID</v>
       </c>
       <c r="H132" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I132" s="11">
         <f>_xlfn.LET(
@@ -12655,7 +12896,7 @@
         <v>32</v>
       </c>
       <c r="J132" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K132" s="11"/>
       <c r="L132" s="9"/>
@@ -12664,13 +12905,13 @@
         <v/>
       </c>
       <c r="N132" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O132" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P132" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q132" s="11"/>
       <c r="R132" s="9"/>
@@ -12728,7 +12969,7 @@
         <v>48</v>
       </c>
       <c r="L133" s="9" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="M133" s="11">
         <f ca="1">IF(K133="","",IF(L133="","参照先未定義",_xlfn.XLOOKUP(L133,B:B,C:C,"エラー")))</f>
@@ -12738,7 +12979,7 @@
       <c r="O133" s="11"/>
       <c r="P133" s="11"/>
       <c r="Q133" s="11" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="R133" s="9"/>
       <c r="S133" s="9"/>
@@ -12795,7 +13036,7 @@
         <v>48</v>
       </c>
       <c r="L134" s="9" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M134" s="11">
         <f>IF(K134="","",IF(L134="","参照先未定義",_xlfn.XLOOKUP(L134,B:B,C:C,"エラー")))</f>
@@ -12807,7 +13048,7 @@
       <c r="O134" s="11"/>
       <c r="P134" s="11"/>
       <c r="Q134" s="11" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="R134" s="9"/>
       <c r="S134" s="9"/>
@@ -12835,10 +13076,10 @@
         <v>プロフィール通報</v>
       </c>
       <c r="F135" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G135" s="11" t="s">
         <v>208</v>
-      </c>
-      <c r="G135" s="11" t="s">
-        <v>209</v>
       </c>
       <c r="H135" s="11" t="s">
         <v>99</v>
@@ -12864,7 +13105,7 @@
         <v>48</v>
       </c>
       <c r="L135" s="9" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="M135" s="11">
         <f ca="1">IF(K135="","",IF(L135="","参照先未定義",_xlfn.XLOOKUP(L135,B:B,C:C,"エラー")))</f>
@@ -12876,7 +13117,7 @@
       <c r="O135" s="11"/>
       <c r="P135" s="11"/>
       <c r="Q135" s="11" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="R135" s="9" t="s">
         <v>48</v>
@@ -12906,10 +13147,10 @@
         <v>プロフィール通報</v>
       </c>
       <c r="F136" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="G136" s="11" t="s">
         <v>210</v>
-      </c>
-      <c r="G136" s="11" t="s">
-        <v>211</v>
       </c>
       <c r="H136" s="11" t="s">
         <v>81</v>
@@ -12971,13 +13212,13 @@
         <v>プロフィール通報</v>
       </c>
       <c r="F137" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="G137" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="G137" s="11" t="s">
-        <v>213</v>
-      </c>
       <c r="H137" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I137" s="11">
         <f>_xlfn.LET(
@@ -13042,7 +13283,7 @@
         <v>105</v>
       </c>
       <c r="H138" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I138" s="11">
         <f>_xlfn.LET(
@@ -13174,7 +13415,7 @@
         <v>112</v>
       </c>
       <c r="H140" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I140" s="11">
         <f>_xlfn.LET(
@@ -13306,7 +13547,7 @@
         <v>116</v>
       </c>
       <c r="H142" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I142" s="11">
         <f>_xlfn.LET(
@@ -13357,10 +13598,10 @@
         <v>142</v>
       </c>
       <c r="D143" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E143" s="11" t="s">
         <v>214</v>
-      </c>
-      <c r="E143" s="11" t="s">
-        <v>215</v>
       </c>
       <c r="F143" s="11" t="str">
         <f>D143&amp;"_sequence_id"</f>
@@ -13371,7 +13612,7 @@
         <v>通報理由ID</v>
       </c>
       <c r="H143" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I143" s="11">
         <f>_xlfn.LET(
@@ -13390,7 +13631,7 @@
         <v>32</v>
       </c>
       <c r="J143" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K143" s="11"/>
       <c r="L143" s="9"/>
@@ -13399,13 +13640,13 @@
         <v/>
       </c>
       <c r="N143" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O143" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P143" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q143" s="11"/>
       <c r="R143" s="9"/>
@@ -13434,10 +13675,10 @@
         <v>通報理由</v>
       </c>
       <c r="F144" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G144" s="11" t="s">
         <v>208</v>
-      </c>
-      <c r="G144" s="11" t="s">
-        <v>209</v>
       </c>
       <c r="H144" s="11" t="s">
         <v>71</v>
@@ -13466,10 +13707,10 @@
         <v/>
       </c>
       <c r="N144" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O144" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P144" s="11"/>
       <c r="Q144" s="11"/>
@@ -13477,7 +13718,7 @@
       <c r="S144" s="9"/>
       <c r="T144" s="9"/>
       <c r="U144" s="11" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="145" spans="1:21" ht="18.75" customHeight="1">
@@ -13507,7 +13748,7 @@
         <v>105</v>
       </c>
       <c r="H145" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I145" s="11">
         <f>_xlfn.LET(
@@ -13639,7 +13880,7 @@
         <v>112</v>
       </c>
       <c r="H147" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I147" s="11">
         <f>_xlfn.LET(
@@ -13771,7 +14012,7 @@
         <v>116</v>
       </c>
       <c r="H149" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I149" s="11">
         <f>_xlfn.LET(
@@ -13822,10 +14063,10 @@
         <v>149</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E150" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F150" s="11" t="str">
         <f>D150&amp;"_sequence_id"</f>
@@ -13836,7 +14077,7 @@
         <v>ユーザーID</v>
       </c>
       <c r="H150" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I150" s="11">
         <f>_xlfn.LET(
@@ -13855,7 +14096,7 @@
         <v>32</v>
       </c>
       <c r="J150" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K150" s="11"/>
       <c r="L150" s="9"/>
@@ -13864,13 +14105,13 @@
         <v/>
       </c>
       <c r="N150" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O150" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P150" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q150" s="11"/>
       <c r="R150" s="9"/>
@@ -13899,7 +14140,7 @@
         <v>ユーザー</v>
       </c>
       <c r="F151" s="11" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="G151" s="11" t="s">
         <v>54</v>
@@ -13931,10 +14172,10 @@
         <v/>
       </c>
       <c r="N151" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O151" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P151" s="11" t="s">
         <v>52</v>
@@ -14027,10 +14268,10 @@
         <v>ユーザー</v>
       </c>
       <c r="F153" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G153" s="11" t="s">
         <v>217</v>
-      </c>
-      <c r="G153" s="11" t="s">
-        <v>218</v>
       </c>
       <c r="H153" s="11" t="s">
         <v>99</v>
@@ -14056,7 +14297,7 @@
         <v>48</v>
       </c>
       <c r="L153" s="9" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="M153" s="11">
         <f ca="1">IF(K153="","",IF(L153="","参照先未定義",_xlfn.XLOOKUP(L153,B:B,C:C,"エラー")))</f>
@@ -14066,7 +14307,7 @@
       <c r="O153" s="11"/>
       <c r="P153" s="11"/>
       <c r="Q153" s="11" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="R153" s="9"/>
       <c r="S153" s="9"/>
@@ -14094,13 +14335,13 @@
         <v>ユーザー</v>
       </c>
       <c r="F154" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="G154" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="G154" s="11" t="s">
-        <v>220</v>
-      </c>
       <c r="H154" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I154" s="11">
         <f>_xlfn.LET(
@@ -14133,7 +14374,7 @@
         <v>0</v>
       </c>
       <c r="Q154" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R154" s="9"/>
       <c r="S154" s="9"/>
@@ -14161,10 +14402,10 @@
         <v>ユーザー</v>
       </c>
       <c r="F155" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G155" s="11" t="s">
         <v>222</v>
-      </c>
-      <c r="G155" s="11" t="s">
-        <v>223</v>
       </c>
       <c r="H155" s="11" t="s">
         <v>99</v>
@@ -14190,7 +14431,7 @@
         <v>48</v>
       </c>
       <c r="L155" s="9" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="M155" s="11">
         <f ca="1">IF(K155="","",IF(L155="","参照先未定義",_xlfn.XLOOKUP(L155,B:B,C:C,"エラー")))</f>
@@ -14200,7 +14441,7 @@
       <c r="O155" s="11"/>
       <c r="P155" s="11"/>
       <c r="Q155" s="11" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="R155" s="9"/>
       <c r="S155" s="9"/>
@@ -14228,13 +14469,13 @@
         <v>ユーザー</v>
       </c>
       <c r="F156" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="G156" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="G156" s="11" t="s">
-        <v>225</v>
-      </c>
       <c r="H156" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I156" s="11">
         <f>_xlfn.LET(
@@ -14293,10 +14534,10 @@
         <v>ユーザー</v>
       </c>
       <c r="F157" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="G157" s="11" t="s">
         <v>226</v>
-      </c>
-      <c r="G157" s="11" t="s">
-        <v>227</v>
       </c>
       <c r="H157" s="11" t="s">
         <v>99</v>
@@ -14322,7 +14563,7 @@
         <v>48</v>
       </c>
       <c r="L157" s="9" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="M157" s="11">
         <f ca="1">IF(K157="","",IF(L157="","参照先未定義",_xlfn.XLOOKUP(L157,B:B,C:C,"エラー")))</f>
@@ -14333,10 +14574,10 @@
       </c>
       <c r="O157" s="11"/>
       <c r="P157" s="11" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="Q157" s="11" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="R157" s="9"/>
       <c r="S157" s="9"/>
@@ -14364,10 +14605,10 @@
         <v>ユーザー</v>
       </c>
       <c r="F158" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="G158" s="11" t="s">
         <v>179</v>
-      </c>
-      <c r="G158" s="11" t="s">
-        <v>180</v>
       </c>
       <c r="H158" s="11" t="s">
         <v>99</v>
@@ -14393,7 +14634,7 @@
         <v>48</v>
       </c>
       <c r="L158" s="9" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="M158" s="11">
         <f ca="1">IF(K158="","",IF(L158="","参照先未定義",_xlfn.XLOOKUP(L158,B:B,C:C,"エラー")))</f>
@@ -14404,10 +14645,10 @@
       </c>
       <c r="O158" s="11"/>
       <c r="P158" s="11" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="Q158" s="11" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="R158" s="9"/>
       <c r="S158" s="9"/>
@@ -14441,7 +14682,7 @@
         <v>105</v>
       </c>
       <c r="H159" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I159" s="11">
         <f>_xlfn.LET(
@@ -14573,7 +14814,7 @@
         <v>112</v>
       </c>
       <c r="H161" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I161" s="11">
         <f>_xlfn.LET(
@@ -14705,7 +14946,7 @@
         <v>116</v>
       </c>
       <c r="H163" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I163" s="11">
         <f>_xlfn.LET(
@@ -14756,10 +14997,10 @@
         <v>163</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E164" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F164" s="11" t="str">
         <f>D164&amp;"_sequence_id"</f>
@@ -14770,7 +15011,7 @@
         <v>画面テーマID</v>
       </c>
       <c r="H164" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I164" s="11">
         <f>_xlfn.LET(
@@ -14789,7 +15030,7 @@
         <v>32</v>
       </c>
       <c r="J164" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K164" s="11"/>
       <c r="L164" s="9"/>
@@ -14798,13 +15039,13 @@
         <v/>
       </c>
       <c r="N164" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O164" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P164" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q164" s="11"/>
       <c r="R164" s="9"/>
@@ -14833,10 +15074,10 @@
         <v>画面テーマ</v>
       </c>
       <c r="F165" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="G165" s="11" t="s">
         <v>229</v>
-      </c>
-      <c r="G165" s="11" t="s">
-        <v>230</v>
       </c>
       <c r="H165" s="11" t="s">
         <v>71</v>
@@ -14865,10 +15106,10 @@
         <v/>
       </c>
       <c r="N165" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O165" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P165" s="11"/>
       <c r="Q165" s="11"/>
@@ -14876,7 +15117,7 @@
       <c r="S165" s="9"/>
       <c r="T165" s="9"/>
       <c r="U165" s="11" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="166" spans="1:21" ht="18.75" customHeight="1">
@@ -14906,7 +15147,7 @@
         <v>105</v>
       </c>
       <c r="H166" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I166" s="11">
         <f>_xlfn.LET(
@@ -15038,7 +15279,7 @@
         <v>112</v>
       </c>
       <c r="H168" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I168" s="11">
         <f>_xlfn.LET(
@@ -15170,7 +15411,7 @@
         <v>116</v>
       </c>
       <c r="H170" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I170" s="11">
         <f>_xlfn.LET(
@@ -15221,10 +15462,10 @@
         <v>170</v>
       </c>
       <c r="D171" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="E171" s="11" t="s">
         <v>231</v>
-      </c>
-      <c r="E171" s="11" t="s">
-        <v>232</v>
       </c>
       <c r="F171" s="11" t="str">
         <f>D171&amp;"_sequence_id"</f>
@@ -15235,7 +15476,7 @@
         <v>ユーザー権限ID</v>
       </c>
       <c r="H171" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I171" s="11">
         <f>_xlfn.LET(
@@ -15254,7 +15495,7 @@
         <v>32</v>
       </c>
       <c r="J171" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K171" s="11"/>
       <c r="L171" s="9"/>
@@ -15263,13 +15504,13 @@
         <v/>
       </c>
       <c r="N171" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O171" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P171" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q171" s="11"/>
       <c r="R171" s="9"/>
@@ -15298,10 +15539,10 @@
         <v>ユーザー権限</v>
       </c>
       <c r="F172" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G172" s="11" t="s">
         <v>217</v>
-      </c>
-      <c r="G172" s="11" t="s">
-        <v>218</v>
       </c>
       <c r="H172" s="11" t="s">
         <v>51</v>
@@ -15330,10 +15571,10 @@
         <v/>
       </c>
       <c r="N172" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O172" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P172" s="11"/>
       <c r="Q172" s="11"/>
@@ -15341,7 +15582,7 @@
       <c r="S172" s="9"/>
       <c r="T172" s="9"/>
       <c r="U172" s="11" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="173" spans="1:21" ht="18.75" customHeight="1">
@@ -15371,7 +15612,7 @@
         <v>105</v>
       </c>
       <c r="H173" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I173" s="11">
         <f>_xlfn.LET(
@@ -15503,7 +15744,7 @@
         <v>112</v>
       </c>
       <c r="H175" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I175" s="11">
         <f>_xlfn.LET(
@@ -15635,7 +15876,7 @@
         <v>116</v>
       </c>
       <c r="H177" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I177" s="11">
         <f>_xlfn.LET(
@@ -15686,10 +15927,10 @@
         <v>177</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E178" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F178" s="11" t="str">
         <f>D178&amp;"_sequence_id"</f>
@@ -15700,7 +15941,7 @@
         <v>画像(ユーザー投稿)ID</v>
       </c>
       <c r="H178" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I178" s="11">
         <f>_xlfn.LET(
@@ -15719,7 +15960,7 @@
         <v>32</v>
       </c>
       <c r="J178" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K178" s="11"/>
       <c r="L178" s="9"/>
@@ -15728,13 +15969,13 @@
         <v/>
       </c>
       <c r="N178" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O178" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P178" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q178" s="11"/>
       <c r="R178" s="9"/>
@@ -15792,7 +16033,7 @@
         <v>48</v>
       </c>
       <c r="L179" s="9" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="M179" s="11">
         <f ca="1">IF(K179="","",IF(L179="","参照先未定義",_xlfn.XLOOKUP(L179,B:B,C:C,"エラー")))</f>
@@ -15804,7 +16045,7 @@
       <c r="O179" s="11"/>
       <c r="P179" s="11"/>
       <c r="Q179" s="11" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="R179" s="9"/>
       <c r="S179" s="9"/>
@@ -15832,13 +16073,13 @@
         <v>画像(ユーザー投稿)</v>
       </c>
       <c r="F180" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="G180" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="G180" s="11" t="s">
+      <c r="H180" s="11" t="s">
         <v>235</v>
-      </c>
-      <c r="H180" s="11" t="s">
-        <v>236</v>
       </c>
       <c r="I180" s="11">
         <f>_xlfn.LET(
@@ -15895,13 +16136,13 @@
         <v>画像(ユーザー投稿)</v>
       </c>
       <c r="F181" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="G181" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="G181" s="11" t="s">
+      <c r="H181" s="11" t="s">
         <v>238</v>
-      </c>
-      <c r="H181" s="11" t="s">
-        <v>239</v>
       </c>
       <c r="I181" s="11">
         <f>_xlfn.LET(
@@ -15932,7 +16173,7 @@
       <c r="O181" s="11"/>
       <c r="P181" s="11"/>
       <c r="Q181" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="R181" s="9"/>
       <c r="S181" s="9"/>
@@ -15960,13 +16201,13 @@
         <v>画像(ユーザー投稿)</v>
       </c>
       <c r="F182" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="G182" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="G182" s="11" t="s">
-        <v>242</v>
-      </c>
       <c r="H182" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I182" s="11">
         <f>_xlfn.LET(
@@ -15995,7 +16236,7 @@
       <c r="O182" s="11"/>
       <c r="P182" s="11"/>
       <c r="Q182" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="R182" s="9"/>
       <c r="S182" s="9"/>
@@ -16023,13 +16264,13 @@
         <v>画像(ユーザー投稿)</v>
       </c>
       <c r="F183" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="G183" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="G183" s="11" t="s">
+      <c r="H183" s="11" t="s">
         <v>245</v>
-      </c>
-      <c r="H183" s="11" t="s">
-        <v>246</v>
       </c>
       <c r="I183" s="11">
         <f>_xlfn.LET(
@@ -16058,7 +16299,7 @@
       <c r="O183" s="11"/>
       <c r="P183" s="11"/>
       <c r="Q183" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="R183" s="9"/>
       <c r="S183" s="9"/>
@@ -16086,10 +16327,10 @@
         <v>画像(ユーザー投稿)</v>
       </c>
       <c r="F184" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="G184" s="11" t="s">
         <v>248</v>
-      </c>
-      <c r="G184" s="11" t="s">
-        <v>249</v>
       </c>
       <c r="H184" s="11" t="s">
         <v>99</v>
@@ -16150,7 +16391,7 @@
         <v>72</v>
       </c>
       <c r="G185" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H185" s="11" t="s">
         <v>99</v>
@@ -16208,10 +16449,10 @@
         <v>画像(ユーザー投稿)</v>
       </c>
       <c r="F186" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="G186" s="11" t="s">
         <v>251</v>
-      </c>
-      <c r="G186" s="11" t="s">
-        <v>252</v>
       </c>
       <c r="H186" s="11" t="s">
         <v>99</v>
@@ -16269,10 +16510,10 @@
         <v>画像(ユーザー投稿)</v>
       </c>
       <c r="F187" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G187" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="G187" s="11" t="s">
-        <v>254</v>
       </c>
       <c r="H187" s="11" t="s">
         <v>162</v>
@@ -16336,7 +16577,7 @@
         <v>105</v>
       </c>
       <c r="H188" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I188" s="11">
         <f>_xlfn.LET(
@@ -16468,7 +16709,7 @@
         <v>112</v>
       </c>
       <c r="H190" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I190" s="11">
         <f>_xlfn.LET(
@@ -16600,7 +16841,7 @@
         <v>116</v>
       </c>
       <c r="H192" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I192" s="11">
         <f>_xlfn.LET(
@@ -16651,10 +16892,10 @@
         <v>192</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E193" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F193" s="11" t="str">
         <f>D193&amp;"_sequence_id"</f>
@@ -16665,7 +16906,7 @@
         <v>画像(システム管理)ID</v>
       </c>
       <c r="H193" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I193" s="11">
         <f>_xlfn.LET(
@@ -16684,7 +16925,7 @@
         <v>32</v>
       </c>
       <c r="J193" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K193" s="11"/>
       <c r="L193" s="9"/>
@@ -16693,13 +16934,13 @@
         <v/>
       </c>
       <c r="N193" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O193" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P193" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q193" s="11"/>
       <c r="R193" s="9"/>
@@ -16728,13 +16969,13 @@
         <v>画像(システム管理)</v>
       </c>
       <c r="F194" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="G194" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="G194" s="11" t="s">
+      <c r="H194" s="11" t="s">
         <v>235</v>
-      </c>
-      <c r="H194" s="11" t="s">
-        <v>236</v>
       </c>
       <c r="I194" s="11">
         <f>_xlfn.LET(
@@ -16791,13 +17032,13 @@
         <v>画像(システム管理)</v>
       </c>
       <c r="F195" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="G195" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="G195" s="11" t="s">
+      <c r="H195" s="11" t="s">
         <v>238</v>
-      </c>
-      <c r="H195" s="11" t="s">
-        <v>239</v>
       </c>
       <c r="I195" s="11">
         <f>_xlfn.LET(
@@ -16828,7 +17069,7 @@
       <c r="O195" s="11"/>
       <c r="P195" s="11"/>
       <c r="Q195" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="R195" s="9"/>
       <c r="S195" s="9"/>
@@ -16856,13 +17097,13 @@
         <v>画像(システム管理)</v>
       </c>
       <c r="F196" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="G196" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="G196" s="11" t="s">
-        <v>242</v>
-      </c>
       <c r="H196" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I196" s="11">
         <f>_xlfn.LET(
@@ -16891,7 +17132,7 @@
       <c r="O196" s="11"/>
       <c r="P196" s="11"/>
       <c r="Q196" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="R196" s="9"/>
       <c r="S196" s="9"/>
@@ -16919,13 +17160,13 @@
         <v>画像(システム管理)</v>
       </c>
       <c r="F197" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="G197" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="G197" s="11" t="s">
+      <c r="H197" s="11" t="s">
         <v>245</v>
-      </c>
-      <c r="H197" s="11" t="s">
-        <v>246</v>
       </c>
       <c r="I197" s="11">
         <f>_xlfn.LET(
@@ -16954,7 +17195,7 @@
       <c r="O197" s="11"/>
       <c r="P197" s="11"/>
       <c r="Q197" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="R197" s="9"/>
       <c r="S197" s="9"/>
@@ -16982,10 +17223,10 @@
         <v>画像(システム管理)</v>
       </c>
       <c r="F198" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="G198" s="11" t="s">
         <v>248</v>
-      </c>
-      <c r="G198" s="11" t="s">
-        <v>249</v>
       </c>
       <c r="H198" s="11" t="s">
         <v>99</v>
@@ -17046,7 +17287,7 @@
         <v>72</v>
       </c>
       <c r="G199" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H199" s="11" t="s">
         <v>99</v>
@@ -17104,10 +17345,10 @@
         <v>画像(システム管理)</v>
       </c>
       <c r="F200" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="G200" s="11" t="s">
         <v>251</v>
-      </c>
-      <c r="G200" s="11" t="s">
-        <v>252</v>
       </c>
       <c r="H200" s="11" t="s">
         <v>99</v>
@@ -17165,10 +17406,10 @@
         <v>画像(システム管理)</v>
       </c>
       <c r="F201" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G201" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="G201" s="11" t="s">
-        <v>254</v>
       </c>
       <c r="H201" s="11" t="s">
         <v>162</v>
@@ -17232,7 +17473,7 @@
         <v>105</v>
       </c>
       <c r="H202" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I202" s="11">
         <f>_xlfn.LET(
@@ -17364,7 +17605,7 @@
         <v>112</v>
       </c>
       <c r="H204" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I204" s="11">
         <f>_xlfn.LET(
@@ -17496,7 +17737,7 @@
         <v>116</v>
       </c>
       <c r="H206" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I206" s="11">
         <f>_xlfn.LET(
@@ -17547,10 +17788,10 @@
         <v>206</v>
       </c>
       <c r="D207" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E207" s="11" t="s">
         <v>256</v>
-      </c>
-      <c r="E207" s="11" t="s">
-        <v>257</v>
       </c>
       <c r="F207" s="11" t="str">
         <f>D207&amp;"_sequence_id"</f>
@@ -17561,7 +17802,7 @@
         <v>画面要素ID</v>
       </c>
       <c r="H207" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I207" s="11">
         <f>_xlfn.LET(
@@ -17580,7 +17821,7 @@
         <v>32</v>
       </c>
       <c r="J207" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K207" s="11"/>
       <c r="L207" s="9"/>
@@ -17589,13 +17830,13 @@
         <v/>
       </c>
       <c r="N207" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O207" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P207" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q207" s="11"/>
       <c r="R207" s="9"/>
@@ -17624,10 +17865,10 @@
         <v>画面要素</v>
       </c>
       <c r="F208" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G208" s="11" t="s">
         <v>190</v>
-      </c>
-      <c r="G208" s="11" t="s">
-        <v>191</v>
       </c>
       <c r="H208" s="11" t="s">
         <v>71</v>
@@ -17656,14 +17897,14 @@
         <v/>
       </c>
       <c r="N208" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="O208" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P208" s="11"/>
       <c r="Q208" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R208" s="9"/>
       <c r="S208" s="9"/>
@@ -17697,7 +17938,7 @@
         <v>105</v>
       </c>
       <c r="H209" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I209" s="11">
         <f>_xlfn.LET(
@@ -17829,7 +18070,7 @@
         <v>112</v>
       </c>
       <c r="H211" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I211" s="11">
         <f>_xlfn.LET(
@@ -17961,7 +18202,7 @@
         <v>116</v>
       </c>
       <c r="H213" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I213" s="11">
         <f>_xlfn.LET(
@@ -18012,7 +18253,7 @@
         <v>213</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E214" s="11" t="s">
         <v>98</v>
@@ -18026,7 +18267,7 @@
         <v>いいねID</v>
       </c>
       <c r="H214" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I214" s="11">
         <f>_xlfn.LET(
@@ -18045,7 +18286,7 @@
         <v>32</v>
       </c>
       <c r="J214" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K214" s="11"/>
       <c r="L214" s="9"/>
@@ -18054,13 +18295,13 @@
         <v/>
       </c>
       <c r="N214" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O214" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P214" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q214" s="11"/>
       <c r="R214" s="9"/>
@@ -18081,17 +18322,17 @@
         <v>214</v>
       </c>
       <c r="D215" s="11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E215" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E215" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>いいね</v>
       </c>
       <c r="F215" s="11" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G215" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H215" s="11" t="s">
         <v>99</v>
@@ -18114,10 +18355,10 @@
       </c>
       <c r="J215" s="11"/>
       <c r="K215" s="11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L215" s="9" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="M215" s="11">
         <f ca="1">IF(K215="","",IF(L215="","参照先未定義",_xlfn.XLOOKUP(L215,B:B,C:C,"エラー")))</f>
@@ -18127,11 +18368,11 @@
         <v>48</v>
       </c>
       <c r="O215" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P215" s="11"/>
       <c r="Q215" s="11" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="R215" s="9"/>
       <c r="S215" s="9"/>
@@ -18159,10 +18400,10 @@
         <v>いいね</v>
       </c>
       <c r="F216" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G216" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H216" s="11" t="s">
         <v>99</v>
@@ -18185,10 +18426,10 @@
       </c>
       <c r="J216" s="11"/>
       <c r="K216" s="11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L216" s="9" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="M216" s="11">
         <f ca="1">IF(K216="","",IF(L216="","参照先未定義",_xlfn.XLOOKUP(L216,B:B,C:C,"エラー")))</f>
@@ -18198,11 +18439,11 @@
         <v>48</v>
       </c>
       <c r="O216" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P216" s="11"/>
       <c r="Q216" s="11" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="R216" s="9"/>
       <c r="S216" s="9"/>
@@ -18230,13 +18471,13 @@
         <v>いいね</v>
       </c>
       <c r="F217" s="11" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G217" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H217" s="11" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I217" s="11" t="str">
         <f>_xlfn.LET(
@@ -18265,11 +18506,11 @@
         <v>48</v>
       </c>
       <c r="O217" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P217" s="11"/>
       <c r="Q217" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="R217" s="9"/>
       <c r="S217" s="9"/>
@@ -18297,13 +18538,13 @@
         <v>いいね</v>
       </c>
       <c r="F218" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G218" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H218" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I218" s="11">
         <f>_xlfn.LET(
@@ -18366,7 +18607,7 @@
         <v>105</v>
       </c>
       <c r="H219" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I219" s="11">
         <f>_xlfn.LET(
@@ -18498,7 +18739,7 @@
         <v>112</v>
       </c>
       <c r="H221" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I221" s="11">
         <f>_xlfn.LET(
@@ -18630,7 +18871,7 @@
         <v>116</v>
       </c>
       <c r="H223" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I223" s="11">
         <f>_xlfn.LET(
@@ -18681,7 +18922,7 @@
         <v>223</v>
       </c>
       <c r="D224" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E224" s="11" t="s">
         <v>77</v>
@@ -18695,7 +18936,7 @@
         <v>動画リンクID</v>
       </c>
       <c r="H224" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I224" s="11">
         <f>_xlfn.LET(
@@ -18714,7 +18955,7 @@
         <v>32</v>
       </c>
       <c r="J224" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K224" s="11"/>
       <c r="L224" s="9"/>
@@ -18723,13 +18964,13 @@
         <v/>
       </c>
       <c r="N224" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O224" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P224" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q224" s="11"/>
       <c r="R224" s="9"/>
@@ -18787,7 +19028,7 @@
         <v>48</v>
       </c>
       <c r="L225" s="9" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M225" s="11">
         <f>IF(K225="","",IF(L225="","参照先未定義",_xlfn.XLOOKUP(L225,B:B,C:C,"エラー")))</f>
@@ -18799,7 +19040,7 @@
       <c r="O225" s="11"/>
       <c r="P225" s="11"/>
       <c r="Q225" s="11" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="R225" s="9"/>
       <c r="S225" s="9"/>
@@ -18827,10 +19068,10 @@
         <v>動画リンク</v>
       </c>
       <c r="F226" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="G226" s="11" t="s">
         <v>263</v>
-      </c>
-      <c r="G226" s="11" t="s">
-        <v>264</v>
       </c>
       <c r="H226" s="11" t="s">
         <v>81</v>
@@ -18896,7 +19137,7 @@
         <v>105</v>
       </c>
       <c r="H227" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I227" s="11">
         <f>_xlfn.LET(
@@ -19028,7 +19269,7 @@
         <v>112</v>
       </c>
       <c r="H229" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I229" s="11">
         <f>_xlfn.LET(
@@ -19160,7 +19401,7 @@
         <v>116</v>
       </c>
       <c r="H231" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I231" s="11">
         <f>_xlfn.LET(
@@ -19211,10 +19452,10 @@
         <v>231</v>
       </c>
       <c r="D232" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="E232" s="11" t="s">
         <v>265</v>
-      </c>
-      <c r="E232" s="11" t="s">
-        <v>266</v>
       </c>
       <c r="F232" s="11" t="str">
         <f>D232&amp;"_sequence_id"</f>
@@ -19225,7 +19466,7 @@
         <v>関係値ID</v>
       </c>
       <c r="H232" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I232" s="11">
         <f>_xlfn.LET(
@@ -19244,7 +19485,7 @@
         <v>32</v>
       </c>
       <c r="J232" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K232" s="11"/>
       <c r="L232" s="9"/>
@@ -19253,13 +19494,13 @@
         <v/>
       </c>
       <c r="N232" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O232" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P232" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q232" s="11"/>
       <c r="R232" s="9"/>
@@ -19288,10 +19529,10 @@
         <v>関係値</v>
       </c>
       <c r="F233" s="11" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G233" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H233" s="11" t="s">
         <v>99</v>
@@ -19317,7 +19558,7 @@
         <v>48</v>
       </c>
       <c r="L233" s="9" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M233" s="11">
         <f>IF(K233="","",IF(L233="","参照先未定義",_xlfn.XLOOKUP(L233,B:B,C:C,"エラー")))</f>
@@ -19327,11 +19568,11 @@
         <v>48</v>
       </c>
       <c r="O233" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P233" s="11"/>
       <c r="Q233" s="11" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="R233" s="9"/>
       <c r="S233" s="9"/>
@@ -19359,10 +19600,10 @@
         <v>関係値</v>
       </c>
       <c r="F234" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="G234" s="11" t="s">
         <v>268</v>
-      </c>
-      <c r="G234" s="11" t="s">
-        <v>269</v>
       </c>
       <c r="H234" s="11" t="s">
         <v>99</v>
@@ -19388,7 +19629,7 @@
         <v>48</v>
       </c>
       <c r="L234" s="9" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M234" s="11">
         <f>IF(K234="","",IF(L234="","参照先未定義",_xlfn.XLOOKUP(L234,B:B,C:C,"エラー")))</f>
@@ -19398,11 +19639,11 @@
         <v>48</v>
       </c>
       <c r="O234" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P234" s="11"/>
       <c r="Q234" s="11" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R234" s="9"/>
       <c r="S234" s="9"/>
@@ -19430,10 +19671,10 @@
         <v>関係値</v>
       </c>
       <c r="F235" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="G235" s="11" t="s">
         <v>270</v>
-      </c>
-      <c r="G235" s="11" t="s">
-        <v>271</v>
       </c>
       <c r="H235" s="11" t="s">
         <v>65</v>
@@ -19499,7 +19740,7 @@
         <v>105</v>
       </c>
       <c r="H236" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I236" s="11">
         <f>_xlfn.LET(
@@ -19631,7 +19872,7 @@
         <v>112</v>
       </c>
       <c r="H238" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I238" s="11">
         <f>_xlfn.LET(
@@ -19763,7 +20004,7 @@
         <v>116</v>
       </c>
       <c r="H240" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I240" s="11">
         <f>_xlfn.LET(
@@ -19814,10 +20055,10 @@
         <v>240</v>
       </c>
       <c r="D241" s="11" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E241" s="11" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F241" s="11" t="str">
         <f>D241&amp;"_sequence_id"</f>
@@ -19828,7 +20069,7 @@
         <v>Vtuberプロフィール(各言語)ID</v>
       </c>
       <c r="H241" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I241" s="11">
         <f>_xlfn.LET(
@@ -19847,7 +20088,7 @@
         <v>32</v>
       </c>
       <c r="J241" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K241" s="11"/>
       <c r="L241" s="9"/>
@@ -19856,13 +20097,13 @@
         <v/>
       </c>
       <c r="N241" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O241" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P241" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q241" s="11"/>
       <c r="R241" s="9"/>
@@ -19891,7 +20132,7 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G242" s="11" t="s">
         <v>50</v>
@@ -19917,10 +20158,10 @@
       </c>
       <c r="J242" s="11"/>
       <c r="K242" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L242" s="9" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M242" s="11">
         <f>IF(K242="","",IF(L242="","参照先未定義",_xlfn.XLOOKUP(L242,B:B,C:C,"エラー")))</f>
@@ -19930,11 +20171,11 @@
         <v>48</v>
       </c>
       <c r="O242" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="P242" s="11"/>
       <c r="Q242" s="11" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R242" s="9"/>
       <c r="S242" s="9"/>
@@ -19962,10 +20203,10 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F243" s="11" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G243" s="11" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H243" s="11" t="s">
         <v>99</v>
@@ -19988,10 +20229,10 @@
       </c>
       <c r="J243" s="11"/>
       <c r="K243" s="11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L243" s="9" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="M243" s="11">
         <f ca="1">IF(K243="","",IF(L243="","参照先未定義",_xlfn.XLOOKUP(L243,B:B,C:C,"エラー")))</f>
@@ -20001,11 +20242,11 @@
         <v>48</v>
       </c>
       <c r="O243" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="P243" s="11"/>
       <c r="Q243" s="11" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="R243" s="9"/>
       <c r="S243" s="9"/>
@@ -20864,7 +21105,7 @@
         <v>105</v>
       </c>
       <c r="H257" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I257" s="11">
         <f>_xlfn.LET(
@@ -20996,7 +21237,7 @@
         <v>112</v>
       </c>
       <c r="H259" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I259" s="11">
         <f>_xlfn.LET(
@@ -21128,7 +21369,7 @@
         <v>116</v>
       </c>
       <c r="H261" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I261" s="11">
         <f>_xlfn.LET(
@@ -21179,10 +21420,10 @@
         <v>261</v>
       </c>
       <c r="D262" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E262" s="11" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F262" s="11" t="str">
         <f>D262&amp;"_sequence_id"</f>
@@ -21193,7 +21434,7 @@
         <v>プロフィールのタグID</v>
       </c>
       <c r="H262" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I262" s="11">
         <f>_xlfn.LET(
@@ -21212,7 +21453,7 @@
         <v>32</v>
       </c>
       <c r="J262" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K262" s="11"/>
       <c r="L262" s="9"/>
@@ -21221,13 +21462,13 @@
         <v/>
       </c>
       <c r="N262" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O262" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P262" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q262" s="11"/>
       <c r="R262" s="9"/>
@@ -21256,7 +21497,7 @@
         <v>プロフィールのタグ</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G263" s="11" t="s">
         <v>50</v>
@@ -21285,7 +21526,7 @@
         <v>48</v>
       </c>
       <c r="L263" s="9" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M263" s="11">
         <f>IF(K263="","",IF(L263="","参照先未定義",_xlfn.XLOOKUP(L263,B:B,C:C,"エラー")))</f>
@@ -21295,11 +21536,11 @@
         <v>48</v>
       </c>
       <c r="O263" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P263" s="11"/>
       <c r="Q263" s="11" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="R263" s="9"/>
       <c r="S263" s="9"/>
@@ -21327,7 +21568,7 @@
         <v>プロフィールのタグ</v>
       </c>
       <c r="F264" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G264" s="11" t="s">
         <v>124</v>
@@ -21353,10 +21594,10 @@
       </c>
       <c r="J264" s="11"/>
       <c r="K264" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L264" s="9" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="M264" s="11">
         <f ca="1">IF(K264="","",IF(L264="","参照先未定義",_xlfn.XLOOKUP(L264,B:B,C:C,"エラー")))</f>
@@ -21366,11 +21607,11 @@
         <v>48</v>
       </c>
       <c r="O264" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P264" s="11"/>
       <c r="Q264" s="11" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="R264" s="9"/>
       <c r="S264" s="9"/>
@@ -21406,7 +21647,7 @@
         <v>105</v>
       </c>
       <c r="H265" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I265" s="11">
         <f>_xlfn.LET(
@@ -21538,7 +21779,7 @@
         <v>112</v>
       </c>
       <c r="H267" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I267" s="11">
         <f>_xlfn.LET(
@@ -21670,7 +21911,7 @@
         <v>116</v>
       </c>
       <c r="H269" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I269" s="11">
         <f>_xlfn.LET(
@@ -21721,10 +21962,10 @@
         <v>269</v>
       </c>
       <c r="D270" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="E270" s="11" t="s">
         <v>481</v>
-      </c>
-      <c r="E270" s="11" t="s">
-        <v>482</v>
       </c>
       <c r="F270" s="11" t="str">
         <f>D270&amp;"_sequence_id"</f>
@@ -21735,7 +21976,7 @@
         <v>プロフィールの活動ジャンルID</v>
       </c>
       <c r="H270" s="11" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I270" s="11">
         <f>_xlfn.LET(
@@ -21754,7 +21995,7 @@
         <v>32</v>
       </c>
       <c r="J270" s="11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K270" s="11"/>
       <c r="L270" s="9"/>
@@ -21763,13 +22004,13 @@
         <v/>
       </c>
       <c r="N270" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O270" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P270" s="11" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="Q270" s="11"/>
       <c r="R270" s="9"/>
@@ -21798,7 +22039,7 @@
         <v>プロフィールの活動ジャンル</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G271" s="11" t="s">
         <v>50</v>
@@ -21827,7 +22068,7 @@
         <v>48</v>
       </c>
       <c r="L271" s="9" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M271" s="11">
         <f>IF(K271="","",IF(L271="","参照先未定義",_xlfn.XLOOKUP(L271,B:B,C:C,"エラー")))</f>
@@ -21837,11 +22078,11 @@
         <v>48</v>
       </c>
       <c r="O271" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P271" s="11"/>
       <c r="Q271" s="11" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="R271" s="9"/>
       <c r="S271" s="9"/>
@@ -21869,13 +22110,13 @@
         <v>プロフィールの活動ジャンル</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G272" s="11" t="s">
         <v>68</v>
       </c>
       <c r="H272" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I272" s="11">
         <f>_xlfn.LET(
@@ -21904,11 +22145,11 @@
         <v>48</v>
       </c>
       <c r="O272" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P272" s="11"/>
       <c r="Q272" s="11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="R272" s="9"/>
       <c r="S272" s="9"/>
@@ -21944,7 +22185,7 @@
         <v>105</v>
       </c>
       <c r="H273" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I273" s="11">
         <f>_xlfn.LET(
@@ -22076,7 +22317,7 @@
         <v>112</v>
       </c>
       <c r="H275" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I275" s="11">
         <f>_xlfn.LET(
@@ -22208,7 +22449,7 @@
         <v>116</v>
       </c>
       <c r="H277" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I277" s="11">
         <f>_xlfn.LET(
@@ -22271,7 +22512,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18">
       <c r="A1" s="33" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
@@ -22282,36 +22523,36 @@
     </row>
     <row r="2" spans="1:7" ht="19">
       <c r="A2" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="12" t="s">
         <v>276</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19">
       <c r="A3" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="C3" s="13" t="s">
         <v>279</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>280</v>
       </c>
       <c r="D3" s="13">
         <v>2</v>
@@ -22321,21 +22562,21 @@
         <v>16</v>
       </c>
       <c r="F3" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>281</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19">
       <c r="A4" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>99</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D4" s="14">
         <v>4</v>
@@ -22345,21 +22586,21 @@
         <v>32</v>
       </c>
       <c r="F4" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="14" t="s">
         <v>284</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19">
       <c r="A5" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>286</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>287</v>
       </c>
       <c r="D5" s="13">
         <v>8</v>
@@ -22369,21 +22610,21 @@
         <v>64</v>
       </c>
       <c r="F5" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>288</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="19">
       <c r="A6" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>290</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>291</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>76</v>
@@ -22393,21 +22634,21 @@
         <v>-</v>
       </c>
       <c r="F6" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>292</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19">
       <c r="A7" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>76</v>
@@ -22417,21 +22658,21 @@
         <v>-</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19">
       <c r="A8" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D8" s="14">
         <v>4</v>
@@ -22441,21 +22682,21 @@
         <v>32</v>
       </c>
       <c r="F8" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>297</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19">
       <c r="A9" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D9" s="13">
         <v>8</v>
@@ -22465,21 +22706,21 @@
         <v>64</v>
       </c>
       <c r="F9" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>300</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="19">
       <c r="A10" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D10" s="14">
         <v>2</v>
@@ -22489,21 +22730,21 @@
         <v>16</v>
       </c>
       <c r="F10" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>303</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="19">
       <c r="A11" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>157</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D11" s="13">
         <v>4</v>
@@ -22513,21 +22754,21 @@
         <v>32</v>
       </c>
       <c r="F11" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>305</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="19">
       <c r="A12" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D12" s="14">
         <v>8</v>
@@ -22537,21 +22778,21 @@
         <v>64</v>
       </c>
       <c r="F12" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>307</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="19">
       <c r="A13" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>310</v>
-      </c>
       <c r="C13" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D13" s="13">
         <v>8</v>
@@ -22561,21 +22802,21 @@
         <v>64</v>
       </c>
       <c r="F13" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G13" s="13" t="s">
         <v>311</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="19">
       <c r="A14" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="C14" s="14" t="s">
         <v>314</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>315</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>76</v>
@@ -22585,21 +22826,21 @@
         <v>-</v>
       </c>
       <c r="F14" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>316</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="19">
       <c r="A15" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B15" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>318</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>319</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>76</v>
@@ -22609,21 +22850,21 @@
         <v>-</v>
       </c>
       <c r="F15" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>320</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="19">
       <c r="A16" s="14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>81</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>76</v>
@@ -22633,21 +22874,21 @@
         <v>-</v>
       </c>
       <c r="F16" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>322</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="19">
       <c r="A17" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D17" s="13">
         <v>8</v>
@@ -22657,21 +22898,21 @@
         <v>64</v>
       </c>
       <c r="F17" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="G17" s="13" t="s">
         <v>325</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="19">
       <c r="A18" s="14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D18" s="14">
         <v>8</v>
@@ -22681,21 +22922,21 @@
         <v>64</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="19">
       <c r="A19" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D19" s="17">
         <v>8</v>
@@ -22706,18 +22947,18 @@
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="17" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="19">
       <c r="A20" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D20" s="17">
         <v>8</v>
@@ -22728,18 +22969,18 @@
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="19">
       <c r="A21" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D21" s="13">
         <v>4</v>
@@ -22749,21 +22990,21 @@
         <v>32</v>
       </c>
       <c r="F21" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="G21" s="13" t="s">
         <v>330</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="19">
       <c r="A22" s="14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D22" s="14">
         <v>8</v>
@@ -22773,21 +23014,21 @@
         <v>64</v>
       </c>
       <c r="F22" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="G22" s="14" t="s">
         <v>333</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="19">
       <c r="A23" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B23" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>335</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>336</v>
       </c>
       <c r="D23" s="13">
         <v>12</v>
@@ -22797,21 +23038,21 @@
         <v>96</v>
       </c>
       <c r="F23" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="G23" s="13" t="s">
         <v>337</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="19">
       <c r="A24" s="14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D24" s="14">
         <v>12</v>
@@ -22821,21 +23062,21 @@
         <v>96</v>
       </c>
       <c r="F24" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="G24" s="14" t="s">
         <v>340</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="19">
       <c r="A25" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="C25" s="13" t="s">
         <v>343</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>344</v>
       </c>
       <c r="D25" s="13">
         <v>1</v>
@@ -22845,21 +23086,21 @@
         <v>8</v>
       </c>
       <c r="F25" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>345</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="19">
       <c r="A26" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="B26" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="B26" s="14" t="s">
-        <v>348</v>
-      </c>
       <c r="C26" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>76</v>
@@ -22869,21 +23110,21 @@
         <v>-</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="19">
       <c r="A27" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>76</v>
@@ -22893,21 +23134,21 @@
         <v>-</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="19">
       <c r="A28" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="B28" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="C28" s="14" t="s">
         <v>353</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>354</v>
       </c>
       <c r="D28" s="14">
         <v>16</v>
@@ -22917,21 +23158,21 @@
         <v>128</v>
       </c>
       <c r="F28" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="G28" s="14" t="s">
         <v>355</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="19">
       <c r="A29" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B29" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>357</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>358</v>
       </c>
       <c r="D29" s="13">
         <v>32</v>
@@ -22941,21 +23182,21 @@
         <v>256</v>
       </c>
       <c r="F29" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="G29" s="13" t="s">
         <v>359</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="19">
       <c r="A30" s="14" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D30" s="14">
         <v>32</v>
@@ -22965,21 +23206,21 @@
         <v>256</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="19">
       <c r="A31" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D31" s="13">
         <v>32</v>
@@ -22989,21 +23230,21 @@
         <v>256</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="19">
       <c r="A32" s="14" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B32" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="C32" s="14" t="s">
         <v>365</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>366</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>76</v>
@@ -23013,21 +23254,21 @@
         <v>-</v>
       </c>
       <c r="F32" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="G32" s="14" t="s">
         <v>367</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="19">
       <c r="A33" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B33" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>365</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>366</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>76</v>
@@ -23037,21 +23278,21 @@
         <v>-</v>
       </c>
       <c r="F33" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="G33" s="13" t="s">
         <v>369</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="19">
       <c r="A34" s="14" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B34" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="C34" s="14" t="s">
         <v>371</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>372</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>76</v>
@@ -23061,21 +23302,21 @@
         <v>-</v>
       </c>
       <c r="F34" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="G34" s="14" t="s">
         <v>373</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="19">
       <c r="A35" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B35" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>375</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>376</v>
       </c>
       <c r="D35" s="13">
         <v>24</v>
@@ -23085,21 +23326,21 @@
         <v>192</v>
       </c>
       <c r="F35" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="G35" s="13" t="s">
         <v>377</v>
-      </c>
-      <c r="G35" s="13" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="19">
       <c r="A36" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="B36" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="C36" s="14" t="s">
         <v>380</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>381</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>76</v>
@@ -23109,21 +23350,21 @@
         <v>-</v>
       </c>
       <c r="F36" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="G36" s="14" t="s">
         <v>382</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="19">
       <c r="A37" s="13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>76</v>
@@ -23133,21 +23374,21 @@
         <v>-</v>
       </c>
       <c r="F37" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="G37" s="13" t="s">
         <v>385</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="19">
       <c r="A38" s="14" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B38" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="C38" s="14" t="s">
         <v>387</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>388</v>
       </c>
       <c r="D38" s="14">
         <v>6</v>
@@ -23157,21 +23398,21 @@
         <v>48</v>
       </c>
       <c r="F38" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="G38" s="14" t="s">
         <v>389</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="19">
       <c r="A39" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="B39" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="C39" s="13" t="s">
         <v>392</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>393</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>76</v>
@@ -23181,21 +23422,21 @@
         <v>-</v>
       </c>
       <c r="F39" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="G39" s="13" t="s">
         <v>394</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="19">
       <c r="A40" s="14" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B40" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="C40" s="14" t="s">
         <v>396</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>397</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>76</v>
@@ -23205,21 +23446,21 @@
         <v>-</v>
       </c>
       <c r="F40" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="G40" s="14" t="s">
         <v>398</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="19">
       <c r="A41" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="B41" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="B41" s="13" t="s">
-        <v>401</v>
-      </c>
       <c r="C41" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>76</v>
@@ -23232,18 +23473,18 @@
         <v>76</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="19">
       <c r="A42" s="14" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>76</v>
@@ -23256,18 +23497,18 @@
         <v>76</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="19">
       <c r="A43" s="13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D43" s="13">
         <v>4</v>
@@ -23280,18 +23521,18 @@
         <v>76</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="19">
       <c r="A44" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="B44" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="B44" s="14" t="s">
-        <v>408</v>
-      </c>
       <c r="C44" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>76</v>
@@ -23301,21 +23542,21 @@
         <v>-</v>
       </c>
       <c r="F44" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="G44" s="14" t="s">
         <v>409</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="19">
       <c r="A45" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D45" s="13">
         <v>16</v>
@@ -23325,21 +23566,21 @@
         <v>128</v>
       </c>
       <c r="F45" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="G45" s="13" t="s">
         <v>412</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="19">
       <c r="A46" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="B46" s="14" t="s">
         <v>414</v>
       </c>
-      <c r="B46" s="14" t="s">
-        <v>415</v>
-      </c>
       <c r="C46" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>76</v>
@@ -23349,21 +23590,21 @@
         <v>-</v>
       </c>
       <c r="F46" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="G46" s="14" t="s">
         <v>416</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="19">
       <c r="A47" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="B47" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="B47" s="13" t="s">
-        <v>419</v>
-      </c>
       <c r="C47" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>76</v>
@@ -23373,21 +23614,21 @@
         <v>-</v>
       </c>
       <c r="F47" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="G47" s="13" t="s">
         <v>420</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="19">
       <c r="A48" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="B48" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="B48" s="14" t="s">
-        <v>423</v>
-      </c>
       <c r="C48" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>76</v>
@@ -23397,21 +23638,21 @@
         <v>-</v>
       </c>
       <c r="F48" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="G48" s="14" t="s">
         <v>424</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="19">
       <c r="A49" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="B49" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="B49" s="13" t="s">
-        <v>427</v>
-      </c>
       <c r="C49" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>76</v>
@@ -23421,21 +23662,21 @@
         <v>-</v>
       </c>
       <c r="F49" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="G49" s="13" t="s">
         <v>428</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="19">
       <c r="A50" s="14" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>76</v>
@@ -23445,21 +23686,21 @@
         <v>-</v>
       </c>
       <c r="F50" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="G50" s="14" t="s">
         <v>431</v>
-      </c>
-      <c r="G50" s="14" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="19">
       <c r="A51" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>76</v>
@@ -23469,21 +23710,21 @@
         <v>-</v>
       </c>
       <c r="F51" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="G51" s="13" t="s">
         <v>434</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="19">
       <c r="A52" s="14" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>76</v>
@@ -23493,21 +23734,21 @@
         <v>-</v>
       </c>
       <c r="F52" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="G52" s="14" t="s">
         <v>437</v>
-      </c>
-      <c r="G52" s="14" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="19">
       <c r="A53" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>76</v>
@@ -23517,21 +23758,21 @@
         <v>-</v>
       </c>
       <c r="F53" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="G53" s="13" t="s">
         <v>440</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="19">
       <c r="A54" s="14" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>76</v>
@@ -23541,10 +23782,10 @@
         <v>-</v>
       </c>
       <c r="F54" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="G54" s="14" t="s">
         <v>443</v>
-      </c>
-      <c r="G54" s="14" t="s">
-        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -23573,7 +23814,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9015CB-442A-4E29-AB18-BB59E1AE0828}">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
@@ -23584,51 +23825,67 @@
     <col min="6" max="6" width="17.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="19" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:19">
       <c r="A1" s="36" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="31" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="H1" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>498</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>539</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="N1" s="31" t="s">
+        <v>591</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>591</v>
+      </c>
+      <c r="P1" s="31" t="s">
+        <v>607</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>607</v>
+      </c>
+      <c r="R1" s="24" t="s">
+        <v>607</v>
+      </c>
+      <c r="S1" s="24"/>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="38" t="s">
         <v>501</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>501</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>542</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>542</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="38" t="s">
-        <v>504</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="21">
@@ -23675,13 +23932,37 @@
         <f t="shared" ref="M2" si="8">IF(L1=M1,L2+1,1)</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" s="21">
+        <f t="shared" ref="N2" si="9">IF(M1=N1,M2+1,1)</f>
+        <v>1</v>
+      </c>
+      <c r="O2" s="21">
+        <f t="shared" ref="O2" si="10">IF(N1=O1,N2+1,1)</f>
+        <v>2</v>
+      </c>
+      <c r="P2" s="21">
+        <f>IF(L1=P1,L2+1,1)</f>
+        <v>1</v>
+      </c>
+      <c r="Q2" s="21">
+        <f>IF(M1=Q1,M2+1,1)</f>
+        <v>1</v>
+      </c>
+      <c r="R2" s="21">
+        <f>IF(N1=R1,N2+1,1)</f>
+        <v>1</v>
+      </c>
+      <c r="S2" s="21">
+        <f>IF(O1=S1,O2+1,1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="35" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C3" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23701,7 +23982,7 @@
       </c>
       <c r="G3" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="G3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=G$1), G$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
-        <v>message_type</v>
+        <v>message_id_table</v>
       </c>
       <c r="H3" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="H3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=H$1), H$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23727,11 +24008,35 @@
         <f t="array" aca="1" ref="M3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
         <v>enable</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="N3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=N$1), N$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>activity_status_sequence_id</v>
+      </c>
+      <c r="O3" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="O3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=O$1), O$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>activity_status_physical_name</v>
+      </c>
+      <c r="P3" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="P3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=P$1), P$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>priority_sequence_id</v>
+      </c>
+      <c r="Q3" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="Q3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=Q$1), Q$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>priority_sequence_id</v>
+      </c>
+      <c r="R3" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="R3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=R$1), R$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>priority_sequence_id</v>
+      </c>
+      <c r="S3" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="S3" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=S$1), S$2, _xlfn.XMATCH($B3, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4" s="35"/>
       <c r="B4" s="26" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C4" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23751,7 +24056,7 @@
       </c>
       <c r="G4" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="G4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=G$1), G$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
-        <v>文言種別</v>
+        <v>メッセージID参照元テーブル</v>
       </c>
       <c r="H4" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="H4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=H$1), H$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23777,11 +24082,35 @@
         <f t="array" aca="1" ref="M4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
         <v>有効フラグ</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="N4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=N$1), N$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>活動状態ID</v>
+      </c>
+      <c r="O4" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="O4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=O$1), O$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>活動状態名(物理名)</v>
+      </c>
+      <c r="P4" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="P4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=P$1), P$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>優先度ID</v>
+      </c>
+      <c r="Q4" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="Q4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=Q$1), Q$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>優先度ID</v>
+      </c>
+      <c r="R4" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="R4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=R$1), R$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>優先度ID</v>
+      </c>
+      <c r="S4" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="S4" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=S$1), S$2, _xlfn.XMATCH($B4, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="35"/>
       <c r="B5" s="22" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C5" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23793,7 +24122,7 @@
       </c>
       <c r="E5" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=E$1), E$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
-        <v>serial</v>
+        <v>integer</v>
       </c>
       <c r="F5" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=F$1), F$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23827,11 +24156,35 @@
         <f t="array" aca="1" ref="M5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
         <v>boolean</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="N5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=N$1), N$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>serial</v>
+      </c>
+      <c r="O5" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="O5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=O$1), O$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>varchar(8)</v>
+      </c>
+      <c r="P5" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="P5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=P$1), P$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>serial</v>
+      </c>
+      <c r="Q5" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="Q5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=Q$1), Q$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>serial</v>
+      </c>
+      <c r="R5" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="R5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=R$1), R$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>serial</v>
+      </c>
+      <c r="S5" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="S5" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=S$1), S$2, _xlfn.XMATCH($B5, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="35"/>
       <c r="B6" s="22" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C6" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23877,11 +24230,35 @@
         <f t="array" aca="1" ref="M6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
         <v/>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="N6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=N$1), N$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="O6" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="O6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=O$1), O$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="P6" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="P6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=P$1), P$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="Q6" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="Q6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=Q$1), Q$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="R6" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="R6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=R$1), R$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="S6" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="S6" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=S$1), S$2, _xlfn.XMATCH($B6, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="35"/>
       <c r="B7" s="22" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C7" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23927,11 +24304,35 @@
         <f t="array" aca="1" ref="M7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
         <v/>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="N7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=N$1), N$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="O7" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="O7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=O$1), O$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="P7" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="P7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=P$1), P$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="Q7" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="Q7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=Q$1), Q$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="R7" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="R7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=R$1), R$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="S7" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="S7" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=S$1), S$2, _xlfn.XMATCH($B7, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="35"/>
       <c r="B8" s="22" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C8" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=C$1), C$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -23977,8 +24378,32 @@
         <f t="array" aca="1" ref="M8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
         <v/>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="N8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=N$1), N$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="O8" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="O8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=O$1), O$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="P8" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="P8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=P$1), P$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="Q8" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="Q8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=Q$1), Q$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="R8" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="R8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=R$1), R$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="S8" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="S8" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=S$1), S$2, _xlfn.XMATCH($B8, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="35"/>
       <c r="B9" s="21" t="s">
         <v>40</v>
@@ -24027,8 +24452,32 @@
         <f t="array" aca="1" ref="M9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
         <v>x</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="N9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=N$1), N$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="O9" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="O9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=O$1), O$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="P9" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="P9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=P$1), P$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="Q9" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="Q9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=Q$1), Q$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="R9" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="R9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=R$1), R$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="S9" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="S9" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=S$1), S$2, _xlfn.XMATCH($B9, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="35"/>
       <c r="B10" s="21" t="s">
         <v>41</v>
@@ -24043,7 +24492,7 @@
       </c>
       <c r="E10" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="E10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=E$1), E$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
-        <v>x</v>
+        <v/>
       </c>
       <c r="F10" s="27" t="str" cm="1">
         <f t="array" aca="1" ref="F10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=F$1), F$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
@@ -24077,8 +24526,32 @@
         <f t="array" aca="1" ref="M10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
         <v/>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="N10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=N$1), N$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="O10" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="O10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=O$1), O$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x</v>
+      </c>
+      <c r="P10" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="P10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=P$1), P$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="Q10" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="Q10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=Q$1), Q$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="R10" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="R10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=R$1), R$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>x(PK制約)</v>
+      </c>
+      <c r="S10" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="S10" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=S$1), S$2, _xlfn.XMATCH($B10, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" s="35"/>
       <c r="B11" s="21" t="s">
         <v>42</v>
@@ -24127,137 +24600,191 @@
         <f t="array" aca="1" ref="M11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=M$1), M$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
         <v>FALSE</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="N11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=N$1), N$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>SEQUENCE</v>
+      </c>
+      <c r="O11" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="O11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=O$1), O$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+      <c r="P11" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="P11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=P$1), P$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>SEQUENCE</v>
+      </c>
+      <c r="Q11" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="Q11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=Q$1), Q$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>SEQUENCE</v>
+      </c>
+      <c r="R11" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="R11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=R$1), R$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v>SEQUENCE</v>
+      </c>
+      <c r="S11" s="27" t="str" cm="1">
+        <f t="array" aca="1" ref="S11" ca="1">INDEX(_xlfn._xlws.FILTER(テーブル定義_一覧!$D:$U, テーブル定義_一覧!$D:$D=S$1), S$2, _xlfn.XMATCH($B11, テーブル定義_一覧!$D$1:$Z$1))&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="35" t="s">
+        <v>525</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>504</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>570</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>572</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>535</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="I12" s="28" t="s">
         <v>528</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>507</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>537</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>573</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>575</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>538</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>541</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>537</v>
-      </c>
-      <c r="I12" s="28" t="s">
-        <v>531</v>
-      </c>
       <c r="J12" s="32" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="K12" s="28" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="L12" s="28" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="M12" s="28" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="O12" s="41" t="s">
+        <v>601</v>
+      </c>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="35"/>
       <c r="B13" s="23" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D13" s="28" t="s">
+        <v>570</v>
+      </c>
+      <c r="E13" s="28" t="s">
         <v>573</v>
       </c>
-      <c r="E13" s="28" t="s">
-        <v>576</v>
-      </c>
       <c r="F13" s="28" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H13" s="32" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="J13" s="32" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="K13" s="28" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="L13" s="28" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="M13" s="28" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="O13" s="28" t="s">
+        <v>596</v>
+      </c>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" s="35"/>
       <c r="B14" s="23" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C14" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>570</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>574</v>
+      </c>
+      <c r="F14" s="28" t="s">
         <v>537</v>
       </c>
-      <c r="D14" s="28" t="s">
-        <v>573</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>577</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>540</v>
-      </c>
       <c r="G14" s="28" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J14" s="32"/>
       <c r="K14" s="28"/>
       <c r="L14" s="28"/>
       <c r="M14" s="28"/>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N14" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="O14" s="28" t="s">
+        <v>598</v>
+      </c>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" s="35"/>
       <c r="B15" s="23" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F15" s="28" t="s">
+        <v>535</v>
+      </c>
+      <c r="G15" s="28" t="s">
         <v>538</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>541</v>
       </c>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
@@ -24265,26 +24792,36 @@
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="O15" s="28" t="s">
+        <v>597</v>
+      </c>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="18"/>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="35"/>
       <c r="B16" s="23" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
@@ -24292,26 +24829,36 @@
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="O16" s="28" t="s">
+        <v>600</v>
+      </c>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="18"/>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="35"/>
       <c r="B17" s="23" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C17" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>571</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>574</v>
+      </c>
+      <c r="F17" s="28" t="s">
         <v>537</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>574</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>577</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>540</v>
-      </c>
       <c r="G17" s="28" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
@@ -24319,181 +24866,347 @@
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
       <c r="M17" s="18"/>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="18"/>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="35"/>
       <c r="B18" s="23" t="s">
-        <v>513</v>
-      </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
+        <v>510</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>570</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>602</v>
+      </c>
+      <c r="F18" s="40" t="s">
+        <v>592</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>538</v>
+      </c>
       <c r="H18" s="18"/>
       <c r="I18" s="18"/>
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
       <c r="M18" s="18"/>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="18"/>
+      <c r="R18" s="18"/>
+      <c r="S18" s="18"/>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="35"/>
       <c r="B19" s="23" t="s">
-        <v>514</v>
-      </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
+        <v>511</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>570</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>593</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>538</v>
+      </c>
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
       <c r="J19" s="18"/>
       <c r="K19" s="18"/>
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="18"/>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="35"/>
       <c r="B20" s="23" t="s">
-        <v>515</v>
-      </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
+        <v>512</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>570</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>604</v>
+      </c>
+      <c r="F20" s="41" t="s">
+        <v>594</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>538</v>
+      </c>
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
       <c r="L20" s="18"/>
       <c r="M20" s="18"/>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="18"/>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="35"/>
       <c r="B21" s="23" t="s">
-        <v>516</v>
-      </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
+        <v>513</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>570</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>605</v>
+      </c>
+      <c r="F21" s="41" t="s">
+        <v>595</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>538</v>
+      </c>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
       <c r="L21" s="18"/>
       <c r="M21" s="18"/>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="18"/>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="35"/>
       <c r="B22" s="23" t="s">
-        <v>517</v>
-      </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
+        <v>514</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>570</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>606</v>
+      </c>
+      <c r="F22" s="41" t="s">
+        <v>599</v>
+      </c>
+      <c r="G22" s="28" t="s">
+        <v>538</v>
+      </c>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
       <c r="J22" s="18"/>
       <c r="K22" s="18"/>
       <c r="L22" s="18"/>
       <c r="M22" s="18"/>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="18"/>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" s="35"/>
       <c r="B23" s="23" t="s">
-        <v>518</v>
-      </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
+        <v>515</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>571</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>602</v>
+      </c>
+      <c r="F23" s="40" t="s">
+        <v>592</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>538</v>
+      </c>
       <c r="H23" s="18"/>
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
       <c r="L23" s="18"/>
       <c r="M23" s="18"/>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="18"/>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" s="35"/>
       <c r="B24" s="23" t="s">
-        <v>519</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
+        <v>516</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>571</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="F24" s="41" t="s">
+        <v>593</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>538</v>
+      </c>
       <c r="H24" s="18"/>
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
       <c r="K24" s="18"/>
       <c r="L24" s="18"/>
       <c r="M24" s="18"/>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="18"/>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" s="35"/>
       <c r="B25" s="23" t="s">
-        <v>520</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
+        <v>517</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>571</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>604</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>594</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>538</v>
+      </c>
       <c r="H25" s="18"/>
       <c r="I25" s="18"/>
       <c r="J25" s="18"/>
       <c r="K25" s="18"/>
       <c r="L25" s="18"/>
       <c r="M25" s="18"/>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="18"/>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="35"/>
       <c r="B26" s="23" t="s">
-        <v>521</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
+        <v>518</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>571</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>605</v>
+      </c>
+      <c r="F26" s="41" t="s">
+        <v>595</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>538</v>
+      </c>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
       <c r="M26" s="18"/>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="18"/>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" s="35"/>
       <c r="B27" s="23" t="s">
-        <v>522</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
+        <v>519</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>571</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>606</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>599</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>538</v>
+      </c>
       <c r="H27" s="18"/>
       <c r="I27" s="18"/>
       <c r="J27" s="18"/>
       <c r="K27" s="18"/>
       <c r="L27" s="18"/>
       <c r="M27" s="18"/>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" s="35"/>
       <c r="B28" s="23" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -24506,11 +25219,17 @@
       <c r="K28" s="18"/>
       <c r="L28" s="18"/>
       <c r="M28" s="18"/>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="18"/>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="35"/>
       <c r="B29" s="23" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -24523,11 +25242,17 @@
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
       <c r="M29" s="18"/>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="18"/>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" s="35"/>
       <c r="B30" s="23" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
@@ -24540,11 +25265,17 @@
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
       <c r="M30" s="18"/>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18"/>
+      <c r="R30" s="18"/>
+      <c r="S30" s="18"/>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" s="35"/>
       <c r="B31" s="23" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
@@ -24557,13 +25288,25 @@
       <c r="K31" s="18"/>
       <c r="L31" s="18"/>
       <c r="M31" s="18"/>
-    </row>
-    <row r="33" spans="9:13">
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="18"/>
+    </row>
+    <row r="33" spans="9:19">
       <c r="I33" s="20"/>
       <c r="J33" s="20"/>
       <c r="K33" s="20"/>
       <c r="L33" s="20"/>
       <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -24574,6 +25317,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -24593,28 +25337,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="36" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="30" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E1" s="29" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="F1" s="29" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G1" s="29" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="38" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="21">
@@ -24640,10 +25384,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="35" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C3" s="27" t="s">
         <v>104</v>
@@ -24664,7 +25408,7 @@
     <row r="4" spans="1:8">
       <c r="A4" s="35"/>
       <c r="B4" s="26" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>105</v>
@@ -24685,22 +25429,22 @@
     <row r="5" spans="1:8">
       <c r="A5" s="35"/>
       <c r="B5" s="22" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>65</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>65</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -24730,19 +25474,19 @@
         <v>41</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -24768,28 +25512,28 @@
     </row>
     <row r="9" spans="1:8" ht="58">
       <c r="A9" s="25" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="G9" s="18" t="b">
         <v>0</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
   </sheetData>

--- a/.design/DB/DB設計.xlsx
+++ b/.design/DB/DB設計.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevelopmentProjects\vtuber-meikan\.design\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACDEB02-F697-45E4-B926-0DFC4FF3B371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C98D155-A8C9-40A3-9596-6E362BC0866F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51480" yWindow="-120" windowWidth="57840" windowHeight="31920" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
